--- a/resultados/Resultados 14-12-25.xlsx
+++ b/resultados/Resultados 14-12-25.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Juan Diaz\Downloads\Creador-Programa\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\juan_\Downloads\Hipódromo\programa gemini original\resultados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F5C6D513-9812-40C4-A920-7C30003E7FA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9D2B220-30C4-42D7-8C4B-1F95E2440F63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{2DAAAAA9-B6FF-43A5-94E7-31CE6C9DB932}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2DAAAAA9-B6FF-43A5-94E7-31CE6C9DB932}"/>
   </bookViews>
   <sheets>
     <sheet name="14-12-25" sheetId="1" r:id="rId1"/>
@@ -2092,30 +2092,15 @@
   </cellStyleXfs>
   <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
@@ -2147,15 +2132,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -2163,6 +2139,30 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2468,4796 +2468,4848 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47482E32-0582-41D2-BE16-56D50195BE2E}">
   <dimension ref="A1:H298"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.28515625" customWidth="1"/>
-    <col min="2" max="2" width="3.140625" customWidth="1"/>
-    <col min="3" max="3" width="23.85546875" customWidth="1"/>
-    <col min="4" max="4" width="6.140625" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" customWidth="1"/>
-    <col min="6" max="6" width="9.85546875" customWidth="1"/>
-    <col min="7" max="8" width="9.28515625" customWidth="1"/>
-    <col min="257" max="257" width="6.28515625" customWidth="1"/>
-    <col min="258" max="258" width="3.140625" customWidth="1"/>
-    <col min="259" max="259" width="23.85546875" customWidth="1"/>
-    <col min="260" max="260" width="6.140625" customWidth="1"/>
-    <col min="261" max="261" width="20.42578125" customWidth="1"/>
-    <col min="262" max="262" width="9.85546875" customWidth="1"/>
-    <col min="263" max="264" width="9.28515625" customWidth="1"/>
-    <col min="513" max="513" width="6.28515625" customWidth="1"/>
-    <col min="514" max="514" width="3.140625" customWidth="1"/>
-    <col min="515" max="515" width="23.85546875" customWidth="1"/>
-    <col min="516" max="516" width="6.140625" customWidth="1"/>
-    <col min="517" max="517" width="20.42578125" customWidth="1"/>
-    <col min="518" max="518" width="9.85546875" customWidth="1"/>
-    <col min="519" max="520" width="9.28515625" customWidth="1"/>
-    <col min="769" max="769" width="6.28515625" customWidth="1"/>
-    <col min="770" max="770" width="3.140625" customWidth="1"/>
-    <col min="771" max="771" width="23.85546875" customWidth="1"/>
-    <col min="772" max="772" width="6.140625" customWidth="1"/>
-    <col min="773" max="773" width="20.42578125" customWidth="1"/>
-    <col min="774" max="774" width="9.85546875" customWidth="1"/>
-    <col min="775" max="776" width="9.28515625" customWidth="1"/>
-    <col min="1025" max="1025" width="6.28515625" customWidth="1"/>
-    <col min="1026" max="1026" width="3.140625" customWidth="1"/>
-    <col min="1027" max="1027" width="23.85546875" customWidth="1"/>
-    <col min="1028" max="1028" width="6.140625" customWidth="1"/>
-    <col min="1029" max="1029" width="20.42578125" customWidth="1"/>
-    <col min="1030" max="1030" width="9.85546875" customWidth="1"/>
-    <col min="1031" max="1032" width="9.28515625" customWidth="1"/>
-    <col min="1281" max="1281" width="6.28515625" customWidth="1"/>
-    <col min="1282" max="1282" width="3.140625" customWidth="1"/>
-    <col min="1283" max="1283" width="23.85546875" customWidth="1"/>
-    <col min="1284" max="1284" width="6.140625" customWidth="1"/>
-    <col min="1285" max="1285" width="20.42578125" customWidth="1"/>
-    <col min="1286" max="1286" width="9.85546875" customWidth="1"/>
-    <col min="1287" max="1288" width="9.28515625" customWidth="1"/>
-    <col min="1537" max="1537" width="6.28515625" customWidth="1"/>
-    <col min="1538" max="1538" width="3.140625" customWidth="1"/>
-    <col min="1539" max="1539" width="23.85546875" customWidth="1"/>
-    <col min="1540" max="1540" width="6.140625" customWidth="1"/>
-    <col min="1541" max="1541" width="20.42578125" customWidth="1"/>
-    <col min="1542" max="1542" width="9.85546875" customWidth="1"/>
-    <col min="1543" max="1544" width="9.28515625" customWidth="1"/>
-    <col min="1793" max="1793" width="6.28515625" customWidth="1"/>
-    <col min="1794" max="1794" width="3.140625" customWidth="1"/>
-    <col min="1795" max="1795" width="23.85546875" customWidth="1"/>
-    <col min="1796" max="1796" width="6.140625" customWidth="1"/>
-    <col min="1797" max="1797" width="20.42578125" customWidth="1"/>
-    <col min="1798" max="1798" width="9.85546875" customWidth="1"/>
-    <col min="1799" max="1800" width="9.28515625" customWidth="1"/>
-    <col min="2049" max="2049" width="6.28515625" customWidth="1"/>
-    <col min="2050" max="2050" width="3.140625" customWidth="1"/>
-    <col min="2051" max="2051" width="23.85546875" customWidth="1"/>
-    <col min="2052" max="2052" width="6.140625" customWidth="1"/>
-    <col min="2053" max="2053" width="20.42578125" customWidth="1"/>
-    <col min="2054" max="2054" width="9.85546875" customWidth="1"/>
-    <col min="2055" max="2056" width="9.28515625" customWidth="1"/>
-    <col min="2305" max="2305" width="6.28515625" customWidth="1"/>
-    <col min="2306" max="2306" width="3.140625" customWidth="1"/>
-    <col min="2307" max="2307" width="23.85546875" customWidth="1"/>
-    <col min="2308" max="2308" width="6.140625" customWidth="1"/>
-    <col min="2309" max="2309" width="20.42578125" customWidth="1"/>
-    <col min="2310" max="2310" width="9.85546875" customWidth="1"/>
-    <col min="2311" max="2312" width="9.28515625" customWidth="1"/>
-    <col min="2561" max="2561" width="6.28515625" customWidth="1"/>
-    <col min="2562" max="2562" width="3.140625" customWidth="1"/>
-    <col min="2563" max="2563" width="23.85546875" customWidth="1"/>
-    <col min="2564" max="2564" width="6.140625" customWidth="1"/>
-    <col min="2565" max="2565" width="20.42578125" customWidth="1"/>
-    <col min="2566" max="2566" width="9.85546875" customWidth="1"/>
-    <col min="2567" max="2568" width="9.28515625" customWidth="1"/>
-    <col min="2817" max="2817" width="6.28515625" customWidth="1"/>
-    <col min="2818" max="2818" width="3.140625" customWidth="1"/>
-    <col min="2819" max="2819" width="23.85546875" customWidth="1"/>
-    <col min="2820" max="2820" width="6.140625" customWidth="1"/>
-    <col min="2821" max="2821" width="20.42578125" customWidth="1"/>
-    <col min="2822" max="2822" width="9.85546875" customWidth="1"/>
-    <col min="2823" max="2824" width="9.28515625" customWidth="1"/>
-    <col min="3073" max="3073" width="6.28515625" customWidth="1"/>
-    <col min="3074" max="3074" width="3.140625" customWidth="1"/>
-    <col min="3075" max="3075" width="23.85546875" customWidth="1"/>
-    <col min="3076" max="3076" width="6.140625" customWidth="1"/>
-    <col min="3077" max="3077" width="20.42578125" customWidth="1"/>
-    <col min="3078" max="3078" width="9.85546875" customWidth="1"/>
-    <col min="3079" max="3080" width="9.28515625" customWidth="1"/>
-    <col min="3329" max="3329" width="6.28515625" customWidth="1"/>
-    <col min="3330" max="3330" width="3.140625" customWidth="1"/>
-    <col min="3331" max="3331" width="23.85546875" customWidth="1"/>
-    <col min="3332" max="3332" width="6.140625" customWidth="1"/>
-    <col min="3333" max="3333" width="20.42578125" customWidth="1"/>
-    <col min="3334" max="3334" width="9.85546875" customWidth="1"/>
-    <col min="3335" max="3336" width="9.28515625" customWidth="1"/>
-    <col min="3585" max="3585" width="6.28515625" customWidth="1"/>
-    <col min="3586" max="3586" width="3.140625" customWidth="1"/>
-    <col min="3587" max="3587" width="23.85546875" customWidth="1"/>
-    <col min="3588" max="3588" width="6.140625" customWidth="1"/>
-    <col min="3589" max="3589" width="20.42578125" customWidth="1"/>
-    <col min="3590" max="3590" width="9.85546875" customWidth="1"/>
-    <col min="3591" max="3592" width="9.28515625" customWidth="1"/>
-    <col min="3841" max="3841" width="6.28515625" customWidth="1"/>
-    <col min="3842" max="3842" width="3.140625" customWidth="1"/>
-    <col min="3843" max="3843" width="23.85546875" customWidth="1"/>
-    <col min="3844" max="3844" width="6.140625" customWidth="1"/>
-    <col min="3845" max="3845" width="20.42578125" customWidth="1"/>
-    <col min="3846" max="3846" width="9.85546875" customWidth="1"/>
-    <col min="3847" max="3848" width="9.28515625" customWidth="1"/>
-    <col min="4097" max="4097" width="6.28515625" customWidth="1"/>
-    <col min="4098" max="4098" width="3.140625" customWidth="1"/>
-    <col min="4099" max="4099" width="23.85546875" customWidth="1"/>
-    <col min="4100" max="4100" width="6.140625" customWidth="1"/>
-    <col min="4101" max="4101" width="20.42578125" customWidth="1"/>
-    <col min="4102" max="4102" width="9.85546875" customWidth="1"/>
-    <col min="4103" max="4104" width="9.28515625" customWidth="1"/>
-    <col min="4353" max="4353" width="6.28515625" customWidth="1"/>
-    <col min="4354" max="4354" width="3.140625" customWidth="1"/>
-    <col min="4355" max="4355" width="23.85546875" customWidth="1"/>
-    <col min="4356" max="4356" width="6.140625" customWidth="1"/>
-    <col min="4357" max="4357" width="20.42578125" customWidth="1"/>
-    <col min="4358" max="4358" width="9.85546875" customWidth="1"/>
-    <col min="4359" max="4360" width="9.28515625" customWidth="1"/>
-    <col min="4609" max="4609" width="6.28515625" customWidth="1"/>
-    <col min="4610" max="4610" width="3.140625" customWidth="1"/>
-    <col min="4611" max="4611" width="23.85546875" customWidth="1"/>
-    <col min="4612" max="4612" width="6.140625" customWidth="1"/>
-    <col min="4613" max="4613" width="20.42578125" customWidth="1"/>
-    <col min="4614" max="4614" width="9.85546875" customWidth="1"/>
-    <col min="4615" max="4616" width="9.28515625" customWidth="1"/>
-    <col min="4865" max="4865" width="6.28515625" customWidth="1"/>
-    <col min="4866" max="4866" width="3.140625" customWidth="1"/>
-    <col min="4867" max="4867" width="23.85546875" customWidth="1"/>
-    <col min="4868" max="4868" width="6.140625" customWidth="1"/>
-    <col min="4869" max="4869" width="20.42578125" customWidth="1"/>
-    <col min="4870" max="4870" width="9.85546875" customWidth="1"/>
-    <col min="4871" max="4872" width="9.28515625" customWidth="1"/>
-    <col min="5121" max="5121" width="6.28515625" customWidth="1"/>
-    <col min="5122" max="5122" width="3.140625" customWidth="1"/>
-    <col min="5123" max="5123" width="23.85546875" customWidth="1"/>
-    <col min="5124" max="5124" width="6.140625" customWidth="1"/>
-    <col min="5125" max="5125" width="20.42578125" customWidth="1"/>
-    <col min="5126" max="5126" width="9.85546875" customWidth="1"/>
-    <col min="5127" max="5128" width="9.28515625" customWidth="1"/>
-    <col min="5377" max="5377" width="6.28515625" customWidth="1"/>
-    <col min="5378" max="5378" width="3.140625" customWidth="1"/>
-    <col min="5379" max="5379" width="23.85546875" customWidth="1"/>
-    <col min="5380" max="5380" width="6.140625" customWidth="1"/>
-    <col min="5381" max="5381" width="20.42578125" customWidth="1"/>
-    <col min="5382" max="5382" width="9.85546875" customWidth="1"/>
-    <col min="5383" max="5384" width="9.28515625" customWidth="1"/>
-    <col min="5633" max="5633" width="6.28515625" customWidth="1"/>
-    <col min="5634" max="5634" width="3.140625" customWidth="1"/>
-    <col min="5635" max="5635" width="23.85546875" customWidth="1"/>
-    <col min="5636" max="5636" width="6.140625" customWidth="1"/>
-    <col min="5637" max="5637" width="20.42578125" customWidth="1"/>
-    <col min="5638" max="5638" width="9.85546875" customWidth="1"/>
-    <col min="5639" max="5640" width="9.28515625" customWidth="1"/>
-    <col min="5889" max="5889" width="6.28515625" customWidth="1"/>
-    <col min="5890" max="5890" width="3.140625" customWidth="1"/>
-    <col min="5891" max="5891" width="23.85546875" customWidth="1"/>
-    <col min="5892" max="5892" width="6.140625" customWidth="1"/>
-    <col min="5893" max="5893" width="20.42578125" customWidth="1"/>
-    <col min="5894" max="5894" width="9.85546875" customWidth="1"/>
-    <col min="5895" max="5896" width="9.28515625" customWidth="1"/>
-    <col min="6145" max="6145" width="6.28515625" customWidth="1"/>
-    <col min="6146" max="6146" width="3.140625" customWidth="1"/>
-    <col min="6147" max="6147" width="23.85546875" customWidth="1"/>
-    <col min="6148" max="6148" width="6.140625" customWidth="1"/>
-    <col min="6149" max="6149" width="20.42578125" customWidth="1"/>
-    <col min="6150" max="6150" width="9.85546875" customWidth="1"/>
-    <col min="6151" max="6152" width="9.28515625" customWidth="1"/>
-    <col min="6401" max="6401" width="6.28515625" customWidth="1"/>
-    <col min="6402" max="6402" width="3.140625" customWidth="1"/>
-    <col min="6403" max="6403" width="23.85546875" customWidth="1"/>
-    <col min="6404" max="6404" width="6.140625" customWidth="1"/>
-    <col min="6405" max="6405" width="20.42578125" customWidth="1"/>
-    <col min="6406" max="6406" width="9.85546875" customWidth="1"/>
-    <col min="6407" max="6408" width="9.28515625" customWidth="1"/>
-    <col min="6657" max="6657" width="6.28515625" customWidth="1"/>
-    <col min="6658" max="6658" width="3.140625" customWidth="1"/>
-    <col min="6659" max="6659" width="23.85546875" customWidth="1"/>
-    <col min="6660" max="6660" width="6.140625" customWidth="1"/>
-    <col min="6661" max="6661" width="20.42578125" customWidth="1"/>
-    <col min="6662" max="6662" width="9.85546875" customWidth="1"/>
-    <col min="6663" max="6664" width="9.28515625" customWidth="1"/>
-    <col min="6913" max="6913" width="6.28515625" customWidth="1"/>
-    <col min="6914" max="6914" width="3.140625" customWidth="1"/>
-    <col min="6915" max="6915" width="23.85546875" customWidth="1"/>
-    <col min="6916" max="6916" width="6.140625" customWidth="1"/>
-    <col min="6917" max="6917" width="20.42578125" customWidth="1"/>
-    <col min="6918" max="6918" width="9.85546875" customWidth="1"/>
-    <col min="6919" max="6920" width="9.28515625" customWidth="1"/>
-    <col min="7169" max="7169" width="6.28515625" customWidth="1"/>
-    <col min="7170" max="7170" width="3.140625" customWidth="1"/>
-    <col min="7171" max="7171" width="23.85546875" customWidth="1"/>
-    <col min="7172" max="7172" width="6.140625" customWidth="1"/>
-    <col min="7173" max="7173" width="20.42578125" customWidth="1"/>
-    <col min="7174" max="7174" width="9.85546875" customWidth="1"/>
-    <col min="7175" max="7176" width="9.28515625" customWidth="1"/>
-    <col min="7425" max="7425" width="6.28515625" customWidth="1"/>
-    <col min="7426" max="7426" width="3.140625" customWidth="1"/>
-    <col min="7427" max="7427" width="23.85546875" customWidth="1"/>
-    <col min="7428" max="7428" width="6.140625" customWidth="1"/>
-    <col min="7429" max="7429" width="20.42578125" customWidth="1"/>
-    <col min="7430" max="7430" width="9.85546875" customWidth="1"/>
-    <col min="7431" max="7432" width="9.28515625" customWidth="1"/>
-    <col min="7681" max="7681" width="6.28515625" customWidth="1"/>
-    <col min="7682" max="7682" width="3.140625" customWidth="1"/>
-    <col min="7683" max="7683" width="23.85546875" customWidth="1"/>
-    <col min="7684" max="7684" width="6.140625" customWidth="1"/>
-    <col min="7685" max="7685" width="20.42578125" customWidth="1"/>
-    <col min="7686" max="7686" width="9.85546875" customWidth="1"/>
-    <col min="7687" max="7688" width="9.28515625" customWidth="1"/>
-    <col min="7937" max="7937" width="6.28515625" customWidth="1"/>
-    <col min="7938" max="7938" width="3.140625" customWidth="1"/>
-    <col min="7939" max="7939" width="23.85546875" customWidth="1"/>
-    <col min="7940" max="7940" width="6.140625" customWidth="1"/>
-    <col min="7941" max="7941" width="20.42578125" customWidth="1"/>
-    <col min="7942" max="7942" width="9.85546875" customWidth="1"/>
-    <col min="7943" max="7944" width="9.28515625" customWidth="1"/>
-    <col min="8193" max="8193" width="6.28515625" customWidth="1"/>
-    <col min="8194" max="8194" width="3.140625" customWidth="1"/>
-    <col min="8195" max="8195" width="23.85546875" customWidth="1"/>
-    <col min="8196" max="8196" width="6.140625" customWidth="1"/>
-    <col min="8197" max="8197" width="20.42578125" customWidth="1"/>
-    <col min="8198" max="8198" width="9.85546875" customWidth="1"/>
-    <col min="8199" max="8200" width="9.28515625" customWidth="1"/>
-    <col min="8449" max="8449" width="6.28515625" customWidth="1"/>
-    <col min="8450" max="8450" width="3.140625" customWidth="1"/>
-    <col min="8451" max="8451" width="23.85546875" customWidth="1"/>
-    <col min="8452" max="8452" width="6.140625" customWidth="1"/>
-    <col min="8453" max="8453" width="20.42578125" customWidth="1"/>
-    <col min="8454" max="8454" width="9.85546875" customWidth="1"/>
-    <col min="8455" max="8456" width="9.28515625" customWidth="1"/>
-    <col min="8705" max="8705" width="6.28515625" customWidth="1"/>
-    <col min="8706" max="8706" width="3.140625" customWidth="1"/>
-    <col min="8707" max="8707" width="23.85546875" customWidth="1"/>
-    <col min="8708" max="8708" width="6.140625" customWidth="1"/>
-    <col min="8709" max="8709" width="20.42578125" customWidth="1"/>
-    <col min="8710" max="8710" width="9.85546875" customWidth="1"/>
-    <col min="8711" max="8712" width="9.28515625" customWidth="1"/>
-    <col min="8961" max="8961" width="6.28515625" customWidth="1"/>
-    <col min="8962" max="8962" width="3.140625" customWidth="1"/>
-    <col min="8963" max="8963" width="23.85546875" customWidth="1"/>
-    <col min="8964" max="8964" width="6.140625" customWidth="1"/>
-    <col min="8965" max="8965" width="20.42578125" customWidth="1"/>
-    <col min="8966" max="8966" width="9.85546875" customWidth="1"/>
-    <col min="8967" max="8968" width="9.28515625" customWidth="1"/>
-    <col min="9217" max="9217" width="6.28515625" customWidth="1"/>
-    <col min="9218" max="9218" width="3.140625" customWidth="1"/>
-    <col min="9219" max="9219" width="23.85546875" customWidth="1"/>
-    <col min="9220" max="9220" width="6.140625" customWidth="1"/>
-    <col min="9221" max="9221" width="20.42578125" customWidth="1"/>
-    <col min="9222" max="9222" width="9.85546875" customWidth="1"/>
-    <col min="9223" max="9224" width="9.28515625" customWidth="1"/>
-    <col min="9473" max="9473" width="6.28515625" customWidth="1"/>
-    <col min="9474" max="9474" width="3.140625" customWidth="1"/>
-    <col min="9475" max="9475" width="23.85546875" customWidth="1"/>
-    <col min="9476" max="9476" width="6.140625" customWidth="1"/>
-    <col min="9477" max="9477" width="20.42578125" customWidth="1"/>
-    <col min="9478" max="9478" width="9.85546875" customWidth="1"/>
-    <col min="9479" max="9480" width="9.28515625" customWidth="1"/>
-    <col min="9729" max="9729" width="6.28515625" customWidth="1"/>
-    <col min="9730" max="9730" width="3.140625" customWidth="1"/>
-    <col min="9731" max="9731" width="23.85546875" customWidth="1"/>
-    <col min="9732" max="9732" width="6.140625" customWidth="1"/>
-    <col min="9733" max="9733" width="20.42578125" customWidth="1"/>
-    <col min="9734" max="9734" width="9.85546875" customWidth="1"/>
-    <col min="9735" max="9736" width="9.28515625" customWidth="1"/>
-    <col min="9985" max="9985" width="6.28515625" customWidth="1"/>
-    <col min="9986" max="9986" width="3.140625" customWidth="1"/>
-    <col min="9987" max="9987" width="23.85546875" customWidth="1"/>
-    <col min="9988" max="9988" width="6.140625" customWidth="1"/>
-    <col min="9989" max="9989" width="20.42578125" customWidth="1"/>
-    <col min="9990" max="9990" width="9.85546875" customWidth="1"/>
-    <col min="9991" max="9992" width="9.28515625" customWidth="1"/>
-    <col min="10241" max="10241" width="6.28515625" customWidth="1"/>
-    <col min="10242" max="10242" width="3.140625" customWidth="1"/>
-    <col min="10243" max="10243" width="23.85546875" customWidth="1"/>
-    <col min="10244" max="10244" width="6.140625" customWidth="1"/>
-    <col min="10245" max="10245" width="20.42578125" customWidth="1"/>
-    <col min="10246" max="10246" width="9.85546875" customWidth="1"/>
-    <col min="10247" max="10248" width="9.28515625" customWidth="1"/>
-    <col min="10497" max="10497" width="6.28515625" customWidth="1"/>
-    <col min="10498" max="10498" width="3.140625" customWidth="1"/>
-    <col min="10499" max="10499" width="23.85546875" customWidth="1"/>
-    <col min="10500" max="10500" width="6.140625" customWidth="1"/>
-    <col min="10501" max="10501" width="20.42578125" customWidth="1"/>
-    <col min="10502" max="10502" width="9.85546875" customWidth="1"/>
-    <col min="10503" max="10504" width="9.28515625" customWidth="1"/>
-    <col min="10753" max="10753" width="6.28515625" customWidth="1"/>
-    <col min="10754" max="10754" width="3.140625" customWidth="1"/>
-    <col min="10755" max="10755" width="23.85546875" customWidth="1"/>
-    <col min="10756" max="10756" width="6.140625" customWidth="1"/>
-    <col min="10757" max="10757" width="20.42578125" customWidth="1"/>
-    <col min="10758" max="10758" width="9.85546875" customWidth="1"/>
-    <col min="10759" max="10760" width="9.28515625" customWidth="1"/>
-    <col min="11009" max="11009" width="6.28515625" customWidth="1"/>
-    <col min="11010" max="11010" width="3.140625" customWidth="1"/>
-    <col min="11011" max="11011" width="23.85546875" customWidth="1"/>
-    <col min="11012" max="11012" width="6.140625" customWidth="1"/>
-    <col min="11013" max="11013" width="20.42578125" customWidth="1"/>
-    <col min="11014" max="11014" width="9.85546875" customWidth="1"/>
-    <col min="11015" max="11016" width="9.28515625" customWidth="1"/>
-    <col min="11265" max="11265" width="6.28515625" customWidth="1"/>
-    <col min="11266" max="11266" width="3.140625" customWidth="1"/>
-    <col min="11267" max="11267" width="23.85546875" customWidth="1"/>
-    <col min="11268" max="11268" width="6.140625" customWidth="1"/>
-    <col min="11269" max="11269" width="20.42578125" customWidth="1"/>
-    <col min="11270" max="11270" width="9.85546875" customWidth="1"/>
-    <col min="11271" max="11272" width="9.28515625" customWidth="1"/>
-    <col min="11521" max="11521" width="6.28515625" customWidth="1"/>
-    <col min="11522" max="11522" width="3.140625" customWidth="1"/>
-    <col min="11523" max="11523" width="23.85546875" customWidth="1"/>
-    <col min="11524" max="11524" width="6.140625" customWidth="1"/>
-    <col min="11525" max="11525" width="20.42578125" customWidth="1"/>
-    <col min="11526" max="11526" width="9.85546875" customWidth="1"/>
-    <col min="11527" max="11528" width="9.28515625" customWidth="1"/>
-    <col min="11777" max="11777" width="6.28515625" customWidth="1"/>
-    <col min="11778" max="11778" width="3.140625" customWidth="1"/>
-    <col min="11779" max="11779" width="23.85546875" customWidth="1"/>
-    <col min="11780" max="11780" width="6.140625" customWidth="1"/>
-    <col min="11781" max="11781" width="20.42578125" customWidth="1"/>
-    <col min="11782" max="11782" width="9.85546875" customWidth="1"/>
-    <col min="11783" max="11784" width="9.28515625" customWidth="1"/>
-    <col min="12033" max="12033" width="6.28515625" customWidth="1"/>
-    <col min="12034" max="12034" width="3.140625" customWidth="1"/>
-    <col min="12035" max="12035" width="23.85546875" customWidth="1"/>
-    <col min="12036" max="12036" width="6.140625" customWidth="1"/>
-    <col min="12037" max="12037" width="20.42578125" customWidth="1"/>
-    <col min="12038" max="12038" width="9.85546875" customWidth="1"/>
-    <col min="12039" max="12040" width="9.28515625" customWidth="1"/>
-    <col min="12289" max="12289" width="6.28515625" customWidth="1"/>
-    <col min="12290" max="12290" width="3.140625" customWidth="1"/>
-    <col min="12291" max="12291" width="23.85546875" customWidth="1"/>
-    <col min="12292" max="12292" width="6.140625" customWidth="1"/>
-    <col min="12293" max="12293" width="20.42578125" customWidth="1"/>
-    <col min="12294" max="12294" width="9.85546875" customWidth="1"/>
-    <col min="12295" max="12296" width="9.28515625" customWidth="1"/>
-    <col min="12545" max="12545" width="6.28515625" customWidth="1"/>
-    <col min="12546" max="12546" width="3.140625" customWidth="1"/>
-    <col min="12547" max="12547" width="23.85546875" customWidth="1"/>
-    <col min="12548" max="12548" width="6.140625" customWidth="1"/>
-    <col min="12549" max="12549" width="20.42578125" customWidth="1"/>
-    <col min="12550" max="12550" width="9.85546875" customWidth="1"/>
-    <col min="12551" max="12552" width="9.28515625" customWidth="1"/>
-    <col min="12801" max="12801" width="6.28515625" customWidth="1"/>
-    <col min="12802" max="12802" width="3.140625" customWidth="1"/>
-    <col min="12803" max="12803" width="23.85546875" customWidth="1"/>
-    <col min="12804" max="12804" width="6.140625" customWidth="1"/>
-    <col min="12805" max="12805" width="20.42578125" customWidth="1"/>
-    <col min="12806" max="12806" width="9.85546875" customWidth="1"/>
-    <col min="12807" max="12808" width="9.28515625" customWidth="1"/>
-    <col min="13057" max="13057" width="6.28515625" customWidth="1"/>
-    <col min="13058" max="13058" width="3.140625" customWidth="1"/>
-    <col min="13059" max="13059" width="23.85546875" customWidth="1"/>
-    <col min="13060" max="13060" width="6.140625" customWidth="1"/>
-    <col min="13061" max="13061" width="20.42578125" customWidth="1"/>
-    <col min="13062" max="13062" width="9.85546875" customWidth="1"/>
-    <col min="13063" max="13064" width="9.28515625" customWidth="1"/>
-    <col min="13313" max="13313" width="6.28515625" customWidth="1"/>
-    <col min="13314" max="13314" width="3.140625" customWidth="1"/>
-    <col min="13315" max="13315" width="23.85546875" customWidth="1"/>
-    <col min="13316" max="13316" width="6.140625" customWidth="1"/>
-    <col min="13317" max="13317" width="20.42578125" customWidth="1"/>
-    <col min="13318" max="13318" width="9.85546875" customWidth="1"/>
-    <col min="13319" max="13320" width="9.28515625" customWidth="1"/>
-    <col min="13569" max="13569" width="6.28515625" customWidth="1"/>
-    <col min="13570" max="13570" width="3.140625" customWidth="1"/>
-    <col min="13571" max="13571" width="23.85546875" customWidth="1"/>
-    <col min="13572" max="13572" width="6.140625" customWidth="1"/>
-    <col min="13573" max="13573" width="20.42578125" customWidth="1"/>
-    <col min="13574" max="13574" width="9.85546875" customWidth="1"/>
-    <col min="13575" max="13576" width="9.28515625" customWidth="1"/>
-    <col min="13825" max="13825" width="6.28515625" customWidth="1"/>
-    <col min="13826" max="13826" width="3.140625" customWidth="1"/>
-    <col min="13827" max="13827" width="23.85546875" customWidth="1"/>
-    <col min="13828" max="13828" width="6.140625" customWidth="1"/>
-    <col min="13829" max="13829" width="20.42578125" customWidth="1"/>
-    <col min="13830" max="13830" width="9.85546875" customWidth="1"/>
-    <col min="13831" max="13832" width="9.28515625" customWidth="1"/>
-    <col min="14081" max="14081" width="6.28515625" customWidth="1"/>
-    <col min="14082" max="14082" width="3.140625" customWidth="1"/>
-    <col min="14083" max="14083" width="23.85546875" customWidth="1"/>
-    <col min="14084" max="14084" width="6.140625" customWidth="1"/>
-    <col min="14085" max="14085" width="20.42578125" customWidth="1"/>
-    <col min="14086" max="14086" width="9.85546875" customWidth="1"/>
-    <col min="14087" max="14088" width="9.28515625" customWidth="1"/>
-    <col min="14337" max="14337" width="6.28515625" customWidth="1"/>
-    <col min="14338" max="14338" width="3.140625" customWidth="1"/>
-    <col min="14339" max="14339" width="23.85546875" customWidth="1"/>
-    <col min="14340" max="14340" width="6.140625" customWidth="1"/>
-    <col min="14341" max="14341" width="20.42578125" customWidth="1"/>
-    <col min="14342" max="14342" width="9.85546875" customWidth="1"/>
-    <col min="14343" max="14344" width="9.28515625" customWidth="1"/>
-    <col min="14593" max="14593" width="6.28515625" customWidth="1"/>
-    <col min="14594" max="14594" width="3.140625" customWidth="1"/>
-    <col min="14595" max="14595" width="23.85546875" customWidth="1"/>
-    <col min="14596" max="14596" width="6.140625" customWidth="1"/>
-    <col min="14597" max="14597" width="20.42578125" customWidth="1"/>
-    <col min="14598" max="14598" width="9.85546875" customWidth="1"/>
-    <col min="14599" max="14600" width="9.28515625" customWidth="1"/>
-    <col min="14849" max="14849" width="6.28515625" customWidth="1"/>
-    <col min="14850" max="14850" width="3.140625" customWidth="1"/>
-    <col min="14851" max="14851" width="23.85546875" customWidth="1"/>
-    <col min="14852" max="14852" width="6.140625" customWidth="1"/>
-    <col min="14853" max="14853" width="20.42578125" customWidth="1"/>
-    <col min="14854" max="14854" width="9.85546875" customWidth="1"/>
-    <col min="14855" max="14856" width="9.28515625" customWidth="1"/>
-    <col min="15105" max="15105" width="6.28515625" customWidth="1"/>
-    <col min="15106" max="15106" width="3.140625" customWidth="1"/>
-    <col min="15107" max="15107" width="23.85546875" customWidth="1"/>
-    <col min="15108" max="15108" width="6.140625" customWidth="1"/>
-    <col min="15109" max="15109" width="20.42578125" customWidth="1"/>
-    <col min="15110" max="15110" width="9.85546875" customWidth="1"/>
-    <col min="15111" max="15112" width="9.28515625" customWidth="1"/>
-    <col min="15361" max="15361" width="6.28515625" customWidth="1"/>
-    <col min="15362" max="15362" width="3.140625" customWidth="1"/>
-    <col min="15363" max="15363" width="23.85546875" customWidth="1"/>
-    <col min="15364" max="15364" width="6.140625" customWidth="1"/>
-    <col min="15365" max="15365" width="20.42578125" customWidth="1"/>
-    <col min="15366" max="15366" width="9.85546875" customWidth="1"/>
-    <col min="15367" max="15368" width="9.28515625" customWidth="1"/>
-    <col min="15617" max="15617" width="6.28515625" customWidth="1"/>
-    <col min="15618" max="15618" width="3.140625" customWidth="1"/>
-    <col min="15619" max="15619" width="23.85546875" customWidth="1"/>
-    <col min="15620" max="15620" width="6.140625" customWidth="1"/>
-    <col min="15621" max="15621" width="20.42578125" customWidth="1"/>
-    <col min="15622" max="15622" width="9.85546875" customWidth="1"/>
-    <col min="15623" max="15624" width="9.28515625" customWidth="1"/>
-    <col min="15873" max="15873" width="6.28515625" customWidth="1"/>
-    <col min="15874" max="15874" width="3.140625" customWidth="1"/>
-    <col min="15875" max="15875" width="23.85546875" customWidth="1"/>
-    <col min="15876" max="15876" width="6.140625" customWidth="1"/>
-    <col min="15877" max="15877" width="20.42578125" customWidth="1"/>
-    <col min="15878" max="15878" width="9.85546875" customWidth="1"/>
-    <col min="15879" max="15880" width="9.28515625" customWidth="1"/>
-    <col min="16129" max="16129" width="6.28515625" customWidth="1"/>
-    <col min="16130" max="16130" width="3.140625" customWidth="1"/>
-    <col min="16131" max="16131" width="23.85546875" customWidth="1"/>
-    <col min="16132" max="16132" width="6.140625" customWidth="1"/>
-    <col min="16133" max="16133" width="20.42578125" customWidth="1"/>
-    <col min="16134" max="16134" width="9.85546875" customWidth="1"/>
-    <col min="16135" max="16136" width="9.28515625" customWidth="1"/>
+    <col min="1" max="1" width="6.33203125" customWidth="1"/>
+    <col min="2" max="2" width="3.109375" customWidth="1"/>
+    <col min="3" max="3" width="23.88671875" customWidth="1"/>
+    <col min="4" max="4" width="6.109375" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" customWidth="1"/>
+    <col min="6" max="6" width="9.88671875" customWidth="1"/>
+    <col min="7" max="8" width="9.33203125" customWidth="1"/>
+    <col min="257" max="257" width="6.33203125" customWidth="1"/>
+    <col min="258" max="258" width="3.109375" customWidth="1"/>
+    <col min="259" max="259" width="23.88671875" customWidth="1"/>
+    <col min="260" max="260" width="6.109375" customWidth="1"/>
+    <col min="261" max="261" width="20.44140625" customWidth="1"/>
+    <col min="262" max="262" width="9.88671875" customWidth="1"/>
+    <col min="263" max="264" width="9.33203125" customWidth="1"/>
+    <col min="513" max="513" width="6.33203125" customWidth="1"/>
+    <col min="514" max="514" width="3.109375" customWidth="1"/>
+    <col min="515" max="515" width="23.88671875" customWidth="1"/>
+    <col min="516" max="516" width="6.109375" customWidth="1"/>
+    <col min="517" max="517" width="20.44140625" customWidth="1"/>
+    <col min="518" max="518" width="9.88671875" customWidth="1"/>
+    <col min="519" max="520" width="9.33203125" customWidth="1"/>
+    <col min="769" max="769" width="6.33203125" customWidth="1"/>
+    <col min="770" max="770" width="3.109375" customWidth="1"/>
+    <col min="771" max="771" width="23.88671875" customWidth="1"/>
+    <col min="772" max="772" width="6.109375" customWidth="1"/>
+    <col min="773" max="773" width="20.44140625" customWidth="1"/>
+    <col min="774" max="774" width="9.88671875" customWidth="1"/>
+    <col min="775" max="776" width="9.33203125" customWidth="1"/>
+    <col min="1025" max="1025" width="6.33203125" customWidth="1"/>
+    <col min="1026" max="1026" width="3.109375" customWidth="1"/>
+    <col min="1027" max="1027" width="23.88671875" customWidth="1"/>
+    <col min="1028" max="1028" width="6.109375" customWidth="1"/>
+    <col min="1029" max="1029" width="20.44140625" customWidth="1"/>
+    <col min="1030" max="1030" width="9.88671875" customWidth="1"/>
+    <col min="1031" max="1032" width="9.33203125" customWidth="1"/>
+    <col min="1281" max="1281" width="6.33203125" customWidth="1"/>
+    <col min="1282" max="1282" width="3.109375" customWidth="1"/>
+    <col min="1283" max="1283" width="23.88671875" customWidth="1"/>
+    <col min="1284" max="1284" width="6.109375" customWidth="1"/>
+    <col min="1285" max="1285" width="20.44140625" customWidth="1"/>
+    <col min="1286" max="1286" width="9.88671875" customWidth="1"/>
+    <col min="1287" max="1288" width="9.33203125" customWidth="1"/>
+    <col min="1537" max="1537" width="6.33203125" customWidth="1"/>
+    <col min="1538" max="1538" width="3.109375" customWidth="1"/>
+    <col min="1539" max="1539" width="23.88671875" customWidth="1"/>
+    <col min="1540" max="1540" width="6.109375" customWidth="1"/>
+    <col min="1541" max="1541" width="20.44140625" customWidth="1"/>
+    <col min="1542" max="1542" width="9.88671875" customWidth="1"/>
+    <col min="1543" max="1544" width="9.33203125" customWidth="1"/>
+    <col min="1793" max="1793" width="6.33203125" customWidth="1"/>
+    <col min="1794" max="1794" width="3.109375" customWidth="1"/>
+    <col min="1795" max="1795" width="23.88671875" customWidth="1"/>
+    <col min="1796" max="1796" width="6.109375" customWidth="1"/>
+    <col min="1797" max="1797" width="20.44140625" customWidth="1"/>
+    <col min="1798" max="1798" width="9.88671875" customWidth="1"/>
+    <col min="1799" max="1800" width="9.33203125" customWidth="1"/>
+    <col min="2049" max="2049" width="6.33203125" customWidth="1"/>
+    <col min="2050" max="2050" width="3.109375" customWidth="1"/>
+    <col min="2051" max="2051" width="23.88671875" customWidth="1"/>
+    <col min="2052" max="2052" width="6.109375" customWidth="1"/>
+    <col min="2053" max="2053" width="20.44140625" customWidth="1"/>
+    <col min="2054" max="2054" width="9.88671875" customWidth="1"/>
+    <col min="2055" max="2056" width="9.33203125" customWidth="1"/>
+    <col min="2305" max="2305" width="6.33203125" customWidth="1"/>
+    <col min="2306" max="2306" width="3.109375" customWidth="1"/>
+    <col min="2307" max="2307" width="23.88671875" customWidth="1"/>
+    <col min="2308" max="2308" width="6.109375" customWidth="1"/>
+    <col min="2309" max="2309" width="20.44140625" customWidth="1"/>
+    <col min="2310" max="2310" width="9.88671875" customWidth="1"/>
+    <col min="2311" max="2312" width="9.33203125" customWidth="1"/>
+    <col min="2561" max="2561" width="6.33203125" customWidth="1"/>
+    <col min="2562" max="2562" width="3.109375" customWidth="1"/>
+    <col min="2563" max="2563" width="23.88671875" customWidth="1"/>
+    <col min="2564" max="2564" width="6.109375" customWidth="1"/>
+    <col min="2565" max="2565" width="20.44140625" customWidth="1"/>
+    <col min="2566" max="2566" width="9.88671875" customWidth="1"/>
+    <col min="2567" max="2568" width="9.33203125" customWidth="1"/>
+    <col min="2817" max="2817" width="6.33203125" customWidth="1"/>
+    <col min="2818" max="2818" width="3.109375" customWidth="1"/>
+    <col min="2819" max="2819" width="23.88671875" customWidth="1"/>
+    <col min="2820" max="2820" width="6.109375" customWidth="1"/>
+    <col min="2821" max="2821" width="20.44140625" customWidth="1"/>
+    <col min="2822" max="2822" width="9.88671875" customWidth="1"/>
+    <col min="2823" max="2824" width="9.33203125" customWidth="1"/>
+    <col min="3073" max="3073" width="6.33203125" customWidth="1"/>
+    <col min="3074" max="3074" width="3.109375" customWidth="1"/>
+    <col min="3075" max="3075" width="23.88671875" customWidth="1"/>
+    <col min="3076" max="3076" width="6.109375" customWidth="1"/>
+    <col min="3077" max="3077" width="20.44140625" customWidth="1"/>
+    <col min="3078" max="3078" width="9.88671875" customWidth="1"/>
+    <col min="3079" max="3080" width="9.33203125" customWidth="1"/>
+    <col min="3329" max="3329" width="6.33203125" customWidth="1"/>
+    <col min="3330" max="3330" width="3.109375" customWidth="1"/>
+    <col min="3331" max="3331" width="23.88671875" customWidth="1"/>
+    <col min="3332" max="3332" width="6.109375" customWidth="1"/>
+    <col min="3333" max="3333" width="20.44140625" customWidth="1"/>
+    <col min="3334" max="3334" width="9.88671875" customWidth="1"/>
+    <col min="3335" max="3336" width="9.33203125" customWidth="1"/>
+    <col min="3585" max="3585" width="6.33203125" customWidth="1"/>
+    <col min="3586" max="3586" width="3.109375" customWidth="1"/>
+    <col min="3587" max="3587" width="23.88671875" customWidth="1"/>
+    <col min="3588" max="3588" width="6.109375" customWidth="1"/>
+    <col min="3589" max="3589" width="20.44140625" customWidth="1"/>
+    <col min="3590" max="3590" width="9.88671875" customWidth="1"/>
+    <col min="3591" max="3592" width="9.33203125" customWidth="1"/>
+    <col min="3841" max="3841" width="6.33203125" customWidth="1"/>
+    <col min="3842" max="3842" width="3.109375" customWidth="1"/>
+    <col min="3843" max="3843" width="23.88671875" customWidth="1"/>
+    <col min="3844" max="3844" width="6.109375" customWidth="1"/>
+    <col min="3845" max="3845" width="20.44140625" customWidth="1"/>
+    <col min="3846" max="3846" width="9.88671875" customWidth="1"/>
+    <col min="3847" max="3848" width="9.33203125" customWidth="1"/>
+    <col min="4097" max="4097" width="6.33203125" customWidth="1"/>
+    <col min="4098" max="4098" width="3.109375" customWidth="1"/>
+    <col min="4099" max="4099" width="23.88671875" customWidth="1"/>
+    <col min="4100" max="4100" width="6.109375" customWidth="1"/>
+    <col min="4101" max="4101" width="20.44140625" customWidth="1"/>
+    <col min="4102" max="4102" width="9.88671875" customWidth="1"/>
+    <col min="4103" max="4104" width="9.33203125" customWidth="1"/>
+    <col min="4353" max="4353" width="6.33203125" customWidth="1"/>
+    <col min="4354" max="4354" width="3.109375" customWidth="1"/>
+    <col min="4355" max="4355" width="23.88671875" customWidth="1"/>
+    <col min="4356" max="4356" width="6.109375" customWidth="1"/>
+    <col min="4357" max="4357" width="20.44140625" customWidth="1"/>
+    <col min="4358" max="4358" width="9.88671875" customWidth="1"/>
+    <col min="4359" max="4360" width="9.33203125" customWidth="1"/>
+    <col min="4609" max="4609" width="6.33203125" customWidth="1"/>
+    <col min="4610" max="4610" width="3.109375" customWidth="1"/>
+    <col min="4611" max="4611" width="23.88671875" customWidth="1"/>
+    <col min="4612" max="4612" width="6.109375" customWidth="1"/>
+    <col min="4613" max="4613" width="20.44140625" customWidth="1"/>
+    <col min="4614" max="4614" width="9.88671875" customWidth="1"/>
+    <col min="4615" max="4616" width="9.33203125" customWidth="1"/>
+    <col min="4865" max="4865" width="6.33203125" customWidth="1"/>
+    <col min="4866" max="4866" width="3.109375" customWidth="1"/>
+    <col min="4867" max="4867" width="23.88671875" customWidth="1"/>
+    <col min="4868" max="4868" width="6.109375" customWidth="1"/>
+    <col min="4869" max="4869" width="20.44140625" customWidth="1"/>
+    <col min="4870" max="4870" width="9.88671875" customWidth="1"/>
+    <col min="4871" max="4872" width="9.33203125" customWidth="1"/>
+    <col min="5121" max="5121" width="6.33203125" customWidth="1"/>
+    <col min="5122" max="5122" width="3.109375" customWidth="1"/>
+    <col min="5123" max="5123" width="23.88671875" customWidth="1"/>
+    <col min="5124" max="5124" width="6.109375" customWidth="1"/>
+    <col min="5125" max="5125" width="20.44140625" customWidth="1"/>
+    <col min="5126" max="5126" width="9.88671875" customWidth="1"/>
+    <col min="5127" max="5128" width="9.33203125" customWidth="1"/>
+    <col min="5377" max="5377" width="6.33203125" customWidth="1"/>
+    <col min="5378" max="5378" width="3.109375" customWidth="1"/>
+    <col min="5379" max="5379" width="23.88671875" customWidth="1"/>
+    <col min="5380" max="5380" width="6.109375" customWidth="1"/>
+    <col min="5381" max="5381" width="20.44140625" customWidth="1"/>
+    <col min="5382" max="5382" width="9.88671875" customWidth="1"/>
+    <col min="5383" max="5384" width="9.33203125" customWidth="1"/>
+    <col min="5633" max="5633" width="6.33203125" customWidth="1"/>
+    <col min="5634" max="5634" width="3.109375" customWidth="1"/>
+    <col min="5635" max="5635" width="23.88671875" customWidth="1"/>
+    <col min="5636" max="5636" width="6.109375" customWidth="1"/>
+    <col min="5637" max="5637" width="20.44140625" customWidth="1"/>
+    <col min="5638" max="5638" width="9.88671875" customWidth="1"/>
+    <col min="5639" max="5640" width="9.33203125" customWidth="1"/>
+    <col min="5889" max="5889" width="6.33203125" customWidth="1"/>
+    <col min="5890" max="5890" width="3.109375" customWidth="1"/>
+    <col min="5891" max="5891" width="23.88671875" customWidth="1"/>
+    <col min="5892" max="5892" width="6.109375" customWidth="1"/>
+    <col min="5893" max="5893" width="20.44140625" customWidth="1"/>
+    <col min="5894" max="5894" width="9.88671875" customWidth="1"/>
+    <col min="5895" max="5896" width="9.33203125" customWidth="1"/>
+    <col min="6145" max="6145" width="6.33203125" customWidth="1"/>
+    <col min="6146" max="6146" width="3.109375" customWidth="1"/>
+    <col min="6147" max="6147" width="23.88671875" customWidth="1"/>
+    <col min="6148" max="6148" width="6.109375" customWidth="1"/>
+    <col min="6149" max="6149" width="20.44140625" customWidth="1"/>
+    <col min="6150" max="6150" width="9.88671875" customWidth="1"/>
+    <col min="6151" max="6152" width="9.33203125" customWidth="1"/>
+    <col min="6401" max="6401" width="6.33203125" customWidth="1"/>
+    <col min="6402" max="6402" width="3.109375" customWidth="1"/>
+    <col min="6403" max="6403" width="23.88671875" customWidth="1"/>
+    <col min="6404" max="6404" width="6.109375" customWidth="1"/>
+    <col min="6405" max="6405" width="20.44140625" customWidth="1"/>
+    <col min="6406" max="6406" width="9.88671875" customWidth="1"/>
+    <col min="6407" max="6408" width="9.33203125" customWidth="1"/>
+    <col min="6657" max="6657" width="6.33203125" customWidth="1"/>
+    <col min="6658" max="6658" width="3.109375" customWidth="1"/>
+    <col min="6659" max="6659" width="23.88671875" customWidth="1"/>
+    <col min="6660" max="6660" width="6.109375" customWidth="1"/>
+    <col min="6661" max="6661" width="20.44140625" customWidth="1"/>
+    <col min="6662" max="6662" width="9.88671875" customWidth="1"/>
+    <col min="6663" max="6664" width="9.33203125" customWidth="1"/>
+    <col min="6913" max="6913" width="6.33203125" customWidth="1"/>
+    <col min="6914" max="6914" width="3.109375" customWidth="1"/>
+    <col min="6915" max="6915" width="23.88671875" customWidth="1"/>
+    <col min="6916" max="6916" width="6.109375" customWidth="1"/>
+    <col min="6917" max="6917" width="20.44140625" customWidth="1"/>
+    <col min="6918" max="6918" width="9.88671875" customWidth="1"/>
+    <col min="6919" max="6920" width="9.33203125" customWidth="1"/>
+    <col min="7169" max="7169" width="6.33203125" customWidth="1"/>
+    <col min="7170" max="7170" width="3.109375" customWidth="1"/>
+    <col min="7171" max="7171" width="23.88671875" customWidth="1"/>
+    <col min="7172" max="7172" width="6.109375" customWidth="1"/>
+    <col min="7173" max="7173" width="20.44140625" customWidth="1"/>
+    <col min="7174" max="7174" width="9.88671875" customWidth="1"/>
+    <col min="7175" max="7176" width="9.33203125" customWidth="1"/>
+    <col min="7425" max="7425" width="6.33203125" customWidth="1"/>
+    <col min="7426" max="7426" width="3.109375" customWidth="1"/>
+    <col min="7427" max="7427" width="23.88671875" customWidth="1"/>
+    <col min="7428" max="7428" width="6.109375" customWidth="1"/>
+    <col min="7429" max="7429" width="20.44140625" customWidth="1"/>
+    <col min="7430" max="7430" width="9.88671875" customWidth="1"/>
+    <col min="7431" max="7432" width="9.33203125" customWidth="1"/>
+    <col min="7681" max="7681" width="6.33203125" customWidth="1"/>
+    <col min="7682" max="7682" width="3.109375" customWidth="1"/>
+    <col min="7683" max="7683" width="23.88671875" customWidth="1"/>
+    <col min="7684" max="7684" width="6.109375" customWidth="1"/>
+    <col min="7685" max="7685" width="20.44140625" customWidth="1"/>
+    <col min="7686" max="7686" width="9.88671875" customWidth="1"/>
+    <col min="7687" max="7688" width="9.33203125" customWidth="1"/>
+    <col min="7937" max="7937" width="6.33203125" customWidth="1"/>
+    <col min="7938" max="7938" width="3.109375" customWidth="1"/>
+    <col min="7939" max="7939" width="23.88671875" customWidth="1"/>
+    <col min="7940" max="7940" width="6.109375" customWidth="1"/>
+    <col min="7941" max="7941" width="20.44140625" customWidth="1"/>
+    <col min="7942" max="7942" width="9.88671875" customWidth="1"/>
+    <col min="7943" max="7944" width="9.33203125" customWidth="1"/>
+    <col min="8193" max="8193" width="6.33203125" customWidth="1"/>
+    <col min="8194" max="8194" width="3.109375" customWidth="1"/>
+    <col min="8195" max="8195" width="23.88671875" customWidth="1"/>
+    <col min="8196" max="8196" width="6.109375" customWidth="1"/>
+    <col min="8197" max="8197" width="20.44140625" customWidth="1"/>
+    <col min="8198" max="8198" width="9.88671875" customWidth="1"/>
+    <col min="8199" max="8200" width="9.33203125" customWidth="1"/>
+    <col min="8449" max="8449" width="6.33203125" customWidth="1"/>
+    <col min="8450" max="8450" width="3.109375" customWidth="1"/>
+    <col min="8451" max="8451" width="23.88671875" customWidth="1"/>
+    <col min="8452" max="8452" width="6.109375" customWidth="1"/>
+    <col min="8453" max="8453" width="20.44140625" customWidth="1"/>
+    <col min="8454" max="8454" width="9.88671875" customWidth="1"/>
+    <col min="8455" max="8456" width="9.33203125" customWidth="1"/>
+    <col min="8705" max="8705" width="6.33203125" customWidth="1"/>
+    <col min="8706" max="8706" width="3.109375" customWidth="1"/>
+    <col min="8707" max="8707" width="23.88671875" customWidth="1"/>
+    <col min="8708" max="8708" width="6.109375" customWidth="1"/>
+    <col min="8709" max="8709" width="20.44140625" customWidth="1"/>
+    <col min="8710" max="8710" width="9.88671875" customWidth="1"/>
+    <col min="8711" max="8712" width="9.33203125" customWidth="1"/>
+    <col min="8961" max="8961" width="6.33203125" customWidth="1"/>
+    <col min="8962" max="8962" width="3.109375" customWidth="1"/>
+    <col min="8963" max="8963" width="23.88671875" customWidth="1"/>
+    <col min="8964" max="8964" width="6.109375" customWidth="1"/>
+    <col min="8965" max="8965" width="20.44140625" customWidth="1"/>
+    <col min="8966" max="8966" width="9.88671875" customWidth="1"/>
+    <col min="8967" max="8968" width="9.33203125" customWidth="1"/>
+    <col min="9217" max="9217" width="6.33203125" customWidth="1"/>
+    <col min="9218" max="9218" width="3.109375" customWidth="1"/>
+    <col min="9219" max="9219" width="23.88671875" customWidth="1"/>
+    <col min="9220" max="9220" width="6.109375" customWidth="1"/>
+    <col min="9221" max="9221" width="20.44140625" customWidth="1"/>
+    <col min="9222" max="9222" width="9.88671875" customWidth="1"/>
+    <col min="9223" max="9224" width="9.33203125" customWidth="1"/>
+    <col min="9473" max="9473" width="6.33203125" customWidth="1"/>
+    <col min="9474" max="9474" width="3.109375" customWidth="1"/>
+    <col min="9475" max="9475" width="23.88671875" customWidth="1"/>
+    <col min="9476" max="9476" width="6.109375" customWidth="1"/>
+    <col min="9477" max="9477" width="20.44140625" customWidth="1"/>
+    <col min="9478" max="9478" width="9.88671875" customWidth="1"/>
+    <col min="9479" max="9480" width="9.33203125" customWidth="1"/>
+    <col min="9729" max="9729" width="6.33203125" customWidth="1"/>
+    <col min="9730" max="9730" width="3.109375" customWidth="1"/>
+    <col min="9731" max="9731" width="23.88671875" customWidth="1"/>
+    <col min="9732" max="9732" width="6.109375" customWidth="1"/>
+    <col min="9733" max="9733" width="20.44140625" customWidth="1"/>
+    <col min="9734" max="9734" width="9.88671875" customWidth="1"/>
+    <col min="9735" max="9736" width="9.33203125" customWidth="1"/>
+    <col min="9985" max="9985" width="6.33203125" customWidth="1"/>
+    <col min="9986" max="9986" width="3.109375" customWidth="1"/>
+    <col min="9987" max="9987" width="23.88671875" customWidth="1"/>
+    <col min="9988" max="9988" width="6.109375" customWidth="1"/>
+    <col min="9989" max="9989" width="20.44140625" customWidth="1"/>
+    <col min="9990" max="9990" width="9.88671875" customWidth="1"/>
+    <col min="9991" max="9992" width="9.33203125" customWidth="1"/>
+    <col min="10241" max="10241" width="6.33203125" customWidth="1"/>
+    <col min="10242" max="10242" width="3.109375" customWidth="1"/>
+    <col min="10243" max="10243" width="23.88671875" customWidth="1"/>
+    <col min="10244" max="10244" width="6.109375" customWidth="1"/>
+    <col min="10245" max="10245" width="20.44140625" customWidth="1"/>
+    <col min="10246" max="10246" width="9.88671875" customWidth="1"/>
+    <col min="10247" max="10248" width="9.33203125" customWidth="1"/>
+    <col min="10497" max="10497" width="6.33203125" customWidth="1"/>
+    <col min="10498" max="10498" width="3.109375" customWidth="1"/>
+    <col min="10499" max="10499" width="23.88671875" customWidth="1"/>
+    <col min="10500" max="10500" width="6.109375" customWidth="1"/>
+    <col min="10501" max="10501" width="20.44140625" customWidth="1"/>
+    <col min="10502" max="10502" width="9.88671875" customWidth="1"/>
+    <col min="10503" max="10504" width="9.33203125" customWidth="1"/>
+    <col min="10753" max="10753" width="6.33203125" customWidth="1"/>
+    <col min="10754" max="10754" width="3.109375" customWidth="1"/>
+    <col min="10755" max="10755" width="23.88671875" customWidth="1"/>
+    <col min="10756" max="10756" width="6.109375" customWidth="1"/>
+    <col min="10757" max="10757" width="20.44140625" customWidth="1"/>
+    <col min="10758" max="10758" width="9.88671875" customWidth="1"/>
+    <col min="10759" max="10760" width="9.33203125" customWidth="1"/>
+    <col min="11009" max="11009" width="6.33203125" customWidth="1"/>
+    <col min="11010" max="11010" width="3.109375" customWidth="1"/>
+    <col min="11011" max="11011" width="23.88671875" customWidth="1"/>
+    <col min="11012" max="11012" width="6.109375" customWidth="1"/>
+    <col min="11013" max="11013" width="20.44140625" customWidth="1"/>
+    <col min="11014" max="11014" width="9.88671875" customWidth="1"/>
+    <col min="11015" max="11016" width="9.33203125" customWidth="1"/>
+    <col min="11265" max="11265" width="6.33203125" customWidth="1"/>
+    <col min="11266" max="11266" width="3.109375" customWidth="1"/>
+    <col min="11267" max="11267" width="23.88671875" customWidth="1"/>
+    <col min="11268" max="11268" width="6.109375" customWidth="1"/>
+    <col min="11269" max="11269" width="20.44140625" customWidth="1"/>
+    <col min="11270" max="11270" width="9.88671875" customWidth="1"/>
+    <col min="11271" max="11272" width="9.33203125" customWidth="1"/>
+    <col min="11521" max="11521" width="6.33203125" customWidth="1"/>
+    <col min="11522" max="11522" width="3.109375" customWidth="1"/>
+    <col min="11523" max="11523" width="23.88671875" customWidth="1"/>
+    <col min="11524" max="11524" width="6.109375" customWidth="1"/>
+    <col min="11525" max="11525" width="20.44140625" customWidth="1"/>
+    <col min="11526" max="11526" width="9.88671875" customWidth="1"/>
+    <col min="11527" max="11528" width="9.33203125" customWidth="1"/>
+    <col min="11777" max="11777" width="6.33203125" customWidth="1"/>
+    <col min="11778" max="11778" width="3.109375" customWidth="1"/>
+    <col min="11779" max="11779" width="23.88671875" customWidth="1"/>
+    <col min="11780" max="11780" width="6.109375" customWidth="1"/>
+    <col min="11781" max="11781" width="20.44140625" customWidth="1"/>
+    <col min="11782" max="11782" width="9.88671875" customWidth="1"/>
+    <col min="11783" max="11784" width="9.33203125" customWidth="1"/>
+    <col min="12033" max="12033" width="6.33203125" customWidth="1"/>
+    <col min="12034" max="12034" width="3.109375" customWidth="1"/>
+    <col min="12035" max="12035" width="23.88671875" customWidth="1"/>
+    <col min="12036" max="12036" width="6.109375" customWidth="1"/>
+    <col min="12037" max="12037" width="20.44140625" customWidth="1"/>
+    <col min="12038" max="12038" width="9.88671875" customWidth="1"/>
+    <col min="12039" max="12040" width="9.33203125" customWidth="1"/>
+    <col min="12289" max="12289" width="6.33203125" customWidth="1"/>
+    <col min="12290" max="12290" width="3.109375" customWidth="1"/>
+    <col min="12291" max="12291" width="23.88671875" customWidth="1"/>
+    <col min="12292" max="12292" width="6.109375" customWidth="1"/>
+    <col min="12293" max="12293" width="20.44140625" customWidth="1"/>
+    <col min="12294" max="12294" width="9.88671875" customWidth="1"/>
+    <col min="12295" max="12296" width="9.33203125" customWidth="1"/>
+    <col min="12545" max="12545" width="6.33203125" customWidth="1"/>
+    <col min="12546" max="12546" width="3.109375" customWidth="1"/>
+    <col min="12547" max="12547" width="23.88671875" customWidth="1"/>
+    <col min="12548" max="12548" width="6.109375" customWidth="1"/>
+    <col min="12549" max="12549" width="20.44140625" customWidth="1"/>
+    <col min="12550" max="12550" width="9.88671875" customWidth="1"/>
+    <col min="12551" max="12552" width="9.33203125" customWidth="1"/>
+    <col min="12801" max="12801" width="6.33203125" customWidth="1"/>
+    <col min="12802" max="12802" width="3.109375" customWidth="1"/>
+    <col min="12803" max="12803" width="23.88671875" customWidth="1"/>
+    <col min="12804" max="12804" width="6.109375" customWidth="1"/>
+    <col min="12805" max="12805" width="20.44140625" customWidth="1"/>
+    <col min="12806" max="12806" width="9.88671875" customWidth="1"/>
+    <col min="12807" max="12808" width="9.33203125" customWidth="1"/>
+    <col min="13057" max="13057" width="6.33203125" customWidth="1"/>
+    <col min="13058" max="13058" width="3.109375" customWidth="1"/>
+    <col min="13059" max="13059" width="23.88671875" customWidth="1"/>
+    <col min="13060" max="13060" width="6.109375" customWidth="1"/>
+    <col min="13061" max="13061" width="20.44140625" customWidth="1"/>
+    <col min="13062" max="13062" width="9.88671875" customWidth="1"/>
+    <col min="13063" max="13064" width="9.33203125" customWidth="1"/>
+    <col min="13313" max="13313" width="6.33203125" customWidth="1"/>
+    <col min="13314" max="13314" width="3.109375" customWidth="1"/>
+    <col min="13315" max="13315" width="23.88671875" customWidth="1"/>
+    <col min="13316" max="13316" width="6.109375" customWidth="1"/>
+    <col min="13317" max="13317" width="20.44140625" customWidth="1"/>
+    <col min="13318" max="13318" width="9.88671875" customWidth="1"/>
+    <col min="13319" max="13320" width="9.33203125" customWidth="1"/>
+    <col min="13569" max="13569" width="6.33203125" customWidth="1"/>
+    <col min="13570" max="13570" width="3.109375" customWidth="1"/>
+    <col min="13571" max="13571" width="23.88671875" customWidth="1"/>
+    <col min="13572" max="13572" width="6.109375" customWidth="1"/>
+    <col min="13573" max="13573" width="20.44140625" customWidth="1"/>
+    <col min="13574" max="13574" width="9.88671875" customWidth="1"/>
+    <col min="13575" max="13576" width="9.33203125" customWidth="1"/>
+    <col min="13825" max="13825" width="6.33203125" customWidth="1"/>
+    <col min="13826" max="13826" width="3.109375" customWidth="1"/>
+    <col min="13827" max="13827" width="23.88671875" customWidth="1"/>
+    <col min="13828" max="13828" width="6.109375" customWidth="1"/>
+    <col min="13829" max="13829" width="20.44140625" customWidth="1"/>
+    <col min="13830" max="13830" width="9.88671875" customWidth="1"/>
+    <col min="13831" max="13832" width="9.33203125" customWidth="1"/>
+    <col min="14081" max="14081" width="6.33203125" customWidth="1"/>
+    <col min="14082" max="14082" width="3.109375" customWidth="1"/>
+    <col min="14083" max="14083" width="23.88671875" customWidth="1"/>
+    <col min="14084" max="14084" width="6.109375" customWidth="1"/>
+    <col min="14085" max="14085" width="20.44140625" customWidth="1"/>
+    <col min="14086" max="14086" width="9.88671875" customWidth="1"/>
+    <col min="14087" max="14088" width="9.33203125" customWidth="1"/>
+    <col min="14337" max="14337" width="6.33203125" customWidth="1"/>
+    <col min="14338" max="14338" width="3.109375" customWidth="1"/>
+    <col min="14339" max="14339" width="23.88671875" customWidth="1"/>
+    <col min="14340" max="14340" width="6.109375" customWidth="1"/>
+    <col min="14341" max="14341" width="20.44140625" customWidth="1"/>
+    <col min="14342" max="14342" width="9.88671875" customWidth="1"/>
+    <col min="14343" max="14344" width="9.33203125" customWidth="1"/>
+    <col min="14593" max="14593" width="6.33203125" customWidth="1"/>
+    <col min="14594" max="14594" width="3.109375" customWidth="1"/>
+    <col min="14595" max="14595" width="23.88671875" customWidth="1"/>
+    <col min="14596" max="14596" width="6.109375" customWidth="1"/>
+    <col min="14597" max="14597" width="20.44140625" customWidth="1"/>
+    <col min="14598" max="14598" width="9.88671875" customWidth="1"/>
+    <col min="14599" max="14600" width="9.33203125" customWidth="1"/>
+    <col min="14849" max="14849" width="6.33203125" customWidth="1"/>
+    <col min="14850" max="14850" width="3.109375" customWidth="1"/>
+    <col min="14851" max="14851" width="23.88671875" customWidth="1"/>
+    <col min="14852" max="14852" width="6.109375" customWidth="1"/>
+    <col min="14853" max="14853" width="20.44140625" customWidth="1"/>
+    <col min="14854" max="14854" width="9.88671875" customWidth="1"/>
+    <col min="14855" max="14856" width="9.33203125" customWidth="1"/>
+    <col min="15105" max="15105" width="6.33203125" customWidth="1"/>
+    <col min="15106" max="15106" width="3.109375" customWidth="1"/>
+    <col min="15107" max="15107" width="23.88671875" customWidth="1"/>
+    <col min="15108" max="15108" width="6.109375" customWidth="1"/>
+    <col min="15109" max="15109" width="20.44140625" customWidth="1"/>
+    <col min="15110" max="15110" width="9.88671875" customWidth="1"/>
+    <col min="15111" max="15112" width="9.33203125" customWidth="1"/>
+    <col min="15361" max="15361" width="6.33203125" customWidth="1"/>
+    <col min="15362" max="15362" width="3.109375" customWidth="1"/>
+    <col min="15363" max="15363" width="23.88671875" customWidth="1"/>
+    <col min="15364" max="15364" width="6.109375" customWidth="1"/>
+    <col min="15365" max="15365" width="20.44140625" customWidth="1"/>
+    <col min="15366" max="15366" width="9.88671875" customWidth="1"/>
+    <col min="15367" max="15368" width="9.33203125" customWidth="1"/>
+    <col min="15617" max="15617" width="6.33203125" customWidth="1"/>
+    <col min="15618" max="15618" width="3.109375" customWidth="1"/>
+    <col min="15619" max="15619" width="23.88671875" customWidth="1"/>
+    <col min="15620" max="15620" width="6.109375" customWidth="1"/>
+    <col min="15621" max="15621" width="20.44140625" customWidth="1"/>
+    <col min="15622" max="15622" width="9.88671875" customWidth="1"/>
+    <col min="15623" max="15624" width="9.33203125" customWidth="1"/>
+    <col min="15873" max="15873" width="6.33203125" customWidth="1"/>
+    <col min="15874" max="15874" width="3.109375" customWidth="1"/>
+    <col min="15875" max="15875" width="23.88671875" customWidth="1"/>
+    <col min="15876" max="15876" width="6.109375" customWidth="1"/>
+    <col min="15877" max="15877" width="20.44140625" customWidth="1"/>
+    <col min="15878" max="15878" width="9.88671875" customWidth="1"/>
+    <col min="15879" max="15880" width="9.33203125" customWidth="1"/>
+    <col min="16129" max="16129" width="6.33203125" customWidth="1"/>
+    <col min="16130" max="16130" width="3.109375" customWidth="1"/>
+    <col min="16131" max="16131" width="23.88671875" customWidth="1"/>
+    <col min="16132" max="16132" width="6.109375" customWidth="1"/>
+    <col min="16133" max="16133" width="20.44140625" customWidth="1"/>
+    <col min="16134" max="16134" width="9.88671875" customWidth="1"/>
+    <col min="16135" max="16136" width="9.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="18" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:8" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="A1" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-    </row>
-    <row r="2" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="2"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="4" t="s">
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+    </row>
+    <row r="2" spans="1:8" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="2"/>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A3" s="5"/>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-    </row>
-    <row r="4" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="6">
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="1"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="28"/>
+      <c r="B3" s="28"/>
+      <c r="C3" s="28"/>
+      <c r="D3" s="28"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="28"/>
+      <c r="G3" s="28"/>
+      <c r="H3" s="28"/>
+    </row>
+    <row r="4" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="4">
         <v>4007</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="8"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A5" s="9"/>
-      <c r="B5" s="10" t="s">
+      <c r="C4" s="29"/>
+      <c r="D4" s="29"/>
+      <c r="E4" s="29"/>
+      <c r="F4" s="29"/>
+      <c r="G4" s="29"/>
+      <c r="H4" s="5"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="6"/>
+      <c r="B5" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="10"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
-      <c r="F5" s="10"/>
-      <c r="G5" s="10"/>
-      <c r="H5" s="9"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A6" s="11"/>
-      <c r="B6" s="12" t="s">
+      <c r="C5" s="26"/>
+      <c r="D5" s="26"/>
+      <c r="E5" s="26"/>
+      <c r="F5" s="26"/>
+      <c r="G5" s="26"/>
+      <c r="H5" s="6"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="7"/>
+      <c r="B6" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="12"/>
-      <c r="D6" s="12"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="11"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A7" s="12" t="s">
+      <c r="C6" s="27"/>
+      <c r="D6" s="27"/>
+      <c r="E6" s="27"/>
+      <c r="F6" s="27"/>
+      <c r="G6" s="27"/>
+      <c r="H6" s="7"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="12"/>
-      <c r="C7" s="12"/>
-      <c r="D7" s="12"/>
-      <c r="E7" s="12"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="12"/>
-      <c r="H7" s="12"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A8" s="5" t="s">
+      <c r="B7" s="27"/>
+      <c r="C7" s="27"/>
+      <c r="D7" s="27"/>
+      <c r="E7" s="27"/>
+      <c r="F7" s="27"/>
+      <c r="G7" s="27"/>
+      <c r="H7" s="27"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A9" s="5" t="s">
+      <c r="B8" s="28"/>
+      <c r="C8" s="28"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="28"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
-    </row>
-    <row r="10" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="13"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A11" s="15">
+      <c r="B9" s="28"/>
+      <c r="C9" s="28"/>
+      <c r="D9" s="28"/>
+      <c r="E9" s="28"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="28"/>
+      <c r="H9" s="28"/>
+    </row>
+    <row r="10" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="8"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="10">
         <v>3987</v>
       </c>
-      <c r="B11" s="16">
+      <c r="B11" s="11">
         <v>1</v>
       </c>
-      <c r="C11" s="17" t="s">
+      <c r="C11" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="D11" s="18">
+      <c r="D11" s="13">
         <v>56</v>
       </c>
-      <c r="E11" s="19" t="s">
+      <c r="E11" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="F11" s="18">
+      <c r="F11" s="13">
         <v>6</v>
       </c>
-      <c r="G11" s="20"/>
-      <c r="H11" s="20"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A12" s="15">
+      <c r="G11" s="15"/>
+      <c r="H11" s="15"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="10">
         <v>3996</v>
       </c>
-      <c r="B12" s="16">
+      <c r="B12" s="11">
         <v>2</v>
       </c>
-      <c r="C12" s="17" t="s">
+      <c r="C12" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="D12" s="18">
+      <c r="D12" s="13">
         <v>56</v>
       </c>
-      <c r="E12" s="19" t="s">
+      <c r="E12" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="F12" s="18">
+      <c r="F12" s="13">
         <v>3</v>
       </c>
-      <c r="G12" s="20">
+      <c r="G12" s="15">
         <v>2.5</v>
       </c>
-      <c r="H12" s="20">
+      <c r="H12" s="15">
         <v>2.5</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A13" s="15">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="10">
         <v>3996</v>
       </c>
-      <c r="B13" s="16">
+      <c r="B13" s="11">
         <v>3</v>
       </c>
-      <c r="C13" s="17" t="s">
+      <c r="C13" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="D13" s="18">
+      <c r="D13" s="13">
         <v>56</v>
       </c>
-      <c r="E13" s="19" t="s">
+      <c r="E13" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="F13" s="18">
+      <c r="F13" s="13">
         <v>7</v>
       </c>
-      <c r="G13" s="20">
+      <c r="G13" s="15">
         <v>3.5</v>
       </c>
-      <c r="H13" s="20">
+      <c r="H13" s="15">
         <v>6</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A14" s="15">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="10">
         <v>3934</v>
       </c>
-      <c r="B14" s="16">
+      <c r="B14" s="11">
         <v>4</v>
       </c>
-      <c r="C14" s="17" t="s">
+      <c r="C14" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="D14" s="18">
+      <c r="D14" s="13">
         <v>56</v>
       </c>
-      <c r="E14" s="19" t="s">
+      <c r="E14" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="F14" s="18">
+      <c r="F14" s="13">
         <v>10</v>
       </c>
-      <c r="G14" s="20">
+      <c r="G14" s="15">
         <v>5.5</v>
       </c>
-      <c r="H14" s="20">
+      <c r="H14" s="15">
         <v>11.5</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A15" s="15">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" s="10">
         <v>3996</v>
       </c>
-      <c r="B15" s="16">
+      <c r="B15" s="11">
         <v>5</v>
       </c>
-      <c r="C15" s="17" t="s">
+      <c r="C15" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="D15" s="18">
+      <c r="D15" s="13">
         <v>56</v>
       </c>
-      <c r="E15" s="19" t="s">
+      <c r="E15" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="F15" s="18">
+      <c r="F15" s="13">
         <v>5</v>
       </c>
-      <c r="G15" s="20">
+      <c r="G15" s="15">
         <v>2.5</v>
       </c>
-      <c r="H15" s="20">
+      <c r="H15" s="15">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A16" s="15">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="10">
         <v>4001</v>
       </c>
-      <c r="B16" s="16">
+      <c r="B16" s="11">
         <v>6</v>
       </c>
-      <c r="C16" s="17" t="s">
+      <c r="C16" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="D16" s="18">
+      <c r="D16" s="13">
         <v>56</v>
       </c>
-      <c r="E16" s="19" t="s">
+      <c r="E16" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="F16" s="18">
+      <c r="F16" s="13">
         <v>2</v>
       </c>
-      <c r="G16" s="20">
+      <c r="G16" s="15">
         <v>2.5</v>
       </c>
-      <c r="H16" s="20">
+      <c r="H16" s="15">
         <v>16.5</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A17" s="15">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="10">
         <v>3996</v>
       </c>
-      <c r="B17" s="16">
+      <c r="B17" s="11">
         <v>7</v>
       </c>
-      <c r="C17" s="17" t="s">
+      <c r="C17" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="D17" s="18">
+      <c r="D17" s="13">
         <v>56</v>
       </c>
-      <c r="E17" s="19" t="s">
+      <c r="E17" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="F17" s="18">
+      <c r="F17" s="13">
         <v>9</v>
       </c>
-      <c r="G17" s="20" t="s">
+      <c r="G17" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="H17" s="20">
+      <c r="H17" s="15">
         <v>17.25</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A18" s="15">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="10">
         <v>3987</v>
       </c>
-      <c r="B18" s="16">
+      <c r="B18" s="11">
         <v>8</v>
       </c>
-      <c r="C18" s="17" t="s">
+      <c r="C18" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="D18" s="18">
+      <c r="D18" s="13">
         <v>56</v>
       </c>
-      <c r="E18" s="19" t="s">
+      <c r="E18" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="F18" s="18">
+      <c r="F18" s="13">
         <v>4</v>
       </c>
-      <c r="G18" s="20" t="s">
+      <c r="G18" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="H18" s="20">
+      <c r="H18" s="15">
         <v>19.25</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A19" s="15">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="10">
         <v>0</v>
       </c>
-      <c r="B19" s="16">
+      <c r="B19" s="11">
         <v>9</v>
       </c>
-      <c r="C19" s="17" t="s">
+      <c r="C19" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="D19" s="18">
+      <c r="D19" s="13">
         <v>56</v>
       </c>
-      <c r="E19" s="19" t="s">
+      <c r="E19" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="F19" s="18">
+      <c r="F19" s="13">
         <v>1</v>
       </c>
-      <c r="G19" s="20" t="s">
+      <c r="G19" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="H19" s="20" t="s">
+      <c r="H19" s="15" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A20" s="15">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="10">
         <v>3407</v>
       </c>
-      <c r="B20" s="16" t="s">
+      <c r="B20" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="C20" s="17" t="s">
+      <c r="C20" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="D20" s="18">
+      <c r="D20" s="13">
         <v>54</v>
       </c>
-      <c r="E20" s="19" t="s">
+      <c r="E20" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="F20" s="18">
+      <c r="F20" s="13">
         <v>8</v>
       </c>
-      <c r="G20" s="20" t="s">
+      <c r="G20" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="H20" s="20" t="s">
+      <c r="H20" s="15" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="21"/>
-      <c r="B21" s="21"/>
-      <c r="D21" s="18"/>
-      <c r="E21" s="21"/>
-      <c r="F21" s="18"/>
-      <c r="G21" s="21"/>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B22" s="22" t="s">
+    <row r="21" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="16"/>
+      <c r="B21" s="16"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="16"/>
+      <c r="F21" s="13"/>
+      <c r="G21" s="16"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B22" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="C22" s="8"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="8"/>
-      <c r="G22" s="8"/>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B23" s="22" t="s">
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B23" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="C23" s="8"/>
-      <c r="D23" s="8"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="8"/>
-      <c r="G23" s="8"/>
-    </row>
-    <row r="24" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B24" s="22"/>
-      <c r="C24" s="21"/>
-      <c r="D24" s="21"/>
-      <c r="E24" s="21"/>
-      <c r="F24" s="21"/>
-      <c r="G24" s="21"/>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B25" s="23" t="s">
+      <c r="C23" s="5"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5"/>
+      <c r="G23" s="5"/>
+    </row>
+    <row r="24" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="17"/>
+      <c r="C24" s="16"/>
+      <c r="D24" s="16"/>
+      <c r="E24" s="16"/>
+      <c r="F24" s="16"/>
+      <c r="G24" s="16"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="C25" s="21"/>
-      <c r="D25" s="21"/>
-      <c r="E25" s="21"/>
-      <c r="F25" s="21"/>
-      <c r="G25" s="21"/>
-    </row>
-    <row r="26" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C26" s="21"/>
-      <c r="D26" s="21"/>
-      <c r="E26" s="21"/>
-      <c r="F26" s="21"/>
-      <c r="G26" s="21"/>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B27" s="23" t="s">
+      <c r="C25" s="16"/>
+      <c r="D25" s="16"/>
+      <c r="E25" s="16"/>
+      <c r="F25" s="16"/>
+      <c r="G25" s="16"/>
+    </row>
+    <row r="26" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C26" s="16"/>
+      <c r="D26" s="16"/>
+      <c r="E26" s="16"/>
+      <c r="F26" s="16"/>
+      <c r="G26" s="16"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="C27" s="21"/>
-      <c r="D27" s="21"/>
-      <c r="E27" s="21"/>
-      <c r="F27" s="21"/>
-      <c r="G27" s="21"/>
-    </row>
-    <row r="28" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B28" s="23"/>
-      <c r="C28" s="21"/>
-      <c r="D28" s="21"/>
-      <c r="E28" s="21"/>
-      <c r="F28" s="21"/>
-      <c r="G28" s="21"/>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B29" s="22" t="s">
+      <c r="C27" s="16"/>
+      <c r="D27" s="16"/>
+      <c r="E27" s="16"/>
+      <c r="F27" s="16"/>
+      <c r="G27" s="16"/>
+    </row>
+    <row r="28" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="18"/>
+      <c r="C28" s="16"/>
+      <c r="D28" s="16"/>
+      <c r="E28" s="16"/>
+      <c r="F28" s="16"/>
+      <c r="G28" s="16"/>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B29" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="21"/>
-      <c r="D29" s="21"/>
-      <c r="E29" s="21"/>
-      <c r="F29" s="21"/>
-      <c r="G29" s="21"/>
-    </row>
-    <row r="30" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B30" s="8"/>
-      <c r="C30" s="21"/>
-      <c r="D30" s="21"/>
-      <c r="E30" s="21"/>
-      <c r="F30" s="21"/>
-      <c r="G30" s="21"/>
-    </row>
-    <row r="31" spans="1:8" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="22" t="s">
+      <c r="C29" s="16"/>
+      <c r="D29" s="16"/>
+      <c r="E29" s="16"/>
+      <c r="F29" s="16"/>
+      <c r="G29" s="16"/>
+    </row>
+    <row r="30" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="5"/>
+      <c r="C30" s="16"/>
+      <c r="D30" s="16"/>
+      <c r="E30" s="16"/>
+      <c r="F30" s="16"/>
+      <c r="G30" s="16"/>
+    </row>
+    <row r="31" spans="1:8" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B31" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="E31" s="22" t="s">
+      <c r="E31" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="F31" s="21"/>
-      <c r="G31" s="21"/>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B32" s="24"/>
-      <c r="C32" s="24"/>
-      <c r="D32" s="24"/>
-      <c r="E32" s="25"/>
-      <c r="F32" s="24"/>
-      <c r="G32" s="24"/>
-    </row>
-    <row r="33" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A33" s="6">
+      <c r="F31" s="16"/>
+      <c r="G31" s="16"/>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B32" s="19"/>
+      <c r="C32" s="19"/>
+      <c r="D32" s="19"/>
+      <c r="E32" s="20"/>
+      <c r="F32" s="19"/>
+      <c r="G32" s="19"/>
+    </row>
+    <row r="33" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A33" s="4">
         <v>4008</v>
       </c>
-      <c r="B33" s="7" t="s">
+      <c r="B33" s="29" t="s">
         <v>39</v>
       </c>
-      <c r="C33" s="7"/>
-      <c r="D33" s="7"/>
-      <c r="E33" s="7"/>
-      <c r="F33" s="7"/>
-      <c r="G33" s="7"/>
-      <c r="H33" s="8"/>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A34" s="9"/>
-      <c r="B34" s="10" t="s">
+      <c r="C33" s="29"/>
+      <c r="D33" s="29"/>
+      <c r="E33" s="29"/>
+      <c r="F33" s="29"/>
+      <c r="G33" s="29"/>
+      <c r="H33" s="5"/>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" s="6"/>
+      <c r="B34" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="C34" s="10"/>
-      <c r="D34" s="10"/>
-      <c r="E34" s="10"/>
-      <c r="F34" s="10"/>
-      <c r="G34" s="10"/>
-      <c r="H34" s="9"/>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A35" s="11"/>
-      <c r="B35" s="12" t="s">
+      <c r="C34" s="26"/>
+      <c r="D34" s="26"/>
+      <c r="E34" s="26"/>
+      <c r="F34" s="26"/>
+      <c r="G34" s="26"/>
+      <c r="H34" s="6"/>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" s="7"/>
+      <c r="B35" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="C35" s="12"/>
-      <c r="D35" s="12"/>
-      <c r="E35" s="12"/>
-      <c r="F35" s="12"/>
-      <c r="G35" s="12"/>
-      <c r="H35" s="11"/>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A36" s="12" t="s">
+      <c r="C35" s="27"/>
+      <c r="D35" s="27"/>
+      <c r="E35" s="27"/>
+      <c r="F35" s="27"/>
+      <c r="G35" s="27"/>
+      <c r="H35" s="7"/>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="B36" s="12"/>
-      <c r="C36" s="12"/>
-      <c r="D36" s="12"/>
-      <c r="E36" s="12"/>
-      <c r="F36" s="12"/>
-      <c r="G36" s="12"/>
-      <c r="H36" s="12"/>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A37" s="26" t="s">
+      <c r="B36" s="27"/>
+      <c r="C36" s="27"/>
+      <c r="D36" s="27"/>
+      <c r="E36" s="27"/>
+      <c r="F36" s="27"/>
+      <c r="G36" s="27"/>
+      <c r="H36" s="27"/>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" s="30" t="s">
         <v>43</v>
       </c>
-      <c r="B37" s="5"/>
-      <c r="C37" s="5"/>
-      <c r="D37" s="5"/>
-      <c r="E37" s="5"/>
-      <c r="F37" s="5"/>
-      <c r="G37" s="5"/>
-      <c r="H37" s="5"/>
-    </row>
-    <row r="38" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B38" s="13"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="14"/>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A39" s="15">
+      <c r="B37" s="28"/>
+      <c r="C37" s="28"/>
+      <c r="D37" s="28"/>
+      <c r="E37" s="28"/>
+      <c r="F37" s="28"/>
+      <c r="G37" s="28"/>
+      <c r="H37" s="28"/>
+    </row>
+    <row r="38" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="8"/>
+      <c r="C38" s="9"/>
+      <c r="D38" s="9"/>
+      <c r="E38" s="9"/>
+      <c r="F38" s="9"/>
+      <c r="G38" s="9"/>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" s="10">
         <v>4003</v>
       </c>
-      <c r="B39" s="18">
+      <c r="B39" s="13">
         <v>1</v>
       </c>
-      <c r="C39" s="17" t="s">
+      <c r="C39" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="D39" s="18">
+      <c r="D39" s="13">
         <v>56</v>
       </c>
-      <c r="E39" s="19" t="s">
+      <c r="E39" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="F39" s="18">
+      <c r="F39" s="13">
         <v>2</v>
       </c>
-      <c r="G39" s="20"/>
-      <c r="H39" s="20"/>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A40" s="15">
+      <c r="G39" s="15"/>
+      <c r="H39" s="15"/>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" s="10">
         <v>4003</v>
       </c>
-      <c r="B40" s="18">
+      <c r="B40" s="13">
         <v>2</v>
       </c>
-      <c r="C40" s="17" t="s">
+      <c r="C40" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="D40" s="18">
+      <c r="D40" s="13">
         <v>54</v>
       </c>
-      <c r="E40" s="19" t="s">
+      <c r="E40" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="F40" s="18">
+      <c r="F40" s="13">
         <v>5</v>
       </c>
-      <c r="G40" s="20" t="s">
+      <c r="G40" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="H40" s="20">
+      <c r="H40" s="15">
         <v>2</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A41" s="15">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" s="10">
         <v>4000</v>
       </c>
-      <c r="B41" s="18">
+      <c r="B41" s="13">
         <v>3</v>
       </c>
-      <c r="C41" s="17" t="s">
+      <c r="C41" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="D41" s="18">
+      <c r="D41" s="13">
         <v>54</v>
       </c>
-      <c r="E41" s="19" t="s">
+      <c r="E41" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="F41" s="18">
+      <c r="F41" s="13">
         <v>4</v>
       </c>
-      <c r="G41" s="20">
+      <c r="G41" s="15">
         <v>1.5</v>
       </c>
-      <c r="H41" s="20">
+      <c r="H41" s="15">
         <v>3.5</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A42" s="15">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" s="10">
         <v>4003</v>
       </c>
-      <c r="B42" s="18">
+      <c r="B42" s="13">
         <v>4</v>
       </c>
-      <c r="C42" s="17" t="s">
+      <c r="C42" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="D42" s="18">
+      <c r="D42" s="13">
         <v>56</v>
       </c>
-      <c r="E42" s="19" t="s">
+      <c r="E42" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="F42" s="18">
+      <c r="F42" s="13">
         <v>3</v>
       </c>
-      <c r="G42" s="20">
+      <c r="G42" s="15">
         <v>2.5</v>
       </c>
-      <c r="H42" s="20">
+      <c r="H42" s="15">
         <v>6</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A43" s="15">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" s="10">
         <v>4003</v>
       </c>
-      <c r="B43" s="18">
+      <c r="B43" s="13">
         <v>5</v>
       </c>
-      <c r="C43" s="17" t="s">
+      <c r="C43" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="D43" s="18">
+      <c r="D43" s="13">
         <v>56</v>
       </c>
-      <c r="E43" s="19" t="s">
+      <c r="E43" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="F43" s="18">
+      <c r="F43" s="13">
         <v>1</v>
       </c>
-      <c r="G43" s="20" t="s">
+      <c r="G43" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="H43" s="20">
+      <c r="H43" s="15">
         <v>17</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A44" s="15">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" s="10">
         <v>4003</v>
       </c>
-      <c r="B44" s="16" t="s">
+      <c r="B44" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="C44" s="17" t="s">
+      <c r="C44" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="D44" s="18">
+      <c r="D44" s="13">
         <v>56</v>
       </c>
-      <c r="E44" s="19" t="s">
+      <c r="E44" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="F44" s="18">
+      <c r="F44" s="13">
         <v>7</v>
       </c>
-      <c r="G44" s="20" t="s">
+      <c r="G44" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="H44" s="20">
+      <c r="H44" s="15">
         <v>17</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="21"/>
-      <c r="B45" s="21"/>
-      <c r="D45" s="18"/>
-      <c r="E45" s="21"/>
-      <c r="F45" s="18"/>
-      <c r="G45" s="20"/>
-      <c r="H45" s="20"/>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B46" s="22" t="s">
+    <row r="45" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="16"/>
+      <c r="B45" s="16"/>
+      <c r="D45" s="13"/>
+      <c r="E45" s="16"/>
+      <c r="F45" s="13"/>
+      <c r="G45" s="15"/>
+      <c r="H45" s="15"/>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B46" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="C46" s="8"/>
-      <c r="D46" s="8"/>
-      <c r="E46" s="8"/>
-      <c r="F46" s="8"/>
-      <c r="G46" s="8"/>
-      <c r="H46" s="20"/>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B47" s="22" t="s">
+      <c r="C46" s="5"/>
+      <c r="D46" s="5"/>
+      <c r="E46" s="5"/>
+      <c r="F46" s="5"/>
+      <c r="G46" s="5"/>
+      <c r="H46" s="15"/>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B47" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="C47" s="8"/>
-      <c r="D47" s="8"/>
-      <c r="E47" s="8"/>
-      <c r="F47" s="8"/>
-      <c r="G47" s="8"/>
-      <c r="H47" s="20"/>
-    </row>
-    <row r="48" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B48" s="22"/>
-      <c r="C48" s="21"/>
-      <c r="D48" s="21"/>
-      <c r="E48" s="21"/>
-      <c r="F48" s="21"/>
-      <c r="G48" s="21"/>
-      <c r="H48" s="20"/>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B49" s="23" t="s">
+      <c r="C47" s="5"/>
+      <c r="D47" s="5"/>
+      <c r="E47" s="5"/>
+      <c r="F47" s="5"/>
+      <c r="G47" s="5"/>
+      <c r="H47" s="15"/>
+    </row>
+    <row r="48" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B48" s="17"/>
+      <c r="C48" s="16"/>
+      <c r="D48" s="16"/>
+      <c r="E48" s="16"/>
+      <c r="F48" s="16"/>
+      <c r="G48" s="16"/>
+      <c r="H48" s="15"/>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B49" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="C49" s="21"/>
-      <c r="D49" s="21"/>
-      <c r="E49" s="21"/>
-      <c r="F49" s="21"/>
-      <c r="G49" s="21"/>
-    </row>
-    <row r="50" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C50" s="21"/>
-      <c r="D50" s="21"/>
-      <c r="E50" s="21"/>
-      <c r="F50" s="21"/>
-      <c r="G50" s="21"/>
-      <c r="H50" s="20"/>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B51" s="23" t="s">
+      <c r="C49" s="16"/>
+      <c r="D49" s="16"/>
+      <c r="E49" s="16"/>
+      <c r="F49" s="16"/>
+      <c r="G49" s="16"/>
+    </row>
+    <row r="50" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C50" s="16"/>
+      <c r="D50" s="16"/>
+      <c r="E50" s="16"/>
+      <c r="F50" s="16"/>
+      <c r="G50" s="16"/>
+      <c r="H50" s="15"/>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B51" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="C51" s="21"/>
-      <c r="D51" s="21"/>
-      <c r="E51" s="21"/>
-      <c r="F51" s="21"/>
-      <c r="G51" s="21"/>
-      <c r="H51" s="20"/>
-    </row>
-    <row r="52" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B52" s="23"/>
-      <c r="C52" s="21"/>
-      <c r="D52" s="21"/>
-      <c r="E52" s="21"/>
-      <c r="F52" s="21"/>
-      <c r="G52" s="21"/>
-      <c r="H52" s="20"/>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B53" s="22" t="s">
+      <c r="C51" s="16"/>
+      <c r="D51" s="16"/>
+      <c r="E51" s="16"/>
+      <c r="F51" s="16"/>
+      <c r="G51" s="16"/>
+      <c r="H51" s="15"/>
+    </row>
+    <row r="52" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B52" s="18"/>
+      <c r="C52" s="16"/>
+      <c r="D52" s="16"/>
+      <c r="E52" s="16"/>
+      <c r="F52" s="16"/>
+      <c r="G52" s="16"/>
+      <c r="H52" s="15"/>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B53" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="C53" s="21"/>
-      <c r="D53" s="21"/>
-      <c r="E53" s="21"/>
-      <c r="F53" s="21"/>
-      <c r="G53" s="21"/>
-    </row>
-    <row r="54" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B54" s="8"/>
-      <c r="C54" s="21"/>
-      <c r="D54" s="21"/>
-      <c r="E54" s="21"/>
-      <c r="F54" s="21"/>
-      <c r="G54" s="21"/>
-    </row>
-    <row r="55" spans="1:8" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B55" s="22" t="s">
+      <c r="C53" s="16"/>
+      <c r="D53" s="16"/>
+      <c r="E53" s="16"/>
+      <c r="F53" s="16"/>
+      <c r="G53" s="16"/>
+    </row>
+    <row r="54" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B54" s="5"/>
+      <c r="C54" s="16"/>
+      <c r="D54" s="16"/>
+      <c r="E54" s="16"/>
+      <c r="F54" s="16"/>
+      <c r="G54" s="16"/>
+    </row>
+    <row r="55" spans="1:8" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B55" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="E55" s="22" t="s">
+      <c r="E55" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="F55" s="21"/>
-      <c r="G55" s="21"/>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B56" s="24"/>
-      <c r="C56" s="24"/>
-      <c r="D56" s="24"/>
-      <c r="E56" s="25"/>
-      <c r="F56" s="24"/>
-      <c r="G56" s="24"/>
-    </row>
-    <row r="57" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A57" s="6">
+      <c r="F55" s="16"/>
+      <c r="G55" s="16"/>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B56" s="19"/>
+      <c r="C56" s="19"/>
+      <c r="D56" s="19"/>
+      <c r="E56" s="20"/>
+      <c r="F56" s="19"/>
+      <c r="G56" s="19"/>
+    </row>
+    <row r="57" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A57" s="4">
         <v>4009</v>
       </c>
-      <c r="B57" s="7" t="s">
+      <c r="B57" s="29" t="s">
         <v>62</v>
       </c>
-      <c r="C57" s="7"/>
-      <c r="D57" s="7"/>
-      <c r="E57" s="7"/>
-      <c r="F57" s="7"/>
-      <c r="G57" s="7"/>
-      <c r="H57" s="8"/>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A58" s="9"/>
-      <c r="B58" s="10" t="s">
+      <c r="C57" s="29"/>
+      <c r="D57" s="29"/>
+      <c r="E57" s="29"/>
+      <c r="F57" s="29"/>
+      <c r="G57" s="29"/>
+      <c r="H57" s="5"/>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" s="6"/>
+      <c r="B58" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="C58" s="10"/>
-      <c r="D58" s="10"/>
-      <c r="E58" s="10"/>
-      <c r="F58" s="10"/>
-      <c r="G58" s="10"/>
-      <c r="H58" s="9"/>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A59" s="12" t="s">
+      <c r="C58" s="26"/>
+      <c r="D58" s="26"/>
+      <c r="E58" s="26"/>
+      <c r="F58" s="26"/>
+      <c r="G58" s="26"/>
+      <c r="H58" s="6"/>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="B59" s="12"/>
-      <c r="C59" s="12"/>
-      <c r="D59" s="12"/>
-      <c r="E59" s="12"/>
-      <c r="F59" s="12"/>
-      <c r="G59" s="12"/>
-      <c r="H59" s="12"/>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A60" s="11"/>
-      <c r="B60" s="12" t="s">
+      <c r="B59" s="27"/>
+      <c r="C59" s="27"/>
+      <c r="D59" s="27"/>
+      <c r="E59" s="27"/>
+      <c r="F59" s="27"/>
+      <c r="G59" s="27"/>
+      <c r="H59" s="27"/>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" s="7"/>
+      <c r="B60" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="C60" s="12"/>
-      <c r="D60" s="12"/>
-      <c r="E60" s="12"/>
-      <c r="F60" s="12"/>
-      <c r="G60" s="12"/>
-      <c r="H60" s="11"/>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A61" s="26" t="s">
+      <c r="C60" s="27"/>
+      <c r="D60" s="27"/>
+      <c r="E60" s="27"/>
+      <c r="F60" s="27"/>
+      <c r="G60" s="27"/>
+      <c r="H60" s="7"/>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" s="30" t="s">
         <v>65</v>
       </c>
-      <c r="B61" s="5"/>
-      <c r="C61" s="5"/>
-      <c r="D61" s="5"/>
-      <c r="E61" s="5"/>
-      <c r="F61" s="5"/>
-      <c r="G61" s="5"/>
-      <c r="H61" s="5"/>
-    </row>
-    <row r="62" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B62" s="13"/>
-      <c r="C62" s="14"/>
-      <c r="D62" s="14"/>
-      <c r="E62" s="14"/>
-      <c r="F62" s="14"/>
-      <c r="G62" s="14"/>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A63" s="15">
+      <c r="B61" s="28"/>
+      <c r="C61" s="28"/>
+      <c r="D61" s="28"/>
+      <c r="E61" s="28"/>
+      <c r="F61" s="28"/>
+      <c r="G61" s="28"/>
+      <c r="H61" s="28"/>
+    </row>
+    <row r="62" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B62" s="8"/>
+      <c r="C62" s="9"/>
+      <c r="D62" s="9"/>
+      <c r="E62" s="9"/>
+      <c r="F62" s="9"/>
+      <c r="G62" s="9"/>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" s="10">
         <v>4003</v>
       </c>
-      <c r="B63" s="18">
+      <c r="B63" s="13">
         <v>1</v>
       </c>
-      <c r="C63" s="17" t="s">
+      <c r="C63" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="D63" s="18">
+      <c r="D63" s="13">
         <v>56</v>
       </c>
-      <c r="E63" s="19" t="s">
+      <c r="E63" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="F63" s="18">
+      <c r="F63" s="13">
         <v>5</v>
       </c>
-      <c r="G63" s="20"/>
-      <c r="H63" s="20"/>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A64" s="15">
+      <c r="G63" s="15"/>
+      <c r="H63" s="15"/>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" s="10">
         <v>4003</v>
       </c>
-      <c r="B64" s="18">
+      <c r="B64" s="13">
         <v>2</v>
       </c>
-      <c r="C64" s="17" t="s">
+      <c r="C64" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="D64" s="18">
+      <c r="D64" s="13">
         <v>54</v>
       </c>
-      <c r="E64" s="19" t="s">
+      <c r="E64" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="F64" s="18">
+      <c r="F64" s="13">
         <v>10</v>
       </c>
-      <c r="G64" s="20" t="s">
+      <c r="G64" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="H64" s="20">
+      <c r="H64" s="15">
         <v>0.75</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A65" s="15">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" s="10">
         <v>4000</v>
       </c>
-      <c r="B65" s="18">
+      <c r="B65" s="13">
         <v>3</v>
       </c>
-      <c r="C65" s="17" t="s">
+      <c r="C65" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="D65" s="18">
+      <c r="D65" s="13">
         <v>52</v>
       </c>
-      <c r="E65" s="19" t="s">
+      <c r="E65" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="F65" s="18">
+      <c r="F65" s="13">
         <v>8</v>
       </c>
-      <c r="G65" s="20">
+      <c r="G65" s="15">
         <v>2.5</v>
       </c>
-      <c r="H65" s="20">
+      <c r="H65" s="15">
         <v>3.25</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A66" s="15">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" s="10">
         <v>3999</v>
       </c>
-      <c r="B66" s="18">
+      <c r="B66" s="13">
         <v>4</v>
       </c>
-      <c r="C66" s="17" t="s">
+      <c r="C66" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="D66" s="18">
+      <c r="D66" s="13">
         <v>52</v>
       </c>
-      <c r="E66" s="19" t="s">
+      <c r="E66" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="F66" s="18">
+      <c r="F66" s="13">
         <v>7</v>
       </c>
-      <c r="G66" s="20" t="s">
+      <c r="G66" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="H66" s="20">
+      <c r="H66" s="15">
         <v>6.25</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A67" s="15">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" s="10">
         <v>4000</v>
       </c>
-      <c r="B67" s="18">
+      <c r="B67" s="13">
         <v>5</v>
       </c>
-      <c r="C67" s="17" t="s">
+      <c r="C67" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="D67" s="18">
+      <c r="D67" s="13">
         <v>56</v>
       </c>
-      <c r="E67" s="19" t="s">
+      <c r="E67" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="F67" s="18">
+      <c r="F67" s="13">
         <v>6</v>
       </c>
-      <c r="G67" s="20" t="s">
+      <c r="G67" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="H67" s="20">
+      <c r="H67" s="15">
         <v>11.25</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A68" s="15">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" s="10">
         <v>4000</v>
       </c>
-      <c r="B68" s="18">
+      <c r="B68" s="13">
         <v>6</v>
       </c>
-      <c r="C68" s="17" t="s">
+      <c r="C68" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="D68" s="18">
+      <c r="D68" s="13">
         <v>56</v>
       </c>
-      <c r="E68" s="19" t="s">
+      <c r="E68" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="F68" s="18">
+      <c r="F68" s="13">
         <v>2</v>
       </c>
-      <c r="G68" s="20" t="s">
+      <c r="G68" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="H68" s="20">
+      <c r="H68" s="15">
         <v>18.25</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A69" s="15">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" s="10">
         <v>4000</v>
       </c>
-      <c r="B69" s="18">
+      <c r="B69" s="13">
         <v>7</v>
       </c>
-      <c r="C69" s="17" t="s">
+      <c r="C69" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="D69" s="18">
+      <c r="D69" s="13">
         <v>56</v>
       </c>
-      <c r="E69" s="19" t="s">
+      <c r="E69" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="F69" s="18">
+      <c r="F69" s="13">
         <v>1</v>
       </c>
-      <c r="G69" s="20" t="s">
+      <c r="G69" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="H69" s="20">
+      <c r="H69" s="15">
         <v>22.25</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A70" s="15">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" s="10">
         <v>3999</v>
       </c>
-      <c r="B70" s="18" t="s">
+      <c r="B70" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C70" s="17" t="s">
+      <c r="C70" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="D70" s="18">
+      <c r="D70" s="13">
         <v>54</v>
       </c>
-      <c r="E70" s="19" t="s">
+      <c r="E70" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="F70" s="18">
+      <c r="F70" s="13">
         <v>4</v>
       </c>
-      <c r="G70" s="20" t="s">
+      <c r="G70" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="H70" s="20">
+      <c r="H70" s="15">
         <v>32.25</v>
       </c>
     </row>
-    <row r="71" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="21"/>
-      <c r="B71" s="21"/>
-      <c r="D71" s="18"/>
-      <c r="E71" s="21"/>
-      <c r="F71" s="18"/>
-      <c r="G71" s="21"/>
-      <c r="H71" s="21"/>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B72" s="22" t="s">
+    <row r="71" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="16"/>
+      <c r="B71" s="16"/>
+      <c r="D71" s="13"/>
+      <c r="E71" s="16"/>
+      <c r="F71" s="13"/>
+      <c r="G71" s="16"/>
+      <c r="H71" s="16"/>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B72" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="C72" s="8"/>
-      <c r="D72" s="8"/>
-      <c r="E72" s="8"/>
-      <c r="F72" s="8"/>
-      <c r="G72" s="8"/>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B73" s="22" t="s">
+      <c r="C72" s="5"/>
+      <c r="D72" s="5"/>
+      <c r="E72" s="5"/>
+      <c r="F72" s="5"/>
+      <c r="G72" s="5"/>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B73" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="C73" s="8"/>
-      <c r="D73" s="8"/>
-      <c r="E73" s="8"/>
-      <c r="F73" s="8"/>
-      <c r="G73" s="8"/>
-    </row>
-    <row r="74" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B74" s="22"/>
-      <c r="C74" s="21"/>
-      <c r="D74" s="21"/>
-      <c r="E74" s="21"/>
-      <c r="F74" s="21"/>
-      <c r="G74" s="21"/>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B75" s="23" t="s">
+      <c r="C73" s="5"/>
+      <c r="D73" s="5"/>
+      <c r="E73" s="5"/>
+      <c r="F73" s="5"/>
+      <c r="G73" s="5"/>
+    </row>
+    <row r="74" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B74" s="17"/>
+      <c r="C74" s="16"/>
+      <c r="D74" s="16"/>
+      <c r="E74" s="16"/>
+      <c r="F74" s="16"/>
+      <c r="G74" s="16"/>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B75" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="C75" s="21"/>
-      <c r="D75" s="21"/>
-      <c r="E75" s="21"/>
-      <c r="F75" s="21"/>
-      <c r="G75" s="21"/>
-    </row>
-    <row r="76" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C76" s="21"/>
-      <c r="D76" s="21"/>
-      <c r="E76" s="21"/>
-      <c r="F76" s="21"/>
-      <c r="G76" s="21"/>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B77" s="23" t="s">
+      <c r="C75" s="16"/>
+      <c r="D75" s="16"/>
+      <c r="E75" s="16"/>
+      <c r="F75" s="16"/>
+      <c r="G75" s="16"/>
+    </row>
+    <row r="76" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C76" s="16"/>
+      <c r="D76" s="16"/>
+      <c r="E76" s="16"/>
+      <c r="F76" s="16"/>
+      <c r="G76" s="16"/>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B77" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="C77" s="21"/>
-      <c r="D77" s="21"/>
-      <c r="E77" s="21"/>
-      <c r="F77" s="21"/>
-      <c r="G77" s="21"/>
-    </row>
-    <row r="78" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B78" s="23"/>
-      <c r="C78" s="21"/>
-      <c r="D78" s="21"/>
-      <c r="E78" s="21"/>
-      <c r="F78" s="21"/>
-      <c r="G78" s="21"/>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B79" s="22" t="s">
+      <c r="C77" s="16"/>
+      <c r="D77" s="16"/>
+      <c r="E77" s="16"/>
+      <c r="F77" s="16"/>
+      <c r="G77" s="16"/>
+    </row>
+    <row r="78" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B78" s="18"/>
+      <c r="C78" s="16"/>
+      <c r="D78" s="16"/>
+      <c r="E78" s="16"/>
+      <c r="F78" s="16"/>
+      <c r="G78" s="16"/>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B79" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="C79" s="21"/>
-      <c r="D79" s="21"/>
-      <c r="E79" s="21"/>
-      <c r="F79" s="21"/>
-      <c r="G79" s="21"/>
-    </row>
-    <row r="80" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B80" s="8"/>
-      <c r="C80" s="21"/>
-      <c r="D80" s="21"/>
-      <c r="E80" s="21"/>
-      <c r="F80" s="21"/>
-      <c r="G80" s="21"/>
-    </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B81" s="22" t="s">
+      <c r="C79" s="16"/>
+      <c r="D79" s="16"/>
+      <c r="E79" s="16"/>
+      <c r="F79" s="16"/>
+      <c r="G79" s="16"/>
+    </row>
+    <row r="80" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B80" s="5"/>
+      <c r="C80" s="16"/>
+      <c r="D80" s="16"/>
+      <c r="E80" s="16"/>
+      <c r="F80" s="16"/>
+      <c r="G80" s="16"/>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B81" s="17" t="s">
         <v>89</v>
       </c>
-      <c r="E81" s="22" t="s">
+      <c r="E81" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="F81" s="21"/>
-      <c r="G81" s="21"/>
-    </row>
-    <row r="82" spans="1:8" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B82" s="22"/>
-      <c r="E82" s="22" t="s">
+      <c r="F81" s="16"/>
+      <c r="G81" s="16"/>
+    </row>
+    <row r="82" spans="1:8" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B82" s="17"/>
+      <c r="E82" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="F82" s="21"/>
-      <c r="G82" s="21"/>
-    </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B83" s="24"/>
-      <c r="C83" s="24"/>
-      <c r="D83" s="24"/>
-      <c r="E83" s="25"/>
-      <c r="F83" s="24"/>
-      <c r="G83" s="24"/>
-    </row>
-    <row r="84" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A84" s="6">
+      <c r="F82" s="16"/>
+      <c r="G82" s="16"/>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B83" s="19"/>
+      <c r="C83" s="19"/>
+      <c r="D83" s="19"/>
+      <c r="E83" s="20"/>
+      <c r="F83" s="19"/>
+      <c r="G83" s="19"/>
+    </row>
+    <row r="84" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A84" s="4">
         <v>4010</v>
       </c>
-      <c r="B84" s="7" t="s">
+      <c r="B84" s="29" t="s">
         <v>92</v>
       </c>
-      <c r="C84" s="7"/>
-      <c r="D84" s="7"/>
-      <c r="E84" s="7"/>
-      <c r="F84" s="7"/>
-      <c r="G84" s="7"/>
-      <c r="H84" s="8"/>
-    </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A85" s="9"/>
-      <c r="B85" s="10" t="s">
+      <c r="C84" s="29"/>
+      <c r="D84" s="29"/>
+      <c r="E84" s="29"/>
+      <c r="F84" s="29"/>
+      <c r="G84" s="29"/>
+      <c r="H84" s="5"/>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85" s="6"/>
+      <c r="B85" s="26" t="s">
         <v>93</v>
       </c>
-      <c r="C85" s="10"/>
-      <c r="D85" s="10"/>
-      <c r="E85" s="10"/>
-      <c r="F85" s="10"/>
-      <c r="G85" s="10"/>
-      <c r="H85" s="9"/>
-    </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B86" s="12" t="s">
+      <c r="C85" s="26"/>
+      <c r="D85" s="26"/>
+      <c r="E85" s="26"/>
+      <c r="F85" s="26"/>
+      <c r="G85" s="26"/>
+      <c r="H85" s="6"/>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B86" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="C86" s="12"/>
-      <c r="D86" s="12"/>
-      <c r="E86" s="12"/>
-      <c r="F86" s="12"/>
-      <c r="G86" s="12"/>
-      <c r="H86" s="11"/>
-    </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B87" s="12" t="s">
+      <c r="C86" s="27"/>
+      <c r="D86" s="27"/>
+      <c r="E86" s="27"/>
+      <c r="F86" s="27"/>
+      <c r="G86" s="27"/>
+      <c r="H86" s="7"/>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B87" s="27" t="s">
         <v>94</v>
       </c>
-      <c r="C87" s="12"/>
-      <c r="D87" s="12"/>
-      <c r="E87" s="12"/>
-      <c r="F87" s="12"/>
-      <c r="G87" s="12"/>
-      <c r="H87" s="11"/>
-    </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A88" s="5" t="s">
+      <c r="C87" s="27"/>
+      <c r="D87" s="27"/>
+      <c r="E87" s="27"/>
+      <c r="F87" s="27"/>
+      <c r="G87" s="27"/>
+      <c r="H87" s="7"/>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88" s="28" t="s">
         <v>95</v>
       </c>
-      <c r="B88" s="5"/>
-      <c r="C88" s="5"/>
-      <c r="D88" s="5"/>
-      <c r="E88" s="5"/>
-      <c r="F88" s="5"/>
-      <c r="G88" s="5"/>
-      <c r="H88" s="5"/>
-    </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A89" s="5" t="s">
+      <c r="B88" s="28"/>
+      <c r="C88" s="28"/>
+      <c r="D88" s="28"/>
+      <c r="E88" s="28"/>
+      <c r="F88" s="28"/>
+      <c r="G88" s="28"/>
+      <c r="H88" s="28"/>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89" s="28" t="s">
         <v>96</v>
       </c>
-      <c r="B89" s="5"/>
-      <c r="C89" s="5"/>
-      <c r="D89" s="5"/>
-      <c r="E89" s="5"/>
-      <c r="F89" s="5"/>
-      <c r="G89" s="5"/>
-      <c r="H89" s="5"/>
-    </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A90" s="5" t="s">
+      <c r="B89" s="28"/>
+      <c r="C89" s="28"/>
+      <c r="D89" s="28"/>
+      <c r="E89" s="28"/>
+      <c r="F89" s="28"/>
+      <c r="G89" s="28"/>
+      <c r="H89" s="28"/>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90" s="28" t="s">
         <v>97</v>
       </c>
-      <c r="B90" s="5"/>
-      <c r="C90" s="5"/>
-      <c r="D90" s="5"/>
-      <c r="E90" s="5"/>
-      <c r="F90" s="5"/>
-      <c r="G90" s="5"/>
-      <c r="H90" s="5"/>
-    </row>
-    <row r="91" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="27"/>
-      <c r="B91" s="27"/>
-      <c r="C91" s="27"/>
-      <c r="D91" s="27"/>
-      <c r="E91" s="27"/>
-      <c r="F91" s="27"/>
-      <c r="G91" s="27"/>
-      <c r="H91" s="27"/>
-    </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A92" s="15">
+      <c r="B90" s="28"/>
+      <c r="C90" s="28"/>
+      <c r="D90" s="28"/>
+      <c r="E90" s="28"/>
+      <c r="F90" s="28"/>
+      <c r="G90" s="28"/>
+      <c r="H90" s="28"/>
+    </row>
+    <row r="91" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="3"/>
+      <c r="B91" s="3"/>
+      <c r="C91" s="3"/>
+      <c r="D91" s="3"/>
+      <c r="E91" s="3"/>
+      <c r="F91" s="3"/>
+      <c r="G91" s="3"/>
+      <c r="H91" s="3"/>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92" s="10">
         <v>4005</v>
       </c>
-      <c r="B92" s="18">
+      <c r="B92" s="13">
         <v>1</v>
       </c>
-      <c r="C92" s="17" t="s">
+      <c r="C92" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="D92" s="18">
+      <c r="D92" s="13">
         <v>52</v>
       </c>
-      <c r="E92" s="19" t="s">
+      <c r="E92" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="F92" s="18">
+      <c r="F92" s="13">
         <v>4</v>
       </c>
-      <c r="G92" s="20"/>
-      <c r="H92" s="20"/>
-    </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A93" s="15">
+      <c r="G92" s="15"/>
+      <c r="H92" s="15"/>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A93" s="10">
         <v>3998</v>
       </c>
-      <c r="B93" s="18">
+      <c r="B93" s="13">
         <v>2</v>
       </c>
-      <c r="C93" s="17" t="s">
+      <c r="C93" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="D93" s="18">
+      <c r="D93" s="13">
         <v>54</v>
       </c>
-      <c r="E93" s="19" t="s">
+      <c r="E93" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="F93" s="18">
+      <c r="F93" s="13">
         <v>3</v>
       </c>
-      <c r="G93" s="20" t="s">
+      <c r="G93" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="H93" s="20">
+      <c r="H93" s="15">
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A94" s="15">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A94" s="10">
         <v>3998</v>
       </c>
-      <c r="B94" s="18">
+      <c r="B94" s="13">
         <v>3</v>
       </c>
-      <c r="C94" s="17" t="s">
+      <c r="C94" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="D94" s="18">
+      <c r="D94" s="13">
         <v>54</v>
       </c>
-      <c r="E94" s="19" t="s">
+      <c r="E94" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="F94" s="18">
+      <c r="F94" s="13">
         <v>5</v>
       </c>
-      <c r="G94" s="20" t="s">
+      <c r="G94" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="H94" s="20">
+      <c r="H94" s="15">
         <v>2</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A95" s="15">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A95" s="10">
         <v>4006</v>
       </c>
-      <c r="B95" s="18">
+      <c r="B95" s="13">
         <v>4</v>
       </c>
-      <c r="C95" s="17" t="s">
+      <c r="C95" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="D95" s="18">
+      <c r="D95" s="13">
         <v>54</v>
       </c>
-      <c r="E95" s="19" t="s">
+      <c r="E95" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="F95" s="18">
+      <c r="F95" s="13">
         <v>7</v>
       </c>
-      <c r="G95" s="20" t="s">
+      <c r="G95" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="H95" s="20">
+      <c r="H95" s="15">
         <v>2</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A96" s="15">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A96" s="10">
         <v>4006</v>
       </c>
-      <c r="B96" s="18">
+      <c r="B96" s="13">
         <v>5</v>
       </c>
-      <c r="C96" s="17" t="s">
+      <c r="C96" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="D96" s="18">
+      <c r="D96" s="13">
         <v>52</v>
       </c>
-      <c r="E96" s="19" t="s">
+      <c r="E96" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="F96" s="18">
+      <c r="F96" s="13">
         <v>2</v>
       </c>
-      <c r="G96" s="20" t="s">
+      <c r="G96" s="15" t="s">
         <v>105</v>
       </c>
-      <c r="H96" s="20">
+      <c r="H96" s="15">
         <v>2.5</v>
       </c>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A97" s="15">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A97" s="10">
         <v>3965</v>
       </c>
-      <c r="B97" s="18">
+      <c r="B97" s="13">
         <v>6</v>
       </c>
-      <c r="C97" s="17" t="s">
+      <c r="C97" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="D97" s="18">
+      <c r="D97" s="13">
         <v>50</v>
       </c>
-      <c r="E97" s="19" t="s">
+      <c r="E97" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="F97" s="18">
+      <c r="F97" s="13">
         <v>8</v>
       </c>
-      <c r="G97" s="20" t="s">
+      <c r="G97" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="H97" s="20">
+      <c r="H97" s="15">
         <v>3.5</v>
       </c>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A98" s="15">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A98" s="10">
         <v>3995</v>
       </c>
-      <c r="B98" s="18">
+      <c r="B98" s="13">
         <v>7</v>
       </c>
-      <c r="C98" s="17" t="s">
+      <c r="C98" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="D98" s="18">
+      <c r="D98" s="13">
         <v>50</v>
       </c>
-      <c r="E98" s="19" t="s">
+      <c r="E98" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="F98" s="18">
+      <c r="F98" s="13">
         <v>9</v>
       </c>
-      <c r="G98" s="20" t="s">
+      <c r="G98" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="H98" s="20">
+      <c r="H98" s="15">
         <v>9.5</v>
       </c>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A99" s="15">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A99" s="10">
         <v>3998</v>
       </c>
-      <c r="B99" s="18">
+      <c r="B99" s="13">
         <v>8</v>
       </c>
-      <c r="C99" s="17" t="s">
+      <c r="C99" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="D99" s="18">
+      <c r="D99" s="13">
         <v>50</v>
       </c>
-      <c r="E99" s="19" t="s">
+      <c r="E99" s="14" t="s">
         <v>112</v>
       </c>
-      <c r="F99" s="18">
+      <c r="F99" s="13">
         <v>10</v>
       </c>
-      <c r="G99" s="20">
+      <c r="G99" s="15">
         <v>3.5</v>
       </c>
-      <c r="H99" s="20">
+      <c r="H99" s="15">
         <v>13</v>
       </c>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A100" s="15">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A100" s="10">
         <v>3995</v>
       </c>
-      <c r="B100" s="18">
+      <c r="B100" s="13">
         <v>9</v>
       </c>
-      <c r="C100" s="17" t="s">
+      <c r="C100" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="D100" s="18">
+      <c r="D100" s="13">
         <v>52</v>
       </c>
-      <c r="E100" s="19" t="s">
+      <c r="E100" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="F100" s="18">
+      <c r="F100" s="13">
         <v>1</v>
       </c>
-      <c r="G100" s="20" t="s">
+      <c r="G100" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="H100" s="20" t="s">
+      <c r="H100" s="15" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A101" s="15">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A101" s="10">
         <v>3996</v>
       </c>
-      <c r="B101" s="18" t="s">
+      <c r="B101" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C101" s="17" t="s">
+      <c r="C101" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="D101" s="18">
+      <c r="D101" s="13">
         <v>52</v>
       </c>
-      <c r="E101" s="19" t="s">
+      <c r="E101" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="F101" s="18">
+      <c r="F101" s="13">
         <v>6</v>
       </c>
-      <c r="G101" s="20" t="s">
+      <c r="G101" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="H101" s="20" t="s">
+      <c r="H101" s="15" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="102" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A102" s="21"/>
-      <c r="B102" s="21"/>
-      <c r="D102" s="18"/>
-      <c r="E102" s="21"/>
-      <c r="F102" s="18"/>
-      <c r="G102" s="21"/>
-    </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B103" s="22" t="s">
+    <row r="102" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="16"/>
+      <c r="B102" s="16"/>
+      <c r="D102" s="13"/>
+      <c r="E102" s="16"/>
+      <c r="F102" s="13"/>
+      <c r="G102" s="16"/>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B103" s="17" t="s">
         <v>115</v>
       </c>
-      <c r="C103" s="8"/>
-      <c r="D103" s="8"/>
-      <c r="E103" s="8"/>
-      <c r="F103" s="8"/>
-      <c r="G103" s="8"/>
-    </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B104" s="22" t="s">
+      <c r="C103" s="5"/>
+      <c r="D103" s="5"/>
+      <c r="E103" s="5"/>
+      <c r="F103" s="5"/>
+      <c r="G103" s="5"/>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B104" s="17" t="s">
         <v>116</v>
       </c>
-      <c r="C104" s="8"/>
-      <c r="D104" s="8"/>
-      <c r="E104" s="8"/>
-      <c r="F104" s="8"/>
-      <c r="G104" s="8"/>
-    </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B105" s="22" t="s">
+      <c r="C104" s="5"/>
+      <c r="D104" s="5"/>
+      <c r="E104" s="5"/>
+      <c r="F104" s="5"/>
+      <c r="G104" s="5"/>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B105" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="C105" s="8"/>
-      <c r="D105" s="8"/>
-      <c r="E105" s="8"/>
-      <c r="F105" s="8"/>
-      <c r="G105" s="8"/>
-    </row>
-    <row r="106" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B106" s="22"/>
-      <c r="C106" s="21"/>
-      <c r="D106" s="21"/>
-      <c r="E106" s="21"/>
-      <c r="F106" s="21"/>
-      <c r="G106" s="21"/>
-    </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B107" s="23" t="s">
+      <c r="C105" s="5"/>
+      <c r="D105" s="5"/>
+      <c r="E105" s="5"/>
+      <c r="F105" s="5"/>
+      <c r="G105" s="5"/>
+    </row>
+    <row r="106" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B106" s="17"/>
+      <c r="C106" s="16"/>
+      <c r="D106" s="16"/>
+      <c r="E106" s="16"/>
+      <c r="F106" s="16"/>
+      <c r="G106" s="16"/>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B107" s="18" t="s">
         <v>118</v>
       </c>
-      <c r="C107" s="21"/>
-      <c r="D107" s="21"/>
-      <c r="E107" s="21"/>
-      <c r="F107" s="21"/>
-      <c r="G107" s="21"/>
-    </row>
-    <row r="108" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C108" s="21"/>
-      <c r="D108" s="21"/>
-      <c r="E108" s="21"/>
-      <c r="F108" s="21"/>
-      <c r="G108" s="21"/>
-    </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B109" s="23" t="s">
+      <c r="C107" s="16"/>
+      <c r="D107" s="16"/>
+      <c r="E107" s="16"/>
+      <c r="F107" s="16"/>
+      <c r="G107" s="16"/>
+    </row>
+    <row r="108" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C108" s="16"/>
+      <c r="D108" s="16"/>
+      <c r="E108" s="16"/>
+      <c r="F108" s="16"/>
+      <c r="G108" s="16"/>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B109" s="18" t="s">
         <v>119</v>
       </c>
-      <c r="C109" s="21"/>
-      <c r="D109" s="21"/>
-      <c r="E109" s="21"/>
-      <c r="F109" s="21"/>
-      <c r="G109" s="21"/>
-    </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B110" s="23" t="s">
+      <c r="C109" s="16"/>
+      <c r="D109" s="16"/>
+      <c r="E109" s="16"/>
+      <c r="F109" s="16"/>
+      <c r="G109" s="16"/>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B110" s="18" t="s">
         <v>120</v>
       </c>
-      <c r="C110" s="21"/>
-      <c r="D110" s="21"/>
-      <c r="E110" s="21"/>
-      <c r="F110" s="21"/>
-      <c r="G110" s="21"/>
-    </row>
-    <row r="111" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B111" s="23"/>
-      <c r="C111" s="21"/>
-      <c r="D111" s="21"/>
-      <c r="E111" s="21"/>
-      <c r="F111" s="21"/>
-      <c r="G111" s="21"/>
-    </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B112" s="22" t="s">
+      <c r="C110" s="16"/>
+      <c r="D110" s="16"/>
+      <c r="E110" s="16"/>
+      <c r="F110" s="16"/>
+      <c r="G110" s="16"/>
+    </row>
+    <row r="111" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B111" s="18"/>
+      <c r="C111" s="16"/>
+      <c r="D111" s="16"/>
+      <c r="E111" s="16"/>
+      <c r="F111" s="16"/>
+      <c r="G111" s="16"/>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B112" s="17" t="s">
         <v>121</v>
       </c>
-      <c r="C112" s="21"/>
-      <c r="D112" s="21"/>
-      <c r="E112" s="21"/>
-      <c r="F112" s="21"/>
-      <c r="G112" s="21"/>
-    </row>
-    <row r="113" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B113" s="8"/>
-      <c r="C113" s="21"/>
-      <c r="D113" s="21"/>
-      <c r="E113" s="21"/>
-      <c r="F113" s="21"/>
-      <c r="G113" s="21"/>
-    </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B114" s="22" t="s">
+      <c r="C112" s="16"/>
+      <c r="D112" s="16"/>
+      <c r="E112" s="16"/>
+      <c r="F112" s="16"/>
+      <c r="G112" s="16"/>
+    </row>
+    <row r="113" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B113" s="5"/>
+      <c r="C113" s="16"/>
+      <c r="D113" s="16"/>
+      <c r="E113" s="16"/>
+      <c r="F113" s="16"/>
+      <c r="G113" s="16"/>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B114" s="17" t="s">
         <v>122</v>
       </c>
-      <c r="E114" s="22" t="s">
+      <c r="E114" s="17" t="s">
         <v>123</v>
       </c>
-      <c r="F114" s="21"/>
-      <c r="G114" s="21"/>
-    </row>
-    <row r="115" spans="1:8" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B115" s="28"/>
-      <c r="C115" s="28"/>
-      <c r="D115" s="28"/>
-      <c r="E115" s="28"/>
-      <c r="F115" s="28"/>
-      <c r="G115" s="28"/>
-    </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B116" s="24"/>
-      <c r="C116" s="24"/>
-      <c r="D116" s="24"/>
-      <c r="E116" s="25"/>
-      <c r="F116" s="24"/>
-      <c r="G116" s="24"/>
-    </row>
-    <row r="117" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A117" s="6">
+      <c r="F114" s="16"/>
+      <c r="G114" s="16"/>
+    </row>
+    <row r="115" spans="1:8" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B115" s="31"/>
+      <c r="C115" s="31"/>
+      <c r="D115" s="31"/>
+      <c r="E115" s="31"/>
+      <c r="F115" s="31"/>
+      <c r="G115" s="31"/>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B116" s="19"/>
+      <c r="C116" s="19"/>
+      <c r="D116" s="19"/>
+      <c r="E116" s="20"/>
+      <c r="F116" s="19"/>
+      <c r="G116" s="19"/>
+    </row>
+    <row r="117" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A117" s="4">
         <v>4011</v>
       </c>
-      <c r="B117" s="7" t="s">
+      <c r="B117" s="29" t="s">
         <v>124</v>
       </c>
-      <c r="C117" s="7"/>
-      <c r="D117" s="7"/>
-      <c r="E117" s="7"/>
-      <c r="F117" s="7"/>
-      <c r="G117" s="7"/>
-      <c r="H117" s="8"/>
-    </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A118" s="9"/>
-      <c r="B118" s="10" t="s">
+      <c r="C117" s="29"/>
+      <c r="D117" s="29"/>
+      <c r="E117" s="29"/>
+      <c r="F117" s="29"/>
+      <c r="G117" s="29"/>
+      <c r="H117" s="5"/>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A118" s="6"/>
+      <c r="B118" s="26" t="s">
         <v>125</v>
       </c>
-      <c r="C118" s="10"/>
-      <c r="D118" s="10"/>
-      <c r="E118" s="10"/>
-      <c r="F118" s="10"/>
-      <c r="G118" s="10"/>
-      <c r="H118" s="9"/>
-    </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B119" s="12" t="s">
+      <c r="C118" s="26"/>
+      <c r="D118" s="26"/>
+      <c r="E118" s="26"/>
+      <c r="F118" s="26"/>
+      <c r="G118" s="26"/>
+      <c r="H118" s="6"/>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B119" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="C119" s="12"/>
-      <c r="D119" s="12"/>
-      <c r="E119" s="12"/>
-      <c r="F119" s="12"/>
-      <c r="G119" s="12"/>
-      <c r="H119" s="11"/>
-    </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B120" s="12" t="s">
+      <c r="C119" s="27"/>
+      <c r="D119" s="27"/>
+      <c r="E119" s="27"/>
+      <c r="F119" s="27"/>
+      <c r="G119" s="27"/>
+      <c r="H119" s="7"/>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B120" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="C120" s="12"/>
-      <c r="D120" s="12"/>
-      <c r="E120" s="12"/>
-      <c r="F120" s="12"/>
-      <c r="G120" s="12"/>
-      <c r="H120" s="11"/>
-    </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A121" s="5" t="s">
+      <c r="C120" s="27"/>
+      <c r="D120" s="27"/>
+      <c r="E120" s="27"/>
+      <c r="F120" s="27"/>
+      <c r="G120" s="27"/>
+      <c r="H120" s="7"/>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A121" s="28" t="s">
         <v>126</v>
       </c>
-      <c r="B121" s="5"/>
-      <c r="C121" s="5"/>
-      <c r="D121" s="5"/>
-      <c r="E121" s="5"/>
-      <c r="F121" s="5"/>
-      <c r="G121" s="5"/>
-      <c r="H121" s="5"/>
-    </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A122" s="5" t="s">
+      <c r="B121" s="28"/>
+      <c r="C121" s="28"/>
+      <c r="D121" s="28"/>
+      <c r="E121" s="28"/>
+      <c r="F121" s="28"/>
+      <c r="G121" s="28"/>
+      <c r="H121" s="28"/>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A122" s="28" t="s">
         <v>127</v>
       </c>
-      <c r="B122" s="5"/>
-      <c r="C122" s="5"/>
-      <c r="D122" s="5"/>
-      <c r="E122" s="5"/>
-      <c r="F122" s="5"/>
-      <c r="G122" s="5"/>
-      <c r="H122" s="5"/>
-    </row>
-    <row r="123" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B123" s="13"/>
-      <c r="C123" s="14"/>
-      <c r="D123" s="14"/>
-      <c r="E123" s="14"/>
-      <c r="F123" s="14"/>
-      <c r="G123" s="14"/>
-    </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A124" s="15">
+      <c r="B122" s="28"/>
+      <c r="C122" s="28"/>
+      <c r="D122" s="28"/>
+      <c r="E122" s="28"/>
+      <c r="F122" s="28"/>
+      <c r="G122" s="28"/>
+      <c r="H122" s="28"/>
+    </row>
+    <row r="123" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B123" s="8"/>
+      <c r="C123" s="9"/>
+      <c r="D123" s="9"/>
+      <c r="E123" s="9"/>
+      <c r="F123" s="9"/>
+      <c r="G123" s="9"/>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A124" s="10">
         <v>3989</v>
       </c>
-      <c r="B124" s="18">
+      <c r="B124" s="13">
         <v>1</v>
       </c>
-      <c r="C124" s="17" t="s">
+      <c r="C124" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="D124" s="18">
+      <c r="D124" s="13">
         <v>58</v>
       </c>
-      <c r="E124" s="19" t="s">
+      <c r="E124" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="F124" s="18">
+      <c r="F124" s="13">
         <v>8</v>
       </c>
-      <c r="G124" s="20"/>
-      <c r="H124" s="20"/>
-    </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A125" s="15">
+      <c r="G124" s="15"/>
+      <c r="H124" s="15"/>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A125" s="10">
         <v>0</v>
       </c>
-      <c r="B125" s="18">
+      <c r="B125" s="13">
         <v>2</v>
       </c>
-      <c r="C125" s="17" t="s">
+      <c r="C125" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="D125" s="18">
+      <c r="D125" s="13">
         <v>56</v>
       </c>
-      <c r="E125" s="19" t="s">
+      <c r="E125" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="F125" s="18">
+      <c r="F125" s="13">
         <v>4</v>
       </c>
-      <c r="G125" s="20">
+      <c r="G125" s="15">
         <v>2.5</v>
       </c>
-      <c r="H125" s="20"/>
-    </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A126" s="15">
+      <c r="H125" s="15">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A126" s="10">
         <v>3989</v>
       </c>
-      <c r="B126" s="18">
+      <c r="B126" s="13">
         <v>3</v>
       </c>
-      <c r="C126" s="17" t="s">
+      <c r="C126" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="D126" s="18">
+      <c r="D126" s="13">
         <v>60</v>
       </c>
-      <c r="E126" s="19" t="s">
+      <c r="E126" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="F126" s="18">
+      <c r="F126" s="13">
         <v>3</v>
       </c>
-      <c r="G126" s="20">
+      <c r="G126" s="15">
         <v>3.5</v>
       </c>
-      <c r="H126" s="20"/>
-    </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A127" s="15">
+      <c r="H126" s="15">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A127" s="10">
         <v>3845</v>
       </c>
-      <c r="B127" s="18">
+      <c r="B127" s="13">
         <v>4</v>
       </c>
-      <c r="C127" s="17" t="s">
+      <c r="C127" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="D127" s="18">
+      <c r="D127" s="13">
         <v>56</v>
       </c>
-      <c r="E127" s="19" t="s">
+      <c r="E127" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="F127" s="18">
+      <c r="F127" s="13">
         <v>2</v>
       </c>
-      <c r="G127" s="20" t="s">
+      <c r="G127" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="H127" s="20"/>
-    </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A128" s="15">
+      <c r="H127" s="15">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A128" s="10">
         <v>3977</v>
       </c>
-      <c r="B128" s="18">
+      <c r="B128" s="13">
         <v>5</v>
       </c>
-      <c r="C128" s="17" t="s">
+      <c r="C128" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="D128" s="18">
+      <c r="D128" s="13">
         <v>56</v>
       </c>
-      <c r="E128" s="19" t="s">
+      <c r="E128" s="14" t="s">
         <v>133</v>
       </c>
-      <c r="F128" s="18">
+      <c r="F128" s="13">
         <v>9</v>
       </c>
-      <c r="G128" s="20" t="s">
+      <c r="G128" s="15" t="s">
         <v>105</v>
       </c>
-      <c r="H128" s="20"/>
-    </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A129" s="15">
+      <c r="H128" s="15">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A129" s="10">
         <v>3810</v>
       </c>
-      <c r="B129" s="18">
+      <c r="B129" s="13">
         <v>6</v>
       </c>
-      <c r="C129" s="17" t="s">
+      <c r="C129" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="D129" s="18">
+      <c r="D129" s="13">
         <v>56</v>
       </c>
-      <c r="E129" s="19" t="s">
+      <c r="E129" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="F129" s="18">
+      <c r="F129" s="13">
         <v>1</v>
       </c>
-      <c r="G129" s="20">
+      <c r="G129" s="15">
         <v>1.5</v>
       </c>
-      <c r="H129" s="20"/>
-    </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A130" s="15">
+      <c r="H129" s="15">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A130" s="10">
         <v>3820</v>
       </c>
-      <c r="B130" s="18">
+      <c r="B130" s="13">
         <v>7</v>
       </c>
-      <c r="C130" s="17" t="s">
+      <c r="C130" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="D130" s="18">
+      <c r="D130" s="13">
         <v>58</v>
       </c>
-      <c r="E130" s="19" t="s">
+      <c r="E130" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="F130" s="18">
+      <c r="F130" s="13">
         <v>7</v>
       </c>
-      <c r="G130" s="20" t="s">
+      <c r="G130" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="H130" s="20"/>
-    </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A131" s="15">
+      <c r="H130" s="15">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A131" s="10">
         <v>3512</v>
       </c>
-      <c r="B131" s="18" t="s">
+      <c r="B131" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C131" s="17" t="s">
+      <c r="C131" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="D131" s="18">
+      <c r="D131" s="13">
         <v>56</v>
       </c>
-      <c r="E131" s="19" t="s">
+      <c r="E131" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="F131" s="18">
+      <c r="F131" s="13">
         <v>6</v>
       </c>
-      <c r="G131" s="20" t="s">
+      <c r="G131" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="H131" s="20"/>
-    </row>
-    <row r="132" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A132" s="21"/>
-      <c r="B132" s="21"/>
-      <c r="D132" s="18"/>
-      <c r="E132" s="21"/>
-      <c r="F132" s="18"/>
-      <c r="G132" s="20"/>
-    </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B133" s="22" t="s">
+      <c r="H131" s="15">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A132" s="16"/>
+      <c r="B132" s="16"/>
+      <c r="D132" s="13"/>
+      <c r="E132" s="16"/>
+      <c r="F132" s="13"/>
+      <c r="G132" s="15"/>
+    </row>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B133" s="17" t="s">
         <v>138</v>
       </c>
-      <c r="C133" s="8"/>
-      <c r="D133" s="8"/>
-      <c r="E133" s="8"/>
-      <c r="F133" s="8"/>
-      <c r="G133" s="8"/>
-    </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B134" s="22" t="s">
+      <c r="C133" s="5"/>
+      <c r="D133" s="5"/>
+      <c r="E133" s="5"/>
+      <c r="F133" s="5"/>
+      <c r="G133" s="5"/>
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B134" s="17" t="s">
         <v>139</v>
       </c>
-      <c r="C134" s="8"/>
-      <c r="D134" s="8"/>
-      <c r="E134" s="8"/>
-      <c r="F134" s="8"/>
-      <c r="G134" s="8"/>
-    </row>
-    <row r="135" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B135" s="22"/>
-      <c r="C135" s="21"/>
-      <c r="D135" s="21"/>
-      <c r="E135" s="21"/>
-      <c r="F135" s="21"/>
-      <c r="G135" s="21"/>
-    </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B136" s="23" t="s">
+      <c r="C134" s="5"/>
+      <c r="D134" s="5"/>
+      <c r="E134" s="5"/>
+      <c r="F134" s="5"/>
+      <c r="G134" s="5"/>
+    </row>
+    <row r="135" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B135" s="17"/>
+      <c r="C135" s="16"/>
+      <c r="D135" s="16"/>
+      <c r="E135" s="16"/>
+      <c r="F135" s="16"/>
+      <c r="G135" s="16"/>
+    </row>
+    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B136" s="18" t="s">
         <v>140</v>
       </c>
-      <c r="C136" s="21"/>
-      <c r="D136" s="21"/>
-      <c r="E136" s="21"/>
-      <c r="F136" s="21"/>
-      <c r="G136" s="21"/>
-    </row>
-    <row r="137" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C137" s="21"/>
-      <c r="D137" s="21"/>
-      <c r="E137" s="21"/>
-      <c r="F137" s="21"/>
-      <c r="G137" s="21"/>
-    </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B138" s="23" t="s">
+      <c r="C136" s="16"/>
+      <c r="D136" s="16"/>
+      <c r="E136" s="16"/>
+      <c r="F136" s="16"/>
+      <c r="G136" s="16"/>
+    </row>
+    <row r="137" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C137" s="16"/>
+      <c r="D137" s="16"/>
+      <c r="E137" s="16"/>
+      <c r="F137" s="16"/>
+      <c r="G137" s="16"/>
+    </row>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B138" s="18" t="s">
         <v>141</v>
       </c>
-      <c r="C138" s="21"/>
-      <c r="D138" s="21"/>
-      <c r="E138" s="21"/>
-      <c r="F138" s="21"/>
-      <c r="G138" s="21"/>
-    </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B139" s="23" t="s">
+      <c r="C138" s="16"/>
+      <c r="D138" s="16"/>
+      <c r="E138" s="16"/>
+      <c r="F138" s="16"/>
+      <c r="G138" s="16"/>
+    </row>
+    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B139" s="18" t="s">
         <v>142</v>
       </c>
-      <c r="C139" s="21"/>
-      <c r="D139" s="21"/>
-      <c r="E139" s="21"/>
-      <c r="F139" s="21"/>
-      <c r="G139" s="21"/>
-    </row>
-    <row r="140" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B140" s="23"/>
-      <c r="C140" s="21"/>
-      <c r="D140" s="21"/>
-      <c r="E140" s="21"/>
-      <c r="F140" s="21"/>
-      <c r="G140" s="21"/>
-    </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B141" s="22" t="s">
+      <c r="C139" s="16"/>
+      <c r="D139" s="16"/>
+      <c r="E139" s="16"/>
+      <c r="F139" s="16"/>
+      <c r="G139" s="16"/>
+    </row>
+    <row r="140" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B140" s="18"/>
+      <c r="C140" s="16"/>
+      <c r="D140" s="16"/>
+      <c r="E140" s="16"/>
+      <c r="F140" s="16"/>
+      <c r="G140" s="16"/>
+    </row>
+    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B141" s="17" t="s">
         <v>143</v>
       </c>
-      <c r="C141" s="21"/>
-      <c r="D141" s="21"/>
-      <c r="E141" s="21"/>
-      <c r="F141" s="21"/>
-      <c r="G141" s="21"/>
-    </row>
-    <row r="142" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B142" s="8"/>
-      <c r="C142" s="21"/>
-      <c r="D142" s="21"/>
-      <c r="E142" s="21"/>
-      <c r="F142" s="21"/>
-      <c r="G142" s="21"/>
-    </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B143" s="22" t="s">
+      <c r="C141" s="16"/>
+      <c r="D141" s="16"/>
+      <c r="E141" s="16"/>
+      <c r="F141" s="16"/>
+      <c r="G141" s="16"/>
+    </row>
+    <row r="142" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B142" s="5"/>
+      <c r="C142" s="16"/>
+      <c r="D142" s="16"/>
+      <c r="E142" s="16"/>
+      <c r="F142" s="16"/>
+      <c r="G142" s="16"/>
+    </row>
+    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B143" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="E143" s="22" t="s">
+      <c r="E143" s="17" t="s">
         <v>144</v>
       </c>
-      <c r="F143" s="21"/>
-      <c r="G143" s="21"/>
-    </row>
-    <row r="144" spans="1:8" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B144" s="22"/>
-      <c r="E144" s="22"/>
-      <c r="F144" s="21"/>
-      <c r="G144" s="21"/>
-    </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B145" s="24"/>
-      <c r="C145" s="24"/>
-      <c r="D145" s="24"/>
-      <c r="E145" s="25"/>
-      <c r="F145" s="24"/>
-      <c r="G145" s="24"/>
-    </row>
-    <row r="146" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A146" s="6">
+      <c r="F143" s="16"/>
+      <c r="G143" s="16"/>
+    </row>
+    <row r="144" spans="1:8" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B144" s="17"/>
+      <c r="E144" s="17"/>
+      <c r="F144" s="16"/>
+      <c r="G144" s="16"/>
+    </row>
+    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B145" s="19"/>
+      <c r="C145" s="19"/>
+      <c r="D145" s="19"/>
+      <c r="E145" s="20"/>
+      <c r="F145" s="19"/>
+      <c r="G145" s="19"/>
+    </row>
+    <row r="146" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A146" s="4">
         <v>4012</v>
       </c>
-      <c r="B146" s="7" t="s">
+      <c r="B146" s="29" t="s">
         <v>145</v>
       </c>
-      <c r="C146" s="7"/>
-      <c r="D146" s="7"/>
-      <c r="E146" s="7"/>
-      <c r="F146" s="7"/>
-      <c r="G146" s="7"/>
-      <c r="H146" s="8"/>
-    </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A147" s="9"/>
-      <c r="B147" s="10" t="s">
+      <c r="C146" s="29"/>
+      <c r="D146" s="29"/>
+      <c r="E146" s="29"/>
+      <c r="F146" s="29"/>
+      <c r="G146" s="29"/>
+      <c r="H146" s="5"/>
+    </row>
+    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A147" s="6"/>
+      <c r="B147" s="26" t="s">
         <v>146</v>
       </c>
-      <c r="C147" s="10"/>
-      <c r="D147" s="10"/>
-      <c r="E147" s="10"/>
-      <c r="F147" s="10"/>
-      <c r="G147" s="10"/>
-      <c r="H147" s="9"/>
-    </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B148" s="12" t="s">
+      <c r="C147" s="26"/>
+      <c r="D147" s="26"/>
+      <c r="E147" s="26"/>
+      <c r="F147" s="26"/>
+      <c r="G147" s="26"/>
+      <c r="H147" s="6"/>
+    </row>
+    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B148" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="C148" s="12"/>
-      <c r="D148" s="12"/>
-      <c r="E148" s="12"/>
-      <c r="F148" s="12"/>
-      <c r="G148" s="12"/>
-      <c r="H148" s="11"/>
-    </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B149" s="12" t="s">
+      <c r="C148" s="27"/>
+      <c r="D148" s="27"/>
+      <c r="E148" s="27"/>
+      <c r="F148" s="27"/>
+      <c r="G148" s="27"/>
+      <c r="H148" s="7"/>
+    </row>
+    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B149" s="27" t="s">
         <v>94</v>
       </c>
-      <c r="C149" s="12"/>
-      <c r="D149" s="12"/>
-      <c r="E149" s="12"/>
-      <c r="F149" s="12"/>
-      <c r="G149" s="12"/>
-      <c r="H149" s="11"/>
-    </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A150" s="5" t="s">
+      <c r="C149" s="27"/>
+      <c r="D149" s="27"/>
+      <c r="E149" s="27"/>
+      <c r="F149" s="27"/>
+      <c r="G149" s="27"/>
+      <c r="H149" s="7"/>
+    </row>
+    <row r="150" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A150" s="28" t="s">
         <v>147</v>
       </c>
-      <c r="B150" s="5"/>
-      <c r="C150" s="5"/>
-      <c r="D150" s="5"/>
-      <c r="E150" s="5"/>
-      <c r="F150" s="5"/>
-      <c r="G150" s="5"/>
-      <c r="H150" s="5"/>
-    </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A151" s="5" t="s">
+      <c r="B150" s="28"/>
+      <c r="C150" s="28"/>
+      <c r="D150" s="28"/>
+      <c r="E150" s="28"/>
+      <c r="F150" s="28"/>
+      <c r="G150" s="28"/>
+      <c r="H150" s="28"/>
+    </row>
+    <row r="151" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A151" s="28" t="s">
         <v>148</v>
       </c>
-      <c r="B151" s="5"/>
-      <c r="C151" s="5"/>
-      <c r="D151" s="5"/>
-      <c r="E151" s="5"/>
-      <c r="F151" s="5"/>
-      <c r="G151" s="5"/>
-      <c r="H151" s="5"/>
-    </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A152" s="5" t="s">
+      <c r="B151" s="28"/>
+      <c r="C151" s="28"/>
+      <c r="D151" s="28"/>
+      <c r="E151" s="28"/>
+      <c r="F151" s="28"/>
+      <c r="G151" s="28"/>
+      <c r="H151" s="28"/>
+    </row>
+    <row r="152" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A152" s="28" t="s">
         <v>149</v>
       </c>
-      <c r="B152" s="5"/>
-      <c r="C152" s="5"/>
-      <c r="D152" s="5"/>
-      <c r="E152" s="5"/>
-      <c r="F152" s="5"/>
-      <c r="G152" s="5"/>
-      <c r="H152" s="5"/>
-    </row>
-    <row r="153" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B153" s="13"/>
-      <c r="C153" s="14"/>
-      <c r="D153" s="14"/>
-      <c r="E153" s="14"/>
-      <c r="F153" s="14"/>
-      <c r="G153" s="14"/>
-    </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A154" s="15">
+      <c r="B152" s="28"/>
+      <c r="C152" s="28"/>
+      <c r="D152" s="28"/>
+      <c r="E152" s="28"/>
+      <c r="F152" s="28"/>
+      <c r="G152" s="28"/>
+      <c r="H152" s="28"/>
+    </row>
+    <row r="153" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B153" s="8"/>
+      <c r="C153" s="9"/>
+      <c r="D153" s="9"/>
+      <c r="E153" s="9"/>
+      <c r="F153" s="9"/>
+      <c r="G153" s="9"/>
+    </row>
+    <row r="154" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A154" s="10">
         <v>4005</v>
       </c>
-      <c r="B154" s="18">
+      <c r="B154" s="13">
         <v>1</v>
       </c>
-      <c r="C154" s="17" t="s">
+      <c r="C154" s="12" t="s">
         <v>150</v>
       </c>
-      <c r="D154" s="18">
+      <c r="D154" s="13">
         <v>52</v>
       </c>
-      <c r="E154" s="19" t="s">
+      <c r="E154" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="F154" s="18">
+      <c r="F154" s="13">
         <v>9</v>
       </c>
-      <c r="G154" s="20"/>
-      <c r="H154" s="20"/>
-    </row>
-    <row r="155" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A155" s="15">
+      <c r="G154" s="15"/>
+      <c r="H154" s="15"/>
+    </row>
+    <row r="155" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A155" s="10">
         <v>4004</v>
       </c>
-      <c r="B155" s="18">
+      <c r="B155" s="13">
         <v>2</v>
       </c>
-      <c r="C155" s="17" t="s">
+      <c r="C155" s="12" t="s">
         <v>151</v>
       </c>
-      <c r="D155" s="18">
+      <c r="D155" s="13">
         <v>56</v>
       </c>
-      <c r="E155" s="19" t="s">
+      <c r="E155" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="F155" s="18">
+      <c r="F155" s="13">
         <v>1</v>
       </c>
-      <c r="G155" s="20" t="s">
+      <c r="G155" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="H155" s="20">
+      <c r="H155" s="15">
         <v>0.25</v>
       </c>
     </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A156" s="15">
+    <row r="156" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A156" s="10">
         <v>3993</v>
       </c>
-      <c r="B156" s="18">
+      <c r="B156" s="13">
         <v>3</v>
       </c>
-      <c r="C156" s="17" t="s">
+      <c r="C156" s="12" t="s">
         <v>152</v>
       </c>
-      <c r="D156" s="18">
+      <c r="D156" s="13">
         <v>54</v>
       </c>
-      <c r="E156" s="19" t="s">
+      <c r="E156" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="F156" s="18">
+      <c r="F156" s="13">
         <v>5</v>
       </c>
-      <c r="G156" s="20" t="s">
+      <c r="G156" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="H156" s="20">
+      <c r="H156" s="15">
         <v>6.25</v>
       </c>
     </row>
-    <row r="157" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A157" s="15">
+    <row r="157" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A157" s="10">
         <v>4006</v>
       </c>
-      <c r="B157" s="18">
+      <c r="B157" s="13">
         <v>4</v>
       </c>
-      <c r="C157" s="17" t="s">
+      <c r="C157" s="12" t="s">
         <v>153</v>
       </c>
-      <c r="D157" s="18">
+      <c r="D157" s="13">
         <v>50</v>
       </c>
-      <c r="E157" s="19" t="s">
+      <c r="E157" s="14" t="s">
         <v>154</v>
       </c>
-      <c r="F157" s="18">
+      <c r="F157" s="13">
         <v>8</v>
       </c>
-      <c r="G157" s="20" t="s">
+      <c r="G157" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="H157" s="20">
+      <c r="H157" s="15">
         <v>10.25</v>
       </c>
     </row>
-    <row r="158" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A158" s="15">
+    <row r="158" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A158" s="10">
         <v>3993</v>
       </c>
-      <c r="B158" s="18">
+      <c r="B158" s="13">
         <v>5</v>
       </c>
-      <c r="C158" s="17" t="s">
+      <c r="C158" s="12" t="s">
         <v>155</v>
       </c>
-      <c r="D158" s="18">
+      <c r="D158" s="13">
         <v>56</v>
       </c>
-      <c r="E158" s="19" t="s">
+      <c r="E158" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="F158" s="18">
+      <c r="F158" s="13">
         <v>2</v>
       </c>
-      <c r="G158" s="20" t="s">
+      <c r="G158" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="H158" s="20">
+      <c r="H158" s="15">
         <v>12.25</v>
       </c>
     </row>
-    <row r="159" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A159" s="15">
+    <row r="159" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A159" s="10">
         <v>4006</v>
       </c>
-      <c r="B159" s="18">
+      <c r="B159" s="13">
         <v>6</v>
       </c>
-      <c r="C159" s="17" t="s">
+      <c r="C159" s="12" t="s">
         <v>156</v>
       </c>
-      <c r="D159" s="18">
+      <c r="D159" s="13">
         <v>52</v>
       </c>
-      <c r="E159" s="19" t="s">
+      <c r="E159" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="F159" s="18">
+      <c r="F159" s="13">
         <v>10</v>
       </c>
-      <c r="G159" s="20">
+      <c r="G159" s="15">
         <v>3.5</v>
       </c>
-      <c r="H159" s="20">
+      <c r="H159" s="15">
         <v>15.75</v>
       </c>
     </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A160" s="15">
+    <row r="160" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A160" s="10">
         <v>4005</v>
       </c>
-      <c r="B160" s="18">
+      <c r="B160" s="13">
         <v>7</v>
       </c>
-      <c r="C160" s="17" t="s">
+      <c r="C160" s="12" t="s">
         <v>157</v>
       </c>
-      <c r="D160" s="18">
+      <c r="D160" s="13">
         <v>52</v>
       </c>
-      <c r="E160" s="19" t="s">
+      <c r="E160" s="14" t="s">
         <v>112</v>
       </c>
-      <c r="F160" s="18">
+      <c r="F160" s="13">
         <v>4</v>
       </c>
-      <c r="G160" s="20">
+      <c r="G160" s="15">
         <v>1.5</v>
       </c>
-      <c r="H160" s="20">
+      <c r="H160" s="15">
         <v>17.25</v>
       </c>
     </row>
-    <row r="161" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A161" s="15">
+    <row r="161" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A161" s="10">
         <v>4006</v>
       </c>
-      <c r="B161" s="18">
+      <c r="B161" s="13">
         <v>8</v>
       </c>
-      <c r="C161" s="17" t="s">
+      <c r="C161" s="12" t="s">
         <v>158</v>
       </c>
-      <c r="D161" s="18">
+      <c r="D161" s="13">
         <v>54</v>
       </c>
-      <c r="E161" s="19" t="s">
+      <c r="E161" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="F161" s="18">
+      <c r="F161" s="13">
         <v>7</v>
       </c>
-      <c r="G161" s="20" t="s">
+      <c r="G161" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="H161" s="20">
+      <c r="H161" s="15">
         <v>21.25</v>
       </c>
     </row>
-    <row r="162" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A162" s="15">
+    <row r="162" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A162" s="10">
         <v>4006</v>
       </c>
-      <c r="B162" s="18">
+      <c r="B162" s="13">
         <v>9</v>
       </c>
-      <c r="C162" s="17" t="s">
+      <c r="C162" s="12" t="s">
         <v>159</v>
       </c>
-      <c r="D162" s="18">
+      <c r="D162" s="13">
         <v>54</v>
       </c>
-      <c r="E162" s="19" t="s">
+      <c r="E162" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="F162" s="18">
+      <c r="F162" s="13">
         <v>3</v>
       </c>
-      <c r="G162" s="20" t="s">
+      <c r="G162" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="H162" s="20">
+      <c r="H162" s="15">
         <v>31.25</v>
       </c>
     </row>
-    <row r="163" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A163" s="15">
+    <row r="163" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A163" s="10">
         <v>4006</v>
       </c>
-      <c r="B163" s="18" t="s">
+      <c r="B163" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C163" s="17" t="s">
+      <c r="C163" s="12" t="s">
         <v>160</v>
       </c>
-      <c r="D163" s="18">
+      <c r="D163" s="13">
         <v>54</v>
       </c>
-      <c r="E163" s="19" t="s">
+      <c r="E163" s="14" t="s">
         <v>133</v>
       </c>
-      <c r="F163" s="18">
+      <c r="F163" s="13">
         <v>6</v>
       </c>
-      <c r="G163" s="20" t="s">
+      <c r="G163" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="H163" s="20">
+      <c r="H163" s="15">
         <v>34.25</v>
       </c>
     </row>
-    <row r="164" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A164" s="21"/>
-      <c r="B164" s="21"/>
-      <c r="D164" s="18"/>
-      <c r="E164" s="21"/>
-      <c r="F164" s="18"/>
-      <c r="G164" s="20"/>
-    </row>
-    <row r="165" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B165" s="22" t="s">
+    <row r="164" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A164" s="16"/>
+      <c r="B164" s="16"/>
+      <c r="D164" s="13"/>
+      <c r="E164" s="16"/>
+      <c r="F164" s="13"/>
+      <c r="G164" s="15"/>
+    </row>
+    <row r="165" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B165" s="17" t="s">
         <v>161</v>
       </c>
-      <c r="C165" s="8"/>
-      <c r="D165" s="8"/>
-      <c r="E165" s="8"/>
-      <c r="F165" s="8"/>
-      <c r="G165" s="8"/>
-    </row>
-    <row r="166" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B166" s="22" t="s">
+      <c r="C165" s="5"/>
+      <c r="D165" s="5"/>
+      <c r="E165" s="5"/>
+      <c r="F165" s="5"/>
+      <c r="G165" s="5"/>
+    </row>
+    <row r="166" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B166" s="17" t="s">
         <v>162</v>
       </c>
-      <c r="C166" s="8"/>
-      <c r="D166" s="8"/>
-      <c r="E166" s="8"/>
-      <c r="F166" s="8"/>
-      <c r="G166" s="8"/>
-    </row>
-    <row r="167" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B167" s="22"/>
-      <c r="C167" s="21"/>
-      <c r="D167" s="21"/>
-      <c r="E167" s="21"/>
-      <c r="F167" s="21"/>
-      <c r="G167" s="21"/>
-    </row>
-    <row r="168" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B168" s="23" t="s">
+      <c r="C166" s="5"/>
+      <c r="D166" s="5"/>
+      <c r="E166" s="5"/>
+      <c r="F166" s="5"/>
+      <c r="G166" s="5"/>
+    </row>
+    <row r="167" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B167" s="17"/>
+      <c r="C167" s="16"/>
+      <c r="D167" s="16"/>
+      <c r="E167" s="16"/>
+      <c r="F167" s="16"/>
+      <c r="G167" s="16"/>
+    </row>
+    <row r="168" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B168" s="18" t="s">
         <v>163</v>
       </c>
-      <c r="C168" s="21"/>
-      <c r="D168" s="21"/>
-      <c r="E168" s="21"/>
-      <c r="F168" s="21"/>
-      <c r="G168" s="21"/>
-    </row>
-    <row r="169" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C169" s="21"/>
-      <c r="D169" s="21"/>
-      <c r="E169" s="21"/>
-      <c r="F169" s="21"/>
-      <c r="G169" s="21"/>
-    </row>
-    <row r="170" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B170" s="23" t="s">
+      <c r="C168" s="16"/>
+      <c r="D168" s="16"/>
+      <c r="E168" s="16"/>
+      <c r="F168" s="16"/>
+      <c r="G168" s="16"/>
+    </row>
+    <row r="169" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C169" s="16"/>
+      <c r="D169" s="16"/>
+      <c r="E169" s="16"/>
+      <c r="F169" s="16"/>
+      <c r="G169" s="16"/>
+    </row>
+    <row r="170" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B170" s="18" t="s">
         <v>164</v>
       </c>
-      <c r="C170" s="21"/>
-      <c r="D170" s="21"/>
-      <c r="E170" s="21"/>
-      <c r="F170" s="21"/>
-      <c r="G170" s="21"/>
-    </row>
-    <row r="171" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B171" s="23" t="s">
+      <c r="C170" s="16"/>
+      <c r="D170" s="16"/>
+      <c r="E170" s="16"/>
+      <c r="F170" s="16"/>
+      <c r="G170" s="16"/>
+    </row>
+    <row r="171" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B171" s="18" t="s">
         <v>165</v>
       </c>
-      <c r="C171" s="21"/>
-      <c r="D171" s="21"/>
-      <c r="E171" s="21"/>
-      <c r="F171" s="21"/>
-      <c r="G171" s="21"/>
-    </row>
-    <row r="172" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B172" s="23"/>
-      <c r="C172" s="21"/>
-      <c r="D172" s="21"/>
-      <c r="E172" s="21"/>
-      <c r="F172" s="21"/>
-      <c r="G172" s="21"/>
-    </row>
-    <row r="173" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B173" s="22" t="s">
+      <c r="C171" s="16"/>
+      <c r="D171" s="16"/>
+      <c r="E171" s="16"/>
+      <c r="F171" s="16"/>
+      <c r="G171" s="16"/>
+    </row>
+    <row r="172" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B172" s="18"/>
+      <c r="C172" s="16"/>
+      <c r="D172" s="16"/>
+      <c r="E172" s="16"/>
+      <c r="F172" s="16"/>
+      <c r="G172" s="16"/>
+    </row>
+    <row r="173" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B173" s="17" t="s">
         <v>166</v>
       </c>
-      <c r="C173" s="21"/>
-      <c r="D173" s="21"/>
-      <c r="E173" s="21"/>
-      <c r="F173" s="21"/>
-      <c r="G173" s="21"/>
-    </row>
-    <row r="174" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B174" s="8"/>
-      <c r="C174" s="21"/>
-      <c r="D174" s="21"/>
-      <c r="E174" s="21"/>
-      <c r="F174" s="21"/>
-      <c r="G174" s="21"/>
-    </row>
-    <row r="175" spans="1:8" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B175" s="22" t="s">
+      <c r="C173" s="16"/>
+      <c r="D173" s="16"/>
+      <c r="E173" s="16"/>
+      <c r="F173" s="16"/>
+      <c r="G173" s="16"/>
+    </row>
+    <row r="174" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B174" s="5"/>
+      <c r="C174" s="16"/>
+      <c r="D174" s="16"/>
+      <c r="E174" s="16"/>
+      <c r="F174" s="16"/>
+      <c r="G174" s="16"/>
+    </row>
+    <row r="175" spans="1:8" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B175" s="17" t="s">
         <v>167</v>
       </c>
-      <c r="E175" s="22" t="s">
+      <c r="E175" s="17" t="s">
         <v>168</v>
       </c>
-      <c r="F175" s="21"/>
-      <c r="G175" s="21"/>
-    </row>
-    <row r="176" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B176" s="24"/>
-      <c r="C176" s="24"/>
-      <c r="D176" s="24"/>
-      <c r="E176" s="25"/>
-      <c r="F176" s="24"/>
-      <c r="G176" s="24"/>
-    </row>
-    <row r="177" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A177" s="6">
+      <c r="F175" s="16"/>
+      <c r="G175" s="16"/>
+    </row>
+    <row r="176" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B176" s="19"/>
+      <c r="C176" s="19"/>
+      <c r="D176" s="19"/>
+      <c r="E176" s="20"/>
+      <c r="F176" s="19"/>
+      <c r="G176" s="19"/>
+    </row>
+    <row r="177" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A177" s="4">
         <v>4013</v>
       </c>
-      <c r="B177" s="7" t="s">
+      <c r="B177" s="29" t="s">
         <v>169</v>
       </c>
-      <c r="C177" s="7"/>
-      <c r="D177" s="7"/>
-      <c r="E177" s="7"/>
-      <c r="F177" s="7"/>
-      <c r="G177" s="7"/>
-      <c r="H177" s="8"/>
-    </row>
-    <row r="178" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A178" s="9"/>
-      <c r="B178" s="10" t="s">
+      <c r="C177" s="29"/>
+      <c r="D177" s="29"/>
+      <c r="E177" s="29"/>
+      <c r="F177" s="29"/>
+      <c r="G177" s="29"/>
+      <c r="H177" s="5"/>
+    </row>
+    <row r="178" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A178" s="6"/>
+      <c r="B178" s="26" t="s">
         <v>170</v>
       </c>
-      <c r="C178" s="10"/>
-      <c r="D178" s="10"/>
-      <c r="E178" s="10"/>
-      <c r="F178" s="10"/>
-      <c r="G178" s="10"/>
-      <c r="H178" s="9"/>
-    </row>
-    <row r="179" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B179" s="12" t="s">
+      <c r="C178" s="26"/>
+      <c r="D178" s="26"/>
+      <c r="E178" s="26"/>
+      <c r="F178" s="26"/>
+      <c r="G178" s="26"/>
+      <c r="H178" s="6"/>
+    </row>
+    <row r="179" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B179" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="C179" s="12"/>
-      <c r="D179" s="12"/>
-      <c r="E179" s="12"/>
-      <c r="F179" s="12"/>
-      <c r="G179" s="12"/>
-      <c r="H179" s="11"/>
-    </row>
-    <row r="180" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B180" s="12" t="s">
+      <c r="C179" s="27"/>
+      <c r="D179" s="27"/>
+      <c r="E179" s="27"/>
+      <c r="F179" s="27"/>
+      <c r="G179" s="27"/>
+      <c r="H179" s="7"/>
+    </row>
+    <row r="180" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B180" s="27" t="s">
         <v>171</v>
       </c>
-      <c r="C180" s="12"/>
-      <c r="D180" s="12"/>
-      <c r="E180" s="12"/>
-      <c r="F180" s="12"/>
-      <c r="G180" s="12"/>
-      <c r="H180" s="11"/>
-    </row>
-    <row r="181" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A181" s="26" t="s">
+      <c r="C180" s="27"/>
+      <c r="D180" s="27"/>
+      <c r="E180" s="27"/>
+      <c r="F180" s="27"/>
+      <c r="G180" s="27"/>
+      <c r="H180" s="7"/>
+    </row>
+    <row r="181" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A181" s="30" t="s">
         <v>172</v>
       </c>
-      <c r="B181" s="5"/>
-      <c r="C181" s="5"/>
-      <c r="D181" s="5"/>
-      <c r="E181" s="5"/>
-      <c r="F181" s="5"/>
-      <c r="G181" s="5"/>
-      <c r="H181" s="5"/>
-    </row>
-    <row r="182" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B182" s="13"/>
-      <c r="C182" s="14"/>
-      <c r="D182" s="14"/>
-      <c r="E182" s="14"/>
-      <c r="F182" s="14"/>
-      <c r="G182" s="14"/>
-    </row>
-    <row r="183" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A183" s="15">
+      <c r="B181" s="28"/>
+      <c r="C181" s="28"/>
+      <c r="D181" s="28"/>
+      <c r="E181" s="28"/>
+      <c r="F181" s="28"/>
+      <c r="G181" s="28"/>
+      <c r="H181" s="28"/>
+    </row>
+    <row r="182" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B182" s="8"/>
+      <c r="C182" s="9"/>
+      <c r="D182" s="9"/>
+      <c r="E182" s="9"/>
+      <c r="F182" s="9"/>
+      <c r="G182" s="9"/>
+    </row>
+    <row r="183" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A183" s="10">
         <v>3997</v>
       </c>
-      <c r="B183" s="18">
+      <c r="B183" s="13">
         <v>1</v>
       </c>
-      <c r="C183" s="17" t="s">
+      <c r="C183" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="D183" s="18">
+      <c r="D183" s="13">
         <v>56</v>
       </c>
-      <c r="E183" s="19" t="s">
+      <c r="E183" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="F183" s="18">
+      <c r="F183" s="13">
         <v>6</v>
       </c>
-      <c r="G183" s="20"/>
-      <c r="H183" s="20"/>
-    </row>
-    <row r="184" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A184" s="15">
+      <c r="G183" s="15"/>
+      <c r="H183" s="15"/>
+    </row>
+    <row r="184" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A184" s="10">
         <v>3986</v>
       </c>
-      <c r="B184" s="18">
+      <c r="B184" s="13">
         <v>2</v>
       </c>
-      <c r="C184" s="17" t="s">
+      <c r="C184" s="12" t="s">
         <v>174</v>
       </c>
-      <c r="D184" s="18">
+      <c r="D184" s="13">
         <v>56</v>
       </c>
-      <c r="E184" s="19" t="s">
+      <c r="E184" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="F184" s="18">
+      <c r="F184" s="13">
         <v>5</v>
       </c>
-      <c r="G184" s="20">
+      <c r="G184" s="15">
         <v>2.5</v>
       </c>
-      <c r="H184" s="20">
+      <c r="H184" s="15">
         <v>2.5</v>
       </c>
     </row>
-    <row r="185" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A185" s="15">
+    <row r="185" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A185" s="10">
         <v>3997</v>
       </c>
-      <c r="B185" s="18">
+      <c r="B185" s="13">
         <v>3</v>
       </c>
-      <c r="C185" s="17" t="s">
+      <c r="C185" s="12" t="s">
         <v>175</v>
       </c>
-      <c r="D185" s="18">
+      <c r="D185" s="13">
         <v>56</v>
       </c>
-      <c r="E185" s="19" t="s">
+      <c r="E185" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="F185" s="18">
+      <c r="F185" s="13">
         <v>1</v>
       </c>
-      <c r="G185" s="20" t="s">
+      <c r="G185" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="H185" s="20">
+      <c r="H185" s="15">
         <v>6.5</v>
       </c>
     </row>
-    <row r="186" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A186" s="15">
+    <row r="186" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A186" s="10">
         <v>3997</v>
       </c>
-      <c r="B186" s="18">
+      <c r="B186" s="13">
         <v>4</v>
       </c>
-      <c r="C186" s="17" t="s">
+      <c r="C186" s="12" t="s">
         <v>176</v>
       </c>
-      <c r="D186" s="18">
+      <c r="D186" s="13">
         <v>56</v>
       </c>
-      <c r="E186" s="19" t="s">
+      <c r="E186" s="14" t="s">
         <v>133</v>
       </c>
-      <c r="F186" s="18">
+      <c r="F186" s="13">
         <v>7</v>
       </c>
-      <c r="G186" s="20" t="s">
+      <c r="G186" s="15" t="s">
         <v>105</v>
       </c>
-      <c r="H186" s="20">
+      <c r="H186" s="15">
         <v>7</v>
       </c>
     </row>
-    <row r="187" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A187" s="15">
+    <row r="187" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A187" s="10">
         <v>3997</v>
       </c>
-      <c r="B187" s="18">
+      <c r="B187" s="13">
         <v>5</v>
       </c>
-      <c r="C187" s="17" t="s">
+      <c r="C187" s="12" t="s">
         <v>177</v>
       </c>
-      <c r="D187" s="18">
+      <c r="D187" s="13">
         <v>56</v>
       </c>
-      <c r="E187" s="19" t="s">
+      <c r="E187" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="F187" s="18">
+      <c r="F187" s="13">
         <v>4</v>
       </c>
-      <c r="G187" s="20">
+      <c r="G187" s="15">
         <v>1.5</v>
       </c>
-      <c r="H187" s="20">
+      <c r="H187" s="15">
         <v>8.5</v>
       </c>
     </row>
-    <row r="188" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A188" s="15">
+    <row r="188" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A188" s="10">
         <v>3986</v>
       </c>
-      <c r="B188" s="18">
+      <c r="B188" s="13">
         <v>6</v>
       </c>
-      <c r="C188" s="17" t="s">
+      <c r="C188" s="12" t="s">
         <v>178</v>
       </c>
-      <c r="D188" s="18">
+      <c r="D188" s="13">
         <v>56</v>
       </c>
-      <c r="E188" s="19" t="s">
+      <c r="E188" s="14" t="s">
         <v>112</v>
       </c>
-      <c r="F188" s="18">
+      <c r="F188" s="13">
         <v>2</v>
       </c>
-      <c r="G188" s="20" t="s">
+      <c r="G188" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="H188" s="20">
+      <c r="H188" s="15">
         <v>15.5</v>
       </c>
     </row>
-    <row r="189" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A189" s="15">
+    <row r="189" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A189" s="10">
         <v>3986</v>
       </c>
-      <c r="B189" s="18" t="s">
+      <c r="B189" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C189" s="17" t="s">
+      <c r="C189" s="12" t="s">
         <v>179</v>
       </c>
-      <c r="D189" s="18">
+      <c r="D189" s="13">
         <v>56</v>
       </c>
-      <c r="E189" s="19" t="s">
+      <c r="E189" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="F189" s="18">
+      <c r="F189" s="13">
         <v>3</v>
       </c>
-      <c r="G189" s="20" t="s">
+      <c r="G189" s="15" t="s">
         <v>180</v>
       </c>
-      <c r="H189" s="20">
+      <c r="H189" s="15">
         <v>27.5</v>
       </c>
     </row>
-    <row r="190" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A190" s="21"/>
-      <c r="B190" s="21"/>
-      <c r="D190" s="18"/>
-      <c r="E190" s="21"/>
-      <c r="F190" s="18"/>
-      <c r="G190" s="20"/>
-    </row>
-    <row r="191" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B191" s="22" t="s">
+    <row r="190" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A190" s="16"/>
+      <c r="B190" s="16"/>
+      <c r="D190" s="13"/>
+      <c r="E190" s="16"/>
+      <c r="F190" s="13"/>
+      <c r="G190" s="15"/>
+    </row>
+    <row r="191" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B191" s="17" t="s">
         <v>181</v>
       </c>
-      <c r="C191" s="8"/>
-      <c r="D191" s="8"/>
-      <c r="E191" s="8"/>
-      <c r="F191" s="8"/>
-      <c r="G191" s="8"/>
-    </row>
-    <row r="192" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B192" s="22" t="s">
+      <c r="C191" s="5"/>
+      <c r="D191" s="5"/>
+      <c r="E191" s="5"/>
+      <c r="F191" s="5"/>
+      <c r="G191" s="5"/>
+    </row>
+    <row r="192" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B192" s="17" t="s">
         <v>182</v>
       </c>
-      <c r="C192" s="8"/>
-      <c r="D192" s="8"/>
-      <c r="E192" s="8"/>
-      <c r="F192" s="8"/>
-      <c r="G192" s="8"/>
-    </row>
-    <row r="193" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B193" s="22"/>
-      <c r="C193" s="21"/>
-      <c r="D193" s="21"/>
-      <c r="E193" s="21"/>
-      <c r="F193" s="21"/>
-      <c r="G193" s="21"/>
-    </row>
-    <row r="194" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B194" s="23" t="s">
+      <c r="C192" s="5"/>
+      <c r="D192" s="5"/>
+      <c r="E192" s="5"/>
+      <c r="F192" s="5"/>
+      <c r="G192" s="5"/>
+    </row>
+    <row r="193" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B193" s="17"/>
+      <c r="C193" s="16"/>
+      <c r="D193" s="16"/>
+      <c r="E193" s="16"/>
+      <c r="F193" s="16"/>
+      <c r="G193" s="16"/>
+    </row>
+    <row r="194" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B194" s="18" t="s">
         <v>183</v>
       </c>
-      <c r="C194" s="21"/>
-      <c r="D194" s="21"/>
-      <c r="E194" s="21"/>
-      <c r="F194" s="21"/>
-      <c r="G194" s="21"/>
-    </row>
-    <row r="195" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B195" s="21"/>
-      <c r="C195" s="21"/>
-      <c r="D195" s="21"/>
-      <c r="E195" s="21"/>
-      <c r="F195" s="21"/>
-      <c r="G195" s="21"/>
-    </row>
-    <row r="196" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B196" s="23" t="s">
+      <c r="C194" s="16"/>
+      <c r="D194" s="16"/>
+      <c r="E194" s="16"/>
+      <c r="F194" s="16"/>
+      <c r="G194" s="16"/>
+    </row>
+    <row r="195" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B195" s="16"/>
+      <c r="C195" s="16"/>
+      <c r="D195" s="16"/>
+      <c r="E195" s="16"/>
+      <c r="F195" s="16"/>
+      <c r="G195" s="16"/>
+    </row>
+    <row r="196" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B196" s="18" t="s">
         <v>184</v>
       </c>
-      <c r="C196" s="21"/>
-      <c r="D196" s="21"/>
-      <c r="E196" s="21"/>
-      <c r="F196" s="21"/>
-      <c r="G196" s="21"/>
-    </row>
-    <row r="197" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B197" s="23"/>
-      <c r="C197" s="21"/>
-      <c r="D197" s="21"/>
-      <c r="E197" s="21"/>
-      <c r="F197" s="21"/>
-      <c r="G197" s="21"/>
-    </row>
-    <row r="198" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B198" s="22" t="s">
+      <c r="C196" s="16"/>
+      <c r="D196" s="16"/>
+      <c r="E196" s="16"/>
+      <c r="F196" s="16"/>
+      <c r="G196" s="16"/>
+    </row>
+    <row r="197" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B197" s="18"/>
+      <c r="C197" s="16"/>
+      <c r="D197" s="16"/>
+      <c r="E197" s="16"/>
+      <c r="F197" s="16"/>
+      <c r="G197" s="16"/>
+    </row>
+    <row r="198" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B198" s="17" t="s">
         <v>185</v>
       </c>
-      <c r="C198" s="21"/>
-      <c r="D198" s="21"/>
-      <c r="E198" s="21"/>
-      <c r="F198" s="21"/>
-      <c r="G198" s="21"/>
-    </row>
-    <row r="199" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B199" s="8"/>
-      <c r="C199" s="21"/>
-      <c r="D199" s="21"/>
-      <c r="E199" s="21"/>
-      <c r="F199" s="21"/>
-      <c r="G199" s="21"/>
-    </row>
-    <row r="200" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B200" s="22" t="s">
+      <c r="C198" s="16"/>
+      <c r="D198" s="16"/>
+      <c r="E198" s="16"/>
+      <c r="F198" s="16"/>
+      <c r="G198" s="16"/>
+    </row>
+    <row r="199" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B199" s="5"/>
+      <c r="C199" s="16"/>
+      <c r="D199" s="16"/>
+      <c r="E199" s="16"/>
+      <c r="F199" s="16"/>
+      <c r="G199" s="16"/>
+    </row>
+    <row r="200" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B200" s="17" t="s">
         <v>186</v>
       </c>
-      <c r="E200" s="22" t="s">
+      <c r="E200" s="17" t="s">
         <v>187</v>
       </c>
-      <c r="F200" s="21"/>
-      <c r="G200" s="21"/>
-    </row>
-    <row r="201" spans="1:8" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B201" s="22"/>
-      <c r="E201" s="22"/>
-      <c r="F201" s="21"/>
-      <c r="G201" s="21"/>
-    </row>
-    <row r="202" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B202" s="24"/>
-      <c r="C202" s="24"/>
-      <c r="D202" s="24"/>
-      <c r="E202" s="25"/>
-      <c r="F202" s="24"/>
-      <c r="G202" s="24"/>
-    </row>
-    <row r="203" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A203" s="6">
+      <c r="F200" s="16"/>
+      <c r="G200" s="16"/>
+    </row>
+    <row r="201" spans="1:8" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B201" s="17"/>
+      <c r="E201" s="17"/>
+      <c r="F201" s="16"/>
+      <c r="G201" s="16"/>
+    </row>
+    <row r="202" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B202" s="19"/>
+      <c r="C202" s="19"/>
+      <c r="D202" s="19"/>
+      <c r="E202" s="20"/>
+      <c r="F202" s="19"/>
+      <c r="G202" s="19"/>
+    </row>
+    <row r="203" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A203" s="4">
         <v>4014</v>
       </c>
-      <c r="B203" s="7" t="s">
+      <c r="B203" s="29" t="s">
         <v>188</v>
       </c>
-      <c r="C203" s="7"/>
-      <c r="D203" s="7"/>
-      <c r="E203" s="7"/>
-      <c r="F203" s="7"/>
-      <c r="G203" s="7"/>
-      <c r="H203" s="29"/>
-    </row>
-    <row r="204" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B204" s="10" t="s">
+      <c r="C203" s="29"/>
+      <c r="D203" s="29"/>
+      <c r="E203" s="29"/>
+      <c r="F203" s="29"/>
+      <c r="G203" s="29"/>
+      <c r="H203" s="21"/>
+    </row>
+    <row r="204" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B204" s="26" t="s">
         <v>189</v>
       </c>
-      <c r="C204" s="10"/>
-      <c r="D204" s="10"/>
-      <c r="E204" s="10"/>
-      <c r="F204" s="10"/>
-      <c r="G204" s="10"/>
-      <c r="H204" s="9"/>
-    </row>
-    <row r="205" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B205" s="12" t="s">
+      <c r="C204" s="26"/>
+      <c r="D204" s="26"/>
+      <c r="E204" s="26"/>
+      <c r="F204" s="26"/>
+      <c r="G204" s="26"/>
+      <c r="H204" s="6"/>
+    </row>
+    <row r="205" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B205" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="C205" s="12"/>
-      <c r="D205" s="12"/>
-      <c r="E205" s="12"/>
-      <c r="F205" s="12"/>
-      <c r="G205" s="12"/>
-      <c r="H205" s="11"/>
-    </row>
-    <row r="206" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B206" s="12" t="s">
+      <c r="C205" s="27"/>
+      <c r="D205" s="27"/>
+      <c r="E205" s="27"/>
+      <c r="F205" s="27"/>
+      <c r="G205" s="27"/>
+      <c r="H205" s="7"/>
+    </row>
+    <row r="206" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B206" s="27" t="s">
         <v>190</v>
       </c>
-      <c r="C206" s="12"/>
-      <c r="D206" s="12"/>
-      <c r="E206" s="12"/>
-      <c r="F206" s="12"/>
-      <c r="G206" s="12"/>
-      <c r="H206" s="11"/>
-    </row>
-    <row r="207" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A207" s="26" t="s">
+      <c r="C206" s="27"/>
+      <c r="D206" s="27"/>
+      <c r="E206" s="27"/>
+      <c r="F206" s="27"/>
+      <c r="G206" s="27"/>
+      <c r="H206" s="7"/>
+    </row>
+    <row r="207" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A207" s="30" t="s">
         <v>191</v>
       </c>
-      <c r="B207" s="26"/>
-      <c r="C207" s="26"/>
-      <c r="D207" s="26"/>
-      <c r="E207" s="26"/>
-      <c r="F207" s="26"/>
-      <c r="G207" s="26"/>
-      <c r="H207" s="26"/>
-    </row>
-    <row r="208" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A208" s="26" t="s">
+      <c r="B207" s="30"/>
+      <c r="C207" s="30"/>
+      <c r="D207" s="30"/>
+      <c r="E207" s="30"/>
+      <c r="F207" s="30"/>
+      <c r="G207" s="30"/>
+      <c r="H207" s="30"/>
+    </row>
+    <row r="208" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A208" s="30" t="s">
         <v>192</v>
       </c>
-      <c r="B208" s="26"/>
-      <c r="C208" s="26"/>
-      <c r="D208" s="26"/>
-      <c r="E208" s="26"/>
-      <c r="F208" s="26"/>
-      <c r="G208" s="26"/>
-      <c r="H208" s="26"/>
-    </row>
-    <row r="209" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A209" s="5" t="s">
+      <c r="B208" s="30"/>
+      <c r="C208" s="30"/>
+      <c r="D208" s="30"/>
+      <c r="E208" s="30"/>
+      <c r="F208" s="30"/>
+      <c r="G208" s="30"/>
+      <c r="H208" s="30"/>
+    </row>
+    <row r="209" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A209" s="28" t="s">
         <v>193</v>
       </c>
-      <c r="B209" s="5"/>
-      <c r="C209" s="5"/>
-      <c r="D209" s="5"/>
-      <c r="E209" s="5"/>
-      <c r="F209" s="5"/>
-      <c r="G209" s="5"/>
-      <c r="H209" s="5"/>
-    </row>
-    <row r="210" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B210" s="13"/>
-      <c r="C210" s="14"/>
-      <c r="D210" s="14"/>
-      <c r="E210" s="14"/>
-      <c r="F210" s="14"/>
-      <c r="G210" s="14"/>
-    </row>
-    <row r="211" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A211" s="15">
+      <c r="B209" s="28"/>
+      <c r="C209" s="28"/>
+      <c r="D209" s="28"/>
+      <c r="E209" s="28"/>
+      <c r="F209" s="28"/>
+      <c r="G209" s="28"/>
+      <c r="H209" s="28"/>
+    </row>
+    <row r="210" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B210" s="8"/>
+      <c r="C210" s="9"/>
+      <c r="D210" s="9"/>
+      <c r="E210" s="9"/>
+      <c r="F210" s="9"/>
+      <c r="G210" s="9"/>
+    </row>
+    <row r="211" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A211" s="10">
         <v>4004</v>
       </c>
-      <c r="B211" s="18">
+      <c r="B211" s="13">
         <v>1</v>
       </c>
-      <c r="C211" s="17" t="s">
+      <c r="C211" s="12" t="s">
         <v>194</v>
       </c>
-      <c r="D211" s="18">
+      <c r="D211" s="13">
         <v>57</v>
       </c>
-      <c r="E211" s="19" t="s">
+      <c r="E211" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="F211" s="18">
+      <c r="F211" s="13">
         <v>7</v>
       </c>
-      <c r="G211" s="20"/>
-      <c r="H211" s="20"/>
-    </row>
-    <row r="212" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A212" s="15">
+      <c r="G211" s="15"/>
+      <c r="H211" s="15"/>
+    </row>
+    <row r="212" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A212" s="10">
         <v>4002</v>
       </c>
-      <c r="B212" s="18">
+      <c r="B212" s="13">
         <v>2</v>
       </c>
-      <c r="C212" s="17" t="s">
+      <c r="C212" s="12" t="s">
         <v>195</v>
       </c>
-      <c r="D212" s="18">
+      <c r="D212" s="13">
         <v>53</v>
       </c>
-      <c r="E212" s="19" t="s">
+      <c r="E212" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="F212" s="18">
+      <c r="F212" s="13">
         <v>8</v>
       </c>
-      <c r="G212" s="20" t="s">
+      <c r="G212" s="15" t="s">
         <v>105</v>
       </c>
-      <c r="H212" s="20">
+      <c r="H212" s="15">
         <v>0.5</v>
       </c>
     </row>
-    <row r="213" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A213" s="15">
+    <row r="213" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A213" s="10">
         <v>3975</v>
       </c>
-      <c r="B213" s="18">
+      <c r="B213" s="13">
         <v>3</v>
       </c>
-      <c r="C213" s="17" t="s">
+      <c r="C213" s="12" t="s">
         <v>196</v>
       </c>
-      <c r="D213" s="18">
+      <c r="D213" s="13">
         <v>56</v>
       </c>
-      <c r="E213" s="19" t="s">
+      <c r="E213" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="F213" s="18">
+      <c r="F213" s="13">
         <v>1</v>
       </c>
-      <c r="G213" s="20">
+      <c r="G213" s="15">
         <v>2.5</v>
       </c>
-      <c r="H213" s="20">
+      <c r="H213" s="15">
         <v>3</v>
       </c>
     </row>
-    <row r="214" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A214" s="15">
+    <row r="214" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A214" s="10">
         <v>4004</v>
       </c>
-      <c r="B214" s="18">
+      <c r="B214" s="13">
         <v>4</v>
       </c>
-      <c r="C214" s="17" t="s">
+      <c r="C214" s="12" t="s">
         <v>197</v>
       </c>
-      <c r="D214" s="18">
+      <c r="D214" s="13">
         <v>55</v>
       </c>
-      <c r="E214" s="19" t="s">
+      <c r="E214" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="F214" s="18">
+      <c r="F214" s="13">
         <v>4</v>
       </c>
-      <c r="G214" s="20" t="s">
+      <c r="G214" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="H214" s="20">
+      <c r="H214" s="15">
         <v>3.25</v>
       </c>
     </row>
-    <row r="215" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A215" s="15">
+    <row r="215" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A215" s="10">
         <v>3994</v>
       </c>
-      <c r="B215" s="18">
+      <c r="B215" s="13">
         <v>5</v>
       </c>
-      <c r="C215" s="17" t="s">
+      <c r="C215" s="12" t="s">
         <v>198</v>
       </c>
-      <c r="D215" s="18">
+      <c r="D215" s="13">
         <v>58</v>
       </c>
-      <c r="E215" s="19" t="s">
+      <c r="E215" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="F215" s="18">
+      <c r="F215" s="13">
         <v>6</v>
       </c>
-      <c r="G215" s="20">
+      <c r="G215" s="15">
         <v>1.5</v>
       </c>
-      <c r="H215" s="20">
+      <c r="H215" s="15">
         <v>4.75</v>
       </c>
     </row>
-    <row r="216" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A216" s="15">
+    <row r="216" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A216" s="10">
         <v>4002</v>
       </c>
-      <c r="B216" s="18">
+      <c r="B216" s="13">
         <v>6</v>
       </c>
-      <c r="C216" s="17" t="s">
+      <c r="C216" s="12" t="s">
         <v>199</v>
       </c>
-      <c r="D216" s="18">
+      <c r="D216" s="13">
         <v>55</v>
       </c>
-      <c r="E216" s="19" t="s">
+      <c r="E216" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="F216" s="18">
+      <c r="F216" s="13">
         <v>2</v>
       </c>
-      <c r="G216" s="20" t="s">
+      <c r="G216" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="H216" s="20">
+      <c r="H216" s="15">
         <v>6.75</v>
       </c>
     </row>
-    <row r="217" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A217" s="15">
+    <row r="217" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A217" s="10">
         <v>3994</v>
       </c>
-      <c r="B217" s="18">
+      <c r="B217" s="13">
         <v>7</v>
       </c>
-      <c r="C217" s="17" t="s">
+      <c r="C217" s="12" t="s">
         <v>200</v>
       </c>
-      <c r="D217" s="18">
+      <c r="D217" s="13">
         <v>55</v>
       </c>
-      <c r="E217" s="19" t="s">
+      <c r="E217" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="F217" s="18">
+      <c r="F217" s="13">
         <v>10</v>
       </c>
-      <c r="G217" s="20" t="s">
+      <c r="G217" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="H217" s="20">
+      <c r="H217" s="15">
         <v>13.75</v>
       </c>
     </row>
-    <row r="218" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A218" s="15">
+    <row r="218" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A218" s="10">
         <v>4006</v>
       </c>
-      <c r="B218" s="18">
+      <c r="B218" s="13">
         <v>8</v>
       </c>
-      <c r="C218" s="17" t="s">
+      <c r="C218" s="12" t="s">
         <v>201</v>
       </c>
-      <c r="D218" s="18">
+      <c r="D218" s="13">
         <v>51</v>
       </c>
-      <c r="E218" s="19" t="s">
+      <c r="E218" s="14" t="s">
         <v>112</v>
       </c>
-      <c r="F218" s="18">
+      <c r="F218" s="13">
         <v>9</v>
       </c>
-      <c r="G218" s="20" t="s">
+      <c r="G218" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="H218" s="20">
+      <c r="H218" s="15">
         <v>16.75</v>
       </c>
     </row>
-    <row r="219" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A219" s="15">
+    <row r="219" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A219" s="10">
         <v>3994</v>
       </c>
-      <c r="B219" s="18" t="s">
+      <c r="B219" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C219" s="17" t="s">
+      <c r="C219" s="12" t="s">
         <v>202</v>
       </c>
-      <c r="D219" s="18">
+      <c r="D219" s="13">
         <v>57</v>
       </c>
-      <c r="E219" s="19" t="s">
+      <c r="E219" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="F219" s="18">
+      <c r="F219" s="13">
         <v>3</v>
       </c>
-      <c r="G219" s="20" t="s">
+      <c r="G219" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="H219" s="20">
+      <c r="H219" s="15">
         <v>19.75</v>
       </c>
     </row>
-    <row r="220" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A220" s="21"/>
-      <c r="B220" s="21"/>
-      <c r="D220" s="18"/>
-      <c r="E220" s="21"/>
-      <c r="F220" s="18"/>
-      <c r="G220" s="21"/>
-      <c r="H220" s="21"/>
-    </row>
-    <row r="221" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B221" s="22" t="s">
+    <row r="220" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A220" s="16"/>
+      <c r="B220" s="16"/>
+      <c r="D220" s="13"/>
+      <c r="E220" s="16"/>
+      <c r="F220" s="13"/>
+      <c r="G220" s="16"/>
+      <c r="H220" s="16"/>
+    </row>
+    <row r="221" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B221" s="17" t="s">
         <v>203</v>
       </c>
-      <c r="C221" s="8"/>
-      <c r="D221" s="8"/>
-      <c r="E221" s="8"/>
-      <c r="F221" s="8"/>
-      <c r="G221" s="8"/>
-    </row>
-    <row r="222" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B222" s="22" t="s">
+      <c r="C221" s="5"/>
+      <c r="D221" s="5"/>
+      <c r="E221" s="5"/>
+      <c r="F221" s="5"/>
+      <c r="G221" s="5"/>
+    </row>
+    <row r="222" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B222" s="17" t="s">
         <v>204</v>
       </c>
-      <c r="C222" s="8"/>
-      <c r="D222" s="8"/>
-      <c r="E222" s="8"/>
-      <c r="F222" s="8"/>
-      <c r="G222" s="8"/>
-    </row>
-    <row r="223" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B223" s="22"/>
-      <c r="C223" s="21"/>
-      <c r="D223" s="21"/>
-      <c r="E223" s="21"/>
-      <c r="F223" s="21"/>
-      <c r="G223" s="21"/>
-    </row>
-    <row r="224" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B224" s="23" t="s">
+      <c r="C222" s="5"/>
+      <c r="D222" s="5"/>
+      <c r="E222" s="5"/>
+      <c r="F222" s="5"/>
+      <c r="G222" s="5"/>
+    </row>
+    <row r="223" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B223" s="17"/>
+      <c r="C223" s="16"/>
+      <c r="D223" s="16"/>
+      <c r="E223" s="16"/>
+      <c r="F223" s="16"/>
+      <c r="G223" s="16"/>
+    </row>
+    <row r="224" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B224" s="18" t="s">
         <v>205</v>
       </c>
-      <c r="C224" s="21"/>
-      <c r="D224" s="21"/>
-      <c r="E224" s="21"/>
-      <c r="F224" s="21"/>
-      <c r="G224" s="21"/>
-    </row>
-    <row r="225" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B225" s="23"/>
-      <c r="C225" s="21"/>
-      <c r="D225" s="21"/>
-      <c r="E225" s="21"/>
-      <c r="F225" s="21"/>
-      <c r="G225" s="21"/>
-    </row>
-    <row r="226" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B226" s="23" t="s">
+      <c r="C224" s="16"/>
+      <c r="D224" s="16"/>
+      <c r="E224" s="16"/>
+      <c r="F224" s="16"/>
+      <c r="G224" s="16"/>
+    </row>
+    <row r="225" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B225" s="18"/>
+      <c r="C225" s="16"/>
+      <c r="D225" s="16"/>
+      <c r="E225" s="16"/>
+      <c r="F225" s="16"/>
+      <c r="G225" s="16"/>
+    </row>
+    <row r="226" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B226" s="18" t="s">
         <v>206</v>
       </c>
-      <c r="C226" s="21"/>
-      <c r="D226" s="21"/>
-      <c r="E226" s="21"/>
-      <c r="F226" s="21"/>
-      <c r="G226" s="21"/>
-    </row>
-    <row r="227" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B227" s="23" t="s">
+      <c r="C226" s="16"/>
+      <c r="D226" s="16"/>
+      <c r="E226" s="16"/>
+      <c r="F226" s="16"/>
+      <c r="G226" s="16"/>
+    </row>
+    <row r="227" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B227" s="18" t="s">
         <v>207</v>
       </c>
-      <c r="C227" s="21"/>
-      <c r="D227" s="21"/>
-      <c r="E227" s="21"/>
-      <c r="F227" s="21"/>
-      <c r="G227" s="21"/>
-    </row>
-    <row r="228" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B228" s="23"/>
-      <c r="C228" s="21"/>
-      <c r="D228" s="21"/>
-      <c r="E228" s="21"/>
-      <c r="F228" s="21"/>
-      <c r="G228" s="21"/>
-    </row>
-    <row r="229" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B229" s="22" t="s">
+      <c r="C227" s="16"/>
+      <c r="D227" s="16"/>
+      <c r="E227" s="16"/>
+      <c r="F227" s="16"/>
+      <c r="G227" s="16"/>
+    </row>
+    <row r="228" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B228" s="18"/>
+      <c r="C228" s="16"/>
+      <c r="D228" s="16"/>
+      <c r="E228" s="16"/>
+      <c r="F228" s="16"/>
+      <c r="G228" s="16"/>
+    </row>
+    <row r="229" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B229" s="17" t="s">
         <v>208</v>
       </c>
-      <c r="C229" s="21"/>
-      <c r="D229" s="21"/>
-      <c r="E229" s="21"/>
-      <c r="F229" s="21"/>
-      <c r="G229" s="21"/>
-    </row>
-    <row r="230" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B230" s="8"/>
-      <c r="C230" s="21"/>
-      <c r="D230" s="21"/>
-      <c r="E230" s="21"/>
-      <c r="F230" s="21"/>
-      <c r="G230" s="21"/>
-    </row>
-    <row r="231" spans="1:8" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B231" s="22" t="s">
+      <c r="C229" s="16"/>
+      <c r="D229" s="16"/>
+      <c r="E229" s="16"/>
+      <c r="F229" s="16"/>
+      <c r="G229" s="16"/>
+    </row>
+    <row r="230" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B230" s="5"/>
+      <c r="C230" s="16"/>
+      <c r="D230" s="16"/>
+      <c r="E230" s="16"/>
+      <c r="F230" s="16"/>
+      <c r="G230" s="16"/>
+    </row>
+    <row r="231" spans="1:8" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B231" s="17" t="s">
         <v>209</v>
       </c>
-      <c r="E231" s="22" t="s">
+      <c r="E231" s="17" t="s">
         <v>210</v>
       </c>
-      <c r="F231" s="21"/>
-      <c r="G231" s="21"/>
-    </row>
-    <row r="232" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B232" s="24"/>
-      <c r="C232" s="24"/>
-      <c r="D232" s="24"/>
-      <c r="E232" s="25"/>
-      <c r="F232" s="24"/>
-      <c r="G232" s="24"/>
-    </row>
-    <row r="233" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A233" s="6">
+      <c r="F231" s="16"/>
+      <c r="G231" s="16"/>
+    </row>
+    <row r="232" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B232" s="19"/>
+      <c r="C232" s="19"/>
+      <c r="D232" s="19"/>
+      <c r="E232" s="20"/>
+      <c r="F232" s="19"/>
+      <c r="G232" s="19"/>
+    </row>
+    <row r="233" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A233" s="4">
         <v>4015</v>
       </c>
-      <c r="B233" s="7" t="s">
+      <c r="B233" s="29" t="s">
         <v>211</v>
       </c>
-      <c r="C233" s="7"/>
-      <c r="D233" s="7"/>
-      <c r="E233" s="7"/>
-      <c r="F233" s="7"/>
-      <c r="G233" s="7"/>
-      <c r="H233" s="29"/>
-    </row>
-    <row r="234" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B234" s="10" t="s">
+      <c r="C233" s="29"/>
+      <c r="D233" s="29"/>
+      <c r="E233" s="29"/>
+      <c r="F233" s="29"/>
+      <c r="G233" s="29"/>
+      <c r="H233" s="21"/>
+    </row>
+    <row r="234" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B234" s="26" t="s">
         <v>212</v>
       </c>
-      <c r="C234" s="10"/>
-      <c r="D234" s="10"/>
-      <c r="E234" s="10"/>
-      <c r="F234" s="10"/>
-      <c r="G234" s="10"/>
-      <c r="H234" s="9"/>
-    </row>
-    <row r="235" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A235" s="11"/>
-      <c r="B235" s="12" t="s">
+      <c r="C234" s="26"/>
+      <c r="D234" s="26"/>
+      <c r="E234" s="26"/>
+      <c r="F234" s="26"/>
+      <c r="G234" s="26"/>
+      <c r="H234" s="6"/>
+    </row>
+    <row r="235" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A235" s="7"/>
+      <c r="B235" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="C235" s="12"/>
-      <c r="D235" s="12"/>
-      <c r="E235" s="12"/>
-      <c r="F235" s="12"/>
-      <c r="G235" s="12"/>
-      <c r="H235" s="11"/>
-    </row>
-    <row r="236" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B236" s="12" t="s">
+      <c r="C235" s="27"/>
+      <c r="D235" s="27"/>
+      <c r="E235" s="27"/>
+      <c r="F235" s="27"/>
+      <c r="G235" s="27"/>
+      <c r="H235" s="7"/>
+    </row>
+    <row r="236" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B236" s="27" t="s">
         <v>94</v>
       </c>
-      <c r="C236" s="12"/>
-      <c r="D236" s="12"/>
-      <c r="E236" s="12"/>
-      <c r="F236" s="12"/>
-      <c r="G236" s="12"/>
-      <c r="H236" s="11"/>
-    </row>
-    <row r="237" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A237" s="5" t="s">
+      <c r="C236" s="27"/>
+      <c r="D236" s="27"/>
+      <c r="E236" s="27"/>
+      <c r="F236" s="27"/>
+      <c r="G236" s="27"/>
+      <c r="H236" s="7"/>
+    </row>
+    <row r="237" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A237" s="28" t="s">
         <v>213</v>
       </c>
-      <c r="B237" s="5"/>
-      <c r="C237" s="5"/>
-      <c r="D237" s="5"/>
-      <c r="E237" s="5"/>
-      <c r="F237" s="5"/>
-      <c r="G237" s="5"/>
-      <c r="H237" s="5"/>
-    </row>
-    <row r="238" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A238" s="5" t="s">
+      <c r="B237" s="28"/>
+      <c r="C237" s="28"/>
+      <c r="D237" s="28"/>
+      <c r="E237" s="28"/>
+      <c r="F237" s="28"/>
+      <c r="G237" s="28"/>
+      <c r="H237" s="28"/>
+    </row>
+    <row r="238" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A238" s="28" t="s">
         <v>214</v>
       </c>
-      <c r="B238" s="5"/>
-      <c r="C238" s="5"/>
-      <c r="D238" s="5"/>
-      <c r="E238" s="5"/>
-      <c r="F238" s="5"/>
-      <c r="G238" s="5"/>
-      <c r="H238" s="5"/>
-    </row>
-    <row r="239" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A239" s="5" t="s">
+      <c r="B238" s="28"/>
+      <c r="C238" s="28"/>
+      <c r="D238" s="28"/>
+      <c r="E238" s="28"/>
+      <c r="F238" s="28"/>
+      <c r="G238" s="28"/>
+      <c r="H238" s="28"/>
+    </row>
+    <row r="239" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A239" s="28" t="s">
         <v>149</v>
       </c>
-      <c r="B239" s="5"/>
-      <c r="C239" s="5"/>
-      <c r="D239" s="5"/>
-      <c r="E239" s="5"/>
-      <c r="F239" s="5"/>
-      <c r="G239" s="5"/>
-      <c r="H239" s="5"/>
-    </row>
-    <row r="240" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B240" s="13"/>
-      <c r="C240" s="14"/>
-      <c r="D240" s="14"/>
-      <c r="E240" s="14"/>
-      <c r="F240" s="14"/>
-      <c r="G240" s="14"/>
-    </row>
-    <row r="241" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A241" s="15">
+      <c r="B239" s="28"/>
+      <c r="C239" s="28"/>
+      <c r="D239" s="28"/>
+      <c r="E239" s="28"/>
+      <c r="F239" s="28"/>
+      <c r="G239" s="28"/>
+      <c r="H239" s="28"/>
+    </row>
+    <row r="240" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B240" s="8"/>
+      <c r="C240" s="9"/>
+      <c r="D240" s="9"/>
+      <c r="E240" s="9"/>
+      <c r="F240" s="9"/>
+      <c r="G240" s="9"/>
+    </row>
+    <row r="241" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A241" s="10">
         <v>3991</v>
       </c>
-      <c r="B241" s="18">
+      <c r="B241" s="13">
         <v>1</v>
       </c>
-      <c r="C241" s="17" t="s">
+      <c r="C241" s="12" t="s">
         <v>215</v>
       </c>
-      <c r="D241" s="18">
+      <c r="D241" s="13">
         <v>54</v>
       </c>
-      <c r="E241" s="19" t="s">
+      <c r="E241" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="F241" s="18">
+      <c r="F241" s="13">
         <v>8</v>
       </c>
-      <c r="G241" s="20"/>
-      <c r="H241" s="20"/>
-    </row>
-    <row r="242" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A242" s="15">
+      <c r="G241" s="15"/>
+      <c r="H241" s="15"/>
+    </row>
+    <row r="242" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A242" s="10">
         <v>3998</v>
       </c>
-      <c r="B242" s="18">
+      <c r="B242" s="13">
         <v>2</v>
       </c>
-      <c r="C242" s="17" t="s">
+      <c r="C242" s="12" t="s">
         <v>216</v>
       </c>
-      <c r="D242" s="18">
+      <c r="D242" s="13">
         <v>56</v>
       </c>
-      <c r="E242" s="19" t="s">
+      <c r="E242" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="F242" s="18">
+      <c r="F242" s="13">
         <v>5</v>
       </c>
-      <c r="G242" s="20" t="s">
+      <c r="G242" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="H242" s="20">
+      <c r="H242" s="15">
         <v>1</v>
       </c>
     </row>
-    <row r="243" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A243" s="15">
+    <row r="243" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A243" s="10">
         <v>4002</v>
       </c>
-      <c r="B243" s="18">
+      <c r="B243" s="13">
         <v>3</v>
       </c>
-      <c r="C243" s="17" t="s">
+      <c r="C243" s="12" t="s">
         <v>217</v>
       </c>
-      <c r="D243" s="18">
+      <c r="D243" s="13">
         <v>54</v>
       </c>
-      <c r="E243" s="19" t="s">
+      <c r="E243" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="F243" s="18">
+      <c r="F243" s="13">
         <v>7</v>
       </c>
-      <c r="G243" s="20" t="s">
+      <c r="G243" s="15" t="s">
         <v>218</v>
       </c>
-      <c r="H243" s="20">
+      <c r="H243" s="15">
         <v>1</v>
       </c>
     </row>
-    <row r="244" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A244" s="15">
+    <row r="244" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A244" s="10">
         <v>4006</v>
       </c>
-      <c r="B244" s="18">
+      <c r="B244" s="13">
         <v>4</v>
       </c>
-      <c r="C244" s="17" t="s">
+      <c r="C244" s="12" t="s">
         <v>219</v>
       </c>
-      <c r="D244" s="18">
+      <c r="D244" s="13">
         <v>54</v>
       </c>
-      <c r="E244" s="19" t="s">
+      <c r="E244" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="F244" s="18">
+      <c r="F244" s="13">
         <v>2</v>
       </c>
-      <c r="G244" s="20" t="s">
+      <c r="G244" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="H244" s="20">
+      <c r="H244" s="15">
         <v>11</v>
       </c>
     </row>
-    <row r="245" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A245" s="15">
+    <row r="245" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A245" s="10">
         <v>3923</v>
       </c>
-      <c r="B245" s="18">
+      <c r="B245" s="13">
         <v>5</v>
       </c>
-      <c r="C245" s="17" t="s">
+      <c r="C245" s="12" t="s">
         <v>220</v>
       </c>
-      <c r="D245" s="18">
+      <c r="D245" s="13">
         <v>52</v>
       </c>
-      <c r="E245" s="19" t="s">
+      <c r="E245" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="F245" s="18">
+      <c r="F245" s="13">
         <v>3</v>
       </c>
-      <c r="G245" s="20" t="s">
+      <c r="G245" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="H245" s="20">
+      <c r="H245" s="15">
         <v>11.75</v>
       </c>
     </row>
-    <row r="246" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A246" s="15">
+    <row r="246" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A246" s="10">
         <v>4005</v>
       </c>
-      <c r="B246" s="18">
+      <c r="B246" s="13">
         <v>6</v>
       </c>
-      <c r="C246" s="17" t="s">
+      <c r="C246" s="12" t="s">
         <v>221</v>
       </c>
-      <c r="D246" s="18">
+      <c r="D246" s="13">
         <v>52</v>
       </c>
-      <c r="E246" s="19" t="s">
+      <c r="E246" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="F246" s="18">
+      <c r="F246" s="13">
         <v>4</v>
       </c>
-      <c r="G246" s="20" t="s">
+      <c r="G246" s="15" t="s">
         <v>105</v>
       </c>
-      <c r="H246" s="20">
+      <c r="H246" s="15">
         <v>12.25</v>
       </c>
     </row>
-    <row r="247" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A247" s="15">
+    <row r="247" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A247" s="10">
         <v>4002</v>
       </c>
-      <c r="B247" s="18">
+      <c r="B247" s="13">
         <v>7</v>
       </c>
-      <c r="C247" s="17" t="s">
+      <c r="C247" s="12" t="s">
         <v>222</v>
       </c>
-      <c r="D247" s="18">
+      <c r="D247" s="13">
         <v>56</v>
       </c>
-      <c r="E247" s="19" t="s">
+      <c r="E247" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="F247" s="18">
+      <c r="F247" s="13">
         <v>1</v>
       </c>
-      <c r="G247" s="20" t="s">
+      <c r="G247" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="H247" s="20">
+      <c r="H247" s="15">
         <v>13</v>
       </c>
     </row>
-    <row r="248" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A248" s="15">
+    <row r="248" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A248" s="10">
         <v>4005</v>
       </c>
-      <c r="B248" s="18">
+      <c r="B248" s="13">
         <v>8</v>
       </c>
-      <c r="C248" s="17" t="s">
+      <c r="C248" s="12" t="s">
         <v>223</v>
       </c>
-      <c r="D248" s="18">
+      <c r="D248" s="13">
         <v>52</v>
       </c>
-      <c r="E248" s="19" t="s">
+      <c r="E248" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="F248" s="18">
+      <c r="F248" s="13">
         <v>9</v>
       </c>
-      <c r="G248" s="20" t="s">
+      <c r="G248" s="15" t="s">
         <v>180</v>
       </c>
-      <c r="H248" s="20">
+      <c r="H248" s="15">
         <v>25</v>
       </c>
     </row>
-    <row r="249" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A249" s="15">
+    <row r="249" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A249" s="10">
         <v>3991</v>
       </c>
-      <c r="B249" s="18" t="s">
+      <c r="B249" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C249" s="17" t="s">
+      <c r="C249" s="12" t="s">
         <v>224</v>
       </c>
-      <c r="D249" s="18">
+      <c r="D249" s="13">
         <v>56</v>
       </c>
-      <c r="E249" s="19" t="s">
+      <c r="E249" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="F249" s="18">
+      <c r="F249" s="13">
         <v>6</v>
       </c>
-      <c r="G249" s="20" t="s">
+      <c r="G249" s="15" t="s">
         <v>180</v>
       </c>
-      <c r="H249" s="20">
+      <c r="H249" s="15">
         <v>37</v>
       </c>
     </row>
-    <row r="250" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A250" s="21"/>
-      <c r="B250" s="21"/>
-      <c r="D250" s="18"/>
-      <c r="E250" s="21"/>
-      <c r="F250" s="18"/>
-      <c r="G250" s="20"/>
-    </row>
-    <row r="251" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B251" s="22" t="s">
+    <row r="250" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A250" s="16"/>
+      <c r="B250" s="16"/>
+      <c r="D250" s="13"/>
+      <c r="E250" s="16"/>
+      <c r="F250" s="13"/>
+      <c r="G250" s="15"/>
+    </row>
+    <row r="251" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B251" s="17" t="s">
         <v>225</v>
       </c>
-      <c r="C251" s="8"/>
-      <c r="D251" s="8"/>
-      <c r="E251" s="8"/>
-      <c r="F251" s="8"/>
-      <c r="G251" s="8"/>
-    </row>
-    <row r="252" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B252" s="22" t="s">
+      <c r="C251" s="5"/>
+      <c r="D251" s="5"/>
+      <c r="E251" s="5"/>
+      <c r="F251" s="5"/>
+      <c r="G251" s="5"/>
+    </row>
+    <row r="252" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B252" s="17" t="s">
         <v>226</v>
       </c>
-      <c r="C252" s="8"/>
-      <c r="D252" s="8"/>
-      <c r="E252" s="8"/>
-      <c r="F252" s="8"/>
-      <c r="G252" s="8"/>
-    </row>
-    <row r="253" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B253" s="22"/>
-      <c r="C253" s="21"/>
-      <c r="D253" s="21"/>
-      <c r="E253" s="21"/>
-      <c r="F253" s="21"/>
-      <c r="G253" s="21"/>
-    </row>
-    <row r="254" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B254" s="23" t="s">
+      <c r="C252" s="5"/>
+      <c r="D252" s="5"/>
+      <c r="E252" s="5"/>
+      <c r="F252" s="5"/>
+      <c r="G252" s="5"/>
+    </row>
+    <row r="253" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B253" s="17"/>
+      <c r="C253" s="16"/>
+      <c r="D253" s="16"/>
+      <c r="E253" s="16"/>
+      <c r="F253" s="16"/>
+      <c r="G253" s="16"/>
+    </row>
+    <row r="254" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B254" s="18" t="s">
         <v>227</v>
       </c>
-      <c r="C254" s="21"/>
-      <c r="D254" s="21"/>
-      <c r="E254" s="21"/>
-      <c r="F254" s="21"/>
-      <c r="G254" s="21"/>
-    </row>
-    <row r="255" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B255" s="21"/>
-      <c r="C255" s="21"/>
-      <c r="D255" s="21"/>
-      <c r="E255" s="21"/>
-      <c r="F255" s="21"/>
-      <c r="G255" s="21"/>
-    </row>
-    <row r="256" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B256" s="23" t="s">
+      <c r="C254" s="16"/>
+      <c r="D254" s="16"/>
+      <c r="E254" s="16"/>
+      <c r="F254" s="16"/>
+      <c r="G254" s="16"/>
+    </row>
+    <row r="255" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B255" s="16"/>
+      <c r="C255" s="16"/>
+      <c r="D255" s="16"/>
+      <c r="E255" s="16"/>
+      <c r="F255" s="16"/>
+      <c r="G255" s="16"/>
+    </row>
+    <row r="256" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B256" s="18" t="s">
         <v>228</v>
       </c>
-      <c r="C256" s="21"/>
-      <c r="D256" s="21"/>
-      <c r="E256" s="21"/>
-      <c r="F256" s="21"/>
-      <c r="G256" s="21"/>
-    </row>
-    <row r="257" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B257" s="23" t="s">
+      <c r="C256" s="16"/>
+      <c r="D256" s="16"/>
+      <c r="E256" s="16"/>
+      <c r="F256" s="16"/>
+      <c r="G256" s="16"/>
+    </row>
+    <row r="257" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B257" s="18" t="s">
         <v>229</v>
       </c>
-      <c r="C257" s="21"/>
-      <c r="D257" s="21"/>
-      <c r="E257" s="21"/>
-      <c r="F257" s="21"/>
-      <c r="G257" s="21"/>
-    </row>
-    <row r="258" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B258" s="23"/>
-      <c r="C258" s="21"/>
-      <c r="D258" s="21"/>
-      <c r="E258" s="21"/>
-      <c r="F258" s="21"/>
-      <c r="G258" s="21"/>
-    </row>
-    <row r="259" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B259" s="22" t="s">
+      <c r="C257" s="16"/>
+      <c r="D257" s="16"/>
+      <c r="E257" s="16"/>
+      <c r="F257" s="16"/>
+      <c r="G257" s="16"/>
+    </row>
+    <row r="258" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B258" s="18"/>
+      <c r="C258" s="16"/>
+      <c r="D258" s="16"/>
+      <c r="E258" s="16"/>
+      <c r="F258" s="16"/>
+      <c r="G258" s="16"/>
+    </row>
+    <row r="259" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B259" s="17" t="s">
         <v>230</v>
       </c>
-      <c r="C259" s="21"/>
-      <c r="D259" s="21"/>
-      <c r="E259" s="21"/>
-      <c r="F259" s="21"/>
-      <c r="G259" s="21"/>
-    </row>
-    <row r="260" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B260" s="8"/>
-      <c r="C260" s="21"/>
-      <c r="D260" s="21"/>
-      <c r="E260" s="21"/>
-      <c r="F260" s="21"/>
-      <c r="G260" s="21"/>
-    </row>
-    <row r="261" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B261" s="22" t="s">
+      <c r="C259" s="16"/>
+      <c r="D259" s="16"/>
+      <c r="E259" s="16"/>
+      <c r="F259" s="16"/>
+      <c r="G259" s="16"/>
+    </row>
+    <row r="260" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B260" s="5"/>
+      <c r="C260" s="16"/>
+      <c r="D260" s="16"/>
+      <c r="E260" s="16"/>
+      <c r="F260" s="16"/>
+      <c r="G260" s="16"/>
+    </row>
+    <row r="261" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B261" s="17" t="s">
         <v>209</v>
       </c>
-      <c r="E261" s="22" t="s">
+      <c r="E261" s="17" t="s">
         <v>231</v>
       </c>
-      <c r="F261" s="21"/>
-      <c r="G261" s="21"/>
-    </row>
-    <row r="262" spans="1:8" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B262" s="30"/>
-      <c r="C262" s="31"/>
-      <c r="D262" s="31"/>
-      <c r="E262" s="30"/>
-      <c r="F262" s="32"/>
-      <c r="G262" s="32"/>
-    </row>
-    <row r="263" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B263" s="24"/>
-      <c r="C263" s="24"/>
-      <c r="D263" s="24"/>
-      <c r="E263" s="25"/>
-      <c r="F263" s="24"/>
-      <c r="G263" s="24"/>
-    </row>
-    <row r="264" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A264" s="6">
+      <c r="F261" s="16"/>
+      <c r="G261" s="16"/>
+    </row>
+    <row r="262" spans="1:8" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B262" s="22"/>
+      <c r="C262" s="23"/>
+      <c r="D262" s="23"/>
+      <c r="E262" s="22"/>
+      <c r="F262" s="24"/>
+      <c r="G262" s="24"/>
+    </row>
+    <row r="263" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B263" s="19"/>
+      <c r="C263" s="19"/>
+      <c r="D263" s="19"/>
+      <c r="E263" s="20"/>
+      <c r="F263" s="19"/>
+      <c r="G263" s="19"/>
+    </row>
+    <row r="264" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A264" s="4">
         <v>4016</v>
       </c>
-      <c r="B264" s="7" t="s">
+      <c r="B264" s="29" t="s">
         <v>232</v>
       </c>
-      <c r="C264" s="7"/>
-      <c r="D264" s="7"/>
-      <c r="E264" s="7"/>
-      <c r="F264" s="7"/>
-      <c r="G264" s="7"/>
-      <c r="H264" s="29"/>
-    </row>
-    <row r="265" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B265" s="10" t="s">
+      <c r="C264" s="29"/>
+      <c r="D264" s="29"/>
+      <c r="E264" s="29"/>
+      <c r="F264" s="29"/>
+      <c r="G264" s="29"/>
+      <c r="H264" s="21"/>
+    </row>
+    <row r="265" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B265" s="26" t="s">
         <v>233</v>
       </c>
-      <c r="C265" s="10"/>
-      <c r="D265" s="10"/>
-      <c r="E265" s="10"/>
-      <c r="F265" s="10"/>
-      <c r="G265" s="10"/>
-      <c r="H265" s="9"/>
-    </row>
-    <row r="266" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A266" s="11"/>
-      <c r="B266" s="12" t="s">
+      <c r="C265" s="26"/>
+      <c r="D265" s="26"/>
+      <c r="E265" s="26"/>
+      <c r="F265" s="26"/>
+      <c r="G265" s="26"/>
+      <c r="H265" s="6"/>
+    </row>
+    <row r="266" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A266" s="7"/>
+      <c r="B266" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="C266" s="12"/>
-      <c r="D266" s="12"/>
-      <c r="E266" s="12"/>
-      <c r="F266" s="12"/>
-      <c r="G266" s="12"/>
-      <c r="H266" s="11"/>
-    </row>
-    <row r="267" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B267" s="12" t="s">
+      <c r="C266" s="27"/>
+      <c r="D266" s="27"/>
+      <c r="E266" s="27"/>
+      <c r="F266" s="27"/>
+      <c r="G266" s="27"/>
+      <c r="H266" s="7"/>
+    </row>
+    <row r="267" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B267" s="27" t="s">
         <v>94</v>
       </c>
-      <c r="C267" s="12"/>
-      <c r="D267" s="12"/>
-      <c r="E267" s="12"/>
-      <c r="F267" s="12"/>
-      <c r="G267" s="12"/>
-      <c r="H267" s="11"/>
-    </row>
-    <row r="268" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A268" s="5" t="s">
+      <c r="C267" s="27"/>
+      <c r="D267" s="27"/>
+      <c r="E267" s="27"/>
+      <c r="F267" s="27"/>
+      <c r="G267" s="27"/>
+      <c r="H267" s="7"/>
+    </row>
+    <row r="268" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A268" s="28" t="s">
         <v>234</v>
       </c>
-      <c r="B268" s="5"/>
-      <c r="C268" s="5"/>
-      <c r="D268" s="5"/>
-      <c r="E268" s="5"/>
-      <c r="F268" s="5"/>
-      <c r="G268" s="5"/>
-      <c r="H268" s="5"/>
-    </row>
-    <row r="269" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A269" s="5" t="s">
+      <c r="B268" s="28"/>
+      <c r="C268" s="28"/>
+      <c r="D268" s="28"/>
+      <c r="E268" s="28"/>
+      <c r="F268" s="28"/>
+      <c r="G268" s="28"/>
+      <c r="H268" s="28"/>
+    </row>
+    <row r="269" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A269" s="28" t="s">
         <v>235</v>
       </c>
-      <c r="B269" s="5"/>
-      <c r="C269" s="5"/>
-      <c r="D269" s="5"/>
-      <c r="E269" s="5"/>
-      <c r="F269" s="5"/>
-      <c r="G269" s="5"/>
-      <c r="H269" s="5"/>
-    </row>
-    <row r="270" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B270" s="13"/>
-      <c r="C270" s="14"/>
-      <c r="D270" s="14"/>
-      <c r="E270" s="14"/>
-      <c r="F270" s="14"/>
-      <c r="G270" s="14"/>
-    </row>
-    <row r="271" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A271" s="15">
+      <c r="B269" s="28"/>
+      <c r="C269" s="28"/>
+      <c r="D269" s="28"/>
+      <c r="E269" s="28"/>
+      <c r="F269" s="28"/>
+      <c r="G269" s="28"/>
+      <c r="H269" s="28"/>
+    </row>
+    <row r="270" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B270" s="8"/>
+      <c r="C270" s="9"/>
+      <c r="D270" s="9"/>
+      <c r="E270" s="9"/>
+      <c r="F270" s="9"/>
+      <c r="G270" s="9"/>
+    </row>
+    <row r="271" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A271" s="10">
         <v>3998</v>
       </c>
-      <c r="B271" s="18">
+      <c r="B271" s="13">
         <v>1</v>
       </c>
-      <c r="C271" s="17" t="s">
+      <c r="C271" s="12" t="s">
         <v>236</v>
       </c>
-      <c r="D271" s="18">
+      <c r="D271" s="13">
         <v>57</v>
       </c>
-      <c r="E271" s="19" t="s">
+      <c r="E271" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="F271" s="18">
+      <c r="F271" s="13">
         <v>5</v>
       </c>
-      <c r="G271" s="20"/>
-      <c r="H271" s="20"/>
-    </row>
-    <row r="272" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A272" s="15">
+      <c r="G271" s="15"/>
+      <c r="H271" s="15"/>
+    </row>
+    <row r="272" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A272" s="10">
         <v>4001</v>
       </c>
-      <c r="B272" s="18">
+      <c r="B272" s="13">
         <v>2</v>
       </c>
-      <c r="C272" s="17" t="s">
+      <c r="C272" s="12" t="s">
         <v>237</v>
       </c>
-      <c r="D272" s="18">
+      <c r="D272" s="13">
         <v>56</v>
       </c>
-      <c r="E272" s="19" t="s">
+      <c r="E272" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="F272" s="18">
+      <c r="F272" s="13">
         <v>7</v>
       </c>
-      <c r="G272" s="20" t="s">
+      <c r="G272" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="H272" s="20">
+      <c r="H272" s="15">
         <v>6</v>
       </c>
     </row>
-    <row r="273" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A273" s="15">
+    <row r="273" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A273" s="10">
         <v>4001</v>
       </c>
-      <c r="B273" s="18">
+      <c r="B273" s="13">
         <v>3</v>
       </c>
-      <c r="C273" s="17" t="s">
+      <c r="C273" s="12" t="s">
         <v>238</v>
       </c>
-      <c r="D273" s="18">
+      <c r="D273" s="13">
         <v>54</v>
       </c>
-      <c r="E273" s="19" t="s">
+      <c r="E273" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="F273" s="18">
+      <c r="F273" s="13">
         <v>3</v>
       </c>
-      <c r="G273" s="20" t="s">
+      <c r="G273" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="H273" s="20">
+      <c r="H273" s="15">
         <v>10</v>
       </c>
     </row>
-    <row r="274" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A274" s="15">
+    <row r="274" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A274" s="10">
         <v>4001</v>
       </c>
-      <c r="B274" s="18">
+      <c r="B274" s="13">
         <v>4</v>
       </c>
-      <c r="C274" s="17" t="s">
+      <c r="C274" s="12" t="s">
         <v>239</v>
       </c>
-      <c r="D274" s="18">
+      <c r="D274" s="13">
         <v>56</v>
       </c>
-      <c r="E274" s="19" t="s">
+      <c r="E274" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="F274" s="18">
+      <c r="F274" s="13">
         <v>9</v>
       </c>
-      <c r="G274" s="20">
+      <c r="G274" s="15">
         <v>2.5</v>
       </c>
-      <c r="H274" s="20">
+      <c r="H274" s="15">
         <v>12.5</v>
       </c>
     </row>
-    <row r="275" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A275" s="15">
+    <row r="275" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A275" s="10">
         <v>3990</v>
       </c>
-      <c r="B275" s="18">
+      <c r="B275" s="13">
         <v>5</v>
       </c>
-      <c r="C275" s="17" t="s">
+      <c r="C275" s="12" t="s">
         <v>240</v>
       </c>
-      <c r="D275" s="18">
+      <c r="D275" s="13">
         <v>55</v>
       </c>
-      <c r="E275" s="19" t="s">
+      <c r="E275" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="F275" s="18">
+      <c r="F275" s="13">
         <v>1</v>
       </c>
-      <c r="G275" s="20" t="s">
+      <c r="G275" s="15" t="s">
         <v>105</v>
       </c>
-      <c r="H275" s="20">
+      <c r="H275" s="15">
         <v>13</v>
       </c>
     </row>
-    <row r="276" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A276" s="15">
+    <row r="276" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A276" s="10">
         <v>3756</v>
       </c>
-      <c r="B276" s="18">
+      <c r="B276" s="13">
         <v>6</v>
       </c>
-      <c r="C276" s="17" t="s">
+      <c r="C276" s="12" t="s">
         <v>241</v>
       </c>
-      <c r="D276" s="18">
+      <c r="D276" s="13">
         <v>54</v>
       </c>
-      <c r="E276" s="19" t="s">
+      <c r="E276" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="F276" s="18">
+      <c r="F276" s="13">
         <v>11</v>
       </c>
-      <c r="G276" s="20" t="s">
+      <c r="G276" s="15" t="s">
         <v>218</v>
       </c>
-      <c r="H276" s="20">
+      <c r="H276" s="15">
         <v>13</v>
       </c>
     </row>
-    <row r="277" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A277" s="15">
+    <row r="277" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A277" s="10">
         <v>3998</v>
       </c>
-      <c r="B277" s="18">
+      <c r="B277" s="13">
         <v>7</v>
       </c>
-      <c r="C277" s="17" t="s">
+      <c r="C277" s="12" t="s">
         <v>242</v>
       </c>
-      <c r="D277" s="18">
+      <c r="D277" s="13">
         <v>51</v>
       </c>
-      <c r="E277" s="19" t="s">
+      <c r="E277" s="14" t="s">
         <v>243</v>
       </c>
-      <c r="F277" s="18">
+      <c r="F277" s="13">
         <v>10</v>
       </c>
-      <c r="G277" s="20" t="s">
+      <c r="G277" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="H277" s="20">
+      <c r="H277" s="15">
         <v>16</v>
       </c>
     </row>
-    <row r="278" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A278" s="15">
+    <row r="278" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A278" s="10">
         <v>4001</v>
       </c>
-      <c r="B278" s="18">
+      <c r="B278" s="13">
         <v>8</v>
       </c>
-      <c r="C278" s="17" t="s">
+      <c r="C278" s="12" t="s">
         <v>244</v>
       </c>
-      <c r="D278" s="18">
+      <c r="D278" s="13">
         <v>54</v>
       </c>
-      <c r="E278" s="19" t="s">
+      <c r="E278" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="F278" s="18">
+      <c r="F278" s="13">
         <v>8</v>
       </c>
-      <c r="G278" s="20" t="s">
+      <c r="G278" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="H278" s="20">
+      <c r="H278" s="15">
         <v>20</v>
       </c>
     </row>
-    <row r="279" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A279" s="15">
+    <row r="279" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A279" s="10">
         <v>4001</v>
       </c>
-      <c r="B279" s="18">
+      <c r="B279" s="13">
         <v>9</v>
       </c>
-      <c r="C279" s="17" t="s">
+      <c r="C279" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="D279" s="18">
+      <c r="D279" s="13">
         <v>52</v>
       </c>
-      <c r="E279" s="19" t="s">
+      <c r="E279" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="F279" s="18">
+      <c r="F279" s="13">
         <v>12</v>
       </c>
-      <c r="G279" s="20" t="s">
+      <c r="G279" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="H279" s="20">
+      <c r="H279" s="15">
         <v>20.75</v>
       </c>
     </row>
-    <row r="280" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A280" s="15">
+    <row r="280" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A280" s="10">
         <v>4001</v>
       </c>
-      <c r="B280" s="18">
+      <c r="B280" s="13">
         <v>10</v>
       </c>
-      <c r="C280" s="17" t="s">
+      <c r="C280" s="12" t="s">
         <v>246</v>
       </c>
-      <c r="D280" s="18">
+      <c r="D280" s="13">
         <v>52</v>
       </c>
-      <c r="E280" s="19" t="s">
+      <c r="E280" s="14" t="s">
         <v>112</v>
       </c>
-      <c r="F280" s="18">
+      <c r="F280" s="13">
         <v>13</v>
       </c>
-      <c r="G280" s="20" t="s">
+      <c r="G280" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="H280" s="20">
+      <c r="H280" s="15">
         <v>30.75</v>
       </c>
     </row>
-    <row r="281" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A281" s="15">
+    <row r="281" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A281" s="10">
         <v>3998</v>
       </c>
-      <c r="B281" s="18">
+      <c r="B281" s="13">
         <v>11</v>
       </c>
-      <c r="C281" s="17" t="s">
+      <c r="C281" s="12" t="s">
         <v>247</v>
       </c>
-      <c r="D281" s="18">
+      <c r="D281" s="13">
         <v>57</v>
       </c>
-      <c r="E281" s="19" t="s">
+      <c r="E281" s="14" t="s">
         <v>133</v>
       </c>
-      <c r="F281" s="18">
+      <c r="F281" s="13">
         <v>4</v>
       </c>
-      <c r="G281" s="20" t="s">
+      <c r="G281" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="H281" s="20">
+      <c r="H281" s="15">
         <v>32.75</v>
       </c>
     </row>
-    <row r="282" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A282" s="15">
+    <row r="282" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A282" s="10">
         <v>4001</v>
       </c>
-      <c r="B282" s="18" t="s">
+      <c r="B282" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C282" s="17" t="s">
+      <c r="C282" s="12" t="s">
         <v>248</v>
       </c>
-      <c r="D282" s="18">
+      <c r="D282" s="13">
         <v>54</v>
       </c>
-      <c r="E282" s="19" t="s">
+      <c r="E282" s="14" t="s">
         <v>249</v>
       </c>
-      <c r="F282" s="18">
+      <c r="F282" s="13">
         <v>2</v>
       </c>
-      <c r="G282" s="20" t="s">
+      <c r="G282" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="H282" s="20">
+      <c r="H282" s="15">
         <v>42.75</v>
       </c>
     </row>
-    <row r="283" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A283" s="21"/>
-      <c r="B283" s="21"/>
-      <c r="D283" s="18"/>
-      <c r="E283" s="21"/>
-      <c r="F283" s="18"/>
-      <c r="G283" s="20"/>
-    </row>
-    <row r="284" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B284" s="22" t="s">
+    <row r="283" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A283" s="16"/>
+      <c r="B283" s="16"/>
+      <c r="D283" s="13"/>
+      <c r="E283" s="16"/>
+      <c r="F283" s="13"/>
+      <c r="G283" s="15"/>
+    </row>
+    <row r="284" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B284" s="17" t="s">
         <v>250</v>
       </c>
-      <c r="C284" s="8"/>
-      <c r="D284" s="8"/>
-      <c r="E284" s="8"/>
-      <c r="F284" s="8"/>
-      <c r="G284" s="8"/>
-    </row>
-    <row r="285" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B285" s="22" t="s">
+      <c r="C284" s="5"/>
+      <c r="D284" s="5"/>
+      <c r="E284" s="5"/>
+      <c r="F284" s="5"/>
+      <c r="G284" s="5"/>
+    </row>
+    <row r="285" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B285" s="17" t="s">
         <v>251</v>
       </c>
-      <c r="C285" s="8"/>
-      <c r="D285" s="8"/>
-      <c r="E285" s="8"/>
-      <c r="F285" s="8"/>
-      <c r="G285" s="8"/>
-    </row>
-    <row r="286" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B286" s="22" t="s">
+      <c r="C285" s="5"/>
+      <c r="D285" s="5"/>
+      <c r="E285" s="5"/>
+      <c r="F285" s="5"/>
+      <c r="G285" s="5"/>
+    </row>
+    <row r="286" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B286" s="17" t="s">
         <v>252</v>
       </c>
-      <c r="C286" s="8"/>
-      <c r="D286" s="8"/>
-      <c r="E286" s="8"/>
-      <c r="F286" s="8"/>
-      <c r="G286" s="8"/>
-    </row>
-    <row r="287" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B287" s="22" t="s">
+      <c r="C286" s="5"/>
+      <c r="D286" s="5"/>
+      <c r="E286" s="5"/>
+      <c r="F286" s="5"/>
+      <c r="G286" s="5"/>
+    </row>
+    <row r="287" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B287" s="17" t="s">
         <v>253</v>
       </c>
-      <c r="C287" s="8"/>
-      <c r="D287" s="8"/>
-      <c r="E287" s="8"/>
-      <c r="F287" s="8"/>
-      <c r="G287" s="8"/>
-    </row>
-    <row r="288" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B288" s="22"/>
-      <c r="C288" s="21"/>
-      <c r="D288" s="21"/>
-      <c r="E288" s="21"/>
-      <c r="F288" s="21"/>
-      <c r="G288" s="21"/>
-    </row>
-    <row r="289" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B289" s="23" t="s">
+      <c r="C287" s="5"/>
+      <c r="D287" s="5"/>
+      <c r="E287" s="5"/>
+      <c r="F287" s="5"/>
+      <c r="G287" s="5"/>
+    </row>
+    <row r="288" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B288" s="17"/>
+      <c r="C288" s="16"/>
+      <c r="D288" s="16"/>
+      <c r="E288" s="16"/>
+      <c r="F288" s="16"/>
+      <c r="G288" s="16"/>
+    </row>
+    <row r="289" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B289" s="18" t="s">
         <v>254</v>
       </c>
-      <c r="C289" s="21"/>
-      <c r="D289" s="21"/>
-      <c r="E289" s="21"/>
-      <c r="F289" s="21"/>
-      <c r="G289" s="21"/>
-    </row>
-    <row r="290" spans="2:7" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C290" s="21"/>
-      <c r="D290" s="21"/>
-      <c r="E290" s="21"/>
-      <c r="F290" s="21"/>
-      <c r="G290" s="21"/>
-    </row>
-    <row r="291" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B291" s="23" t="s">
+      <c r="C289" s="16"/>
+      <c r="D289" s="16"/>
+      <c r="E289" s="16"/>
+      <c r="F289" s="16"/>
+      <c r="G289" s="16"/>
+    </row>
+    <row r="290" spans="2:7" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C290" s="16"/>
+      <c r="D290" s="16"/>
+      <c r="E290" s="16"/>
+      <c r="F290" s="16"/>
+      <c r="G290" s="16"/>
+    </row>
+    <row r="291" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B291" s="18" t="s">
         <v>255</v>
       </c>
-      <c r="C291" s="21"/>
-      <c r="D291" s="21"/>
-      <c r="E291" s="21"/>
-      <c r="F291" s="21"/>
-      <c r="G291" s="21"/>
-    </row>
-    <row r="292" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B292" s="23" t="s">
+      <c r="C291" s="16"/>
+      <c r="D291" s="16"/>
+      <c r="E291" s="16"/>
+      <c r="F291" s="16"/>
+      <c r="G291" s="16"/>
+    </row>
+    <row r="292" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B292" s="18" t="s">
         <v>256</v>
       </c>
-      <c r="C292" s="21"/>
-      <c r="D292" s="21"/>
-      <c r="E292" s="21"/>
-      <c r="F292" s="21"/>
-      <c r="G292" s="21"/>
-    </row>
-    <row r="293" spans="2:7" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B293" s="23"/>
-      <c r="C293" s="21"/>
-      <c r="D293" s="21"/>
-      <c r="E293" s="21"/>
-      <c r="F293" s="21"/>
-      <c r="G293" s="21"/>
-    </row>
-    <row r="294" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B294" s="22" t="s">
+      <c r="C292" s="16"/>
+      <c r="D292" s="16"/>
+      <c r="E292" s="16"/>
+      <c r="F292" s="16"/>
+      <c r="G292" s="16"/>
+    </row>
+    <row r="293" spans="2:7" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B293" s="18"/>
+      <c r="C293" s="16"/>
+      <c r="D293" s="16"/>
+      <c r="E293" s="16"/>
+      <c r="F293" s="16"/>
+      <c r="G293" s="16"/>
+    </row>
+    <row r="294" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B294" s="17" t="s">
         <v>257</v>
       </c>
-      <c r="C294" s="21"/>
-      <c r="D294" s="21"/>
-      <c r="E294" s="21"/>
-      <c r="F294" s="21"/>
-      <c r="G294" s="21"/>
-    </row>
-    <row r="295" spans="2:7" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B295" s="8"/>
-      <c r="C295" s="21"/>
-      <c r="D295" s="21"/>
-      <c r="E295" s="21"/>
-      <c r="F295" s="21"/>
-      <c r="G295" s="21"/>
-    </row>
-    <row r="296" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B296" s="22" t="s">
+      <c r="C294" s="16"/>
+      <c r="D294" s="16"/>
+      <c r="E294" s="16"/>
+      <c r="F294" s="16"/>
+      <c r="G294" s="16"/>
+    </row>
+    <row r="295" spans="2:7" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B295" s="5"/>
+      <c r="C295" s="16"/>
+      <c r="D295" s="16"/>
+      <c r="E295" s="16"/>
+      <c r="F295" s="16"/>
+      <c r="G295" s="16"/>
+    </row>
+    <row r="296" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B296" s="17" t="s">
         <v>258</v>
       </c>
-      <c r="E296" s="22" t="s">
+      <c r="E296" s="17" t="s">
         <v>259</v>
       </c>
-      <c r="F296" s="21"/>
-      <c r="G296" s="21"/>
-    </row>
-    <row r="297" spans="2:7" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B297" s="30"/>
-      <c r="C297" s="31"/>
-      <c r="D297" s="31"/>
-      <c r="E297" s="30"/>
-      <c r="F297" s="32"/>
-      <c r="G297" s="32"/>
-    </row>
-    <row r="298" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B298" s="33" t="s">
+      <c r="F296" s="16"/>
+      <c r="G296" s="16"/>
+    </row>
+    <row r="297" spans="2:7" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B297" s="22"/>
+      <c r="C297" s="23"/>
+      <c r="D297" s="23"/>
+      <c r="E297" s="22"/>
+      <c r="F297" s="24"/>
+      <c r="G297" s="24"/>
+    </row>
+    <row r="298" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B298" s="25" t="s">
         <v>260</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="65">
-    <mergeCell ref="B265:G265"/>
-    <mergeCell ref="B266:G266"/>
-    <mergeCell ref="B267:G267"/>
-    <mergeCell ref="A268:H268"/>
-    <mergeCell ref="A269:H269"/>
-    <mergeCell ref="B235:G235"/>
-    <mergeCell ref="B236:G236"/>
-    <mergeCell ref="A237:H237"/>
-    <mergeCell ref="A238:H238"/>
-    <mergeCell ref="A239:H239"/>
+    <mergeCell ref="B35:G35"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="B4:G4"/>
+    <mergeCell ref="B5:G5"/>
+    <mergeCell ref="B6:G6"/>
+    <mergeCell ref="A7:H7"/>
+    <mergeCell ref="A8:H8"/>
+    <mergeCell ref="A9:H9"/>
+    <mergeCell ref="B33:G33"/>
+    <mergeCell ref="B34:G34"/>
+    <mergeCell ref="A88:H88"/>
+    <mergeCell ref="A36:H36"/>
+    <mergeCell ref="A37:H37"/>
+    <mergeCell ref="B57:G57"/>
+    <mergeCell ref="B58:G58"/>
+    <mergeCell ref="A59:H59"/>
+    <mergeCell ref="B60:G60"/>
+    <mergeCell ref="A61:H61"/>
+    <mergeCell ref="B84:G84"/>
+    <mergeCell ref="B85:G85"/>
+    <mergeCell ref="B86:G86"/>
+    <mergeCell ref="B87:G87"/>
+    <mergeCell ref="B148:G148"/>
+    <mergeCell ref="A89:H89"/>
+    <mergeCell ref="A90:H90"/>
+    <mergeCell ref="B115:G115"/>
+    <mergeCell ref="B117:G117"/>
+    <mergeCell ref="B118:G118"/>
+    <mergeCell ref="B119:G119"/>
+    <mergeCell ref="B120:G120"/>
+    <mergeCell ref="A121:H121"/>
+    <mergeCell ref="A122:H122"/>
+    <mergeCell ref="B146:G146"/>
+    <mergeCell ref="B147:G147"/>
+    <mergeCell ref="B205:G205"/>
+    <mergeCell ref="B149:G149"/>
+    <mergeCell ref="A150:H150"/>
+    <mergeCell ref="A151:H151"/>
+    <mergeCell ref="A152:H152"/>
+    <mergeCell ref="B177:G177"/>
+    <mergeCell ref="B178:G178"/>
+    <mergeCell ref="B179:G179"/>
+    <mergeCell ref="B180:G180"/>
+    <mergeCell ref="A181:H181"/>
+    <mergeCell ref="B203:G203"/>
+    <mergeCell ref="B204:G204"/>
     <mergeCell ref="B264:G264"/>
     <mergeCell ref="B206:G206"/>
     <mergeCell ref="A207:H207"/>
@@ -7265,54 +7317,16 @@
     <mergeCell ref="A209:H209"/>
     <mergeCell ref="B233:G233"/>
     <mergeCell ref="B234:G234"/>
-    <mergeCell ref="B179:G179"/>
-    <mergeCell ref="B180:G180"/>
-    <mergeCell ref="A181:H181"/>
-    <mergeCell ref="B203:G203"/>
-    <mergeCell ref="B204:G204"/>
-    <mergeCell ref="B205:G205"/>
-    <mergeCell ref="B149:G149"/>
-    <mergeCell ref="A150:H150"/>
-    <mergeCell ref="A151:H151"/>
-    <mergeCell ref="A152:H152"/>
-    <mergeCell ref="B177:G177"/>
-    <mergeCell ref="B178:G178"/>
-    <mergeCell ref="B120:G120"/>
-    <mergeCell ref="A121:H121"/>
-    <mergeCell ref="A122:H122"/>
-    <mergeCell ref="B146:G146"/>
-    <mergeCell ref="B147:G147"/>
-    <mergeCell ref="B148:G148"/>
-    <mergeCell ref="A89:H89"/>
-    <mergeCell ref="A90:H90"/>
-    <mergeCell ref="B115:G115"/>
-    <mergeCell ref="B117:G117"/>
-    <mergeCell ref="B118:G118"/>
-    <mergeCell ref="B119:G119"/>
-    <mergeCell ref="A61:H61"/>
-    <mergeCell ref="B84:G84"/>
-    <mergeCell ref="B85:G85"/>
-    <mergeCell ref="B86:G86"/>
-    <mergeCell ref="B87:G87"/>
-    <mergeCell ref="A88:H88"/>
-    <mergeCell ref="A36:H36"/>
-    <mergeCell ref="A37:H37"/>
-    <mergeCell ref="B57:G57"/>
-    <mergeCell ref="B58:G58"/>
-    <mergeCell ref="A59:H59"/>
-    <mergeCell ref="B60:G60"/>
-    <mergeCell ref="A7:H7"/>
-    <mergeCell ref="A8:H8"/>
-    <mergeCell ref="A9:H9"/>
-    <mergeCell ref="B33:G33"/>
-    <mergeCell ref="B34:G34"/>
-    <mergeCell ref="B35:G35"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="B4:G4"/>
-    <mergeCell ref="B5:G5"/>
-    <mergeCell ref="B6:G6"/>
+    <mergeCell ref="B235:G235"/>
+    <mergeCell ref="B236:G236"/>
+    <mergeCell ref="A237:H237"/>
+    <mergeCell ref="A238:H238"/>
+    <mergeCell ref="A239:H239"/>
+    <mergeCell ref="B265:G265"/>
+    <mergeCell ref="B266:G266"/>
+    <mergeCell ref="B267:G267"/>
+    <mergeCell ref="A268:H268"/>
+    <mergeCell ref="A269:H269"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
